--- a/songs/TellItToMyHeart_v1/quelle/struktur.xlsx
+++ b/songs/TellItToMyHeart_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>118</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0.375</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,19 @@
           <t>pause</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(7375, 5)   (Matrix: progScrollText("Tell it to my heart by Taylor Dayne", 23645, 90, getRandomColor(), 10))</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(7375, 5)   (Matrix: progScrollText("Tell it to my heart by Taylor Dayne", 23645, 90, getRandomColor(), 10))</t>
         </is>
@@ -551,13 +566,19 @@
           <t>intro chorus</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(16270, 1015, 10, 5, 26, 5, false, 4)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16270, 1015, 10, 5, 26, 5, false, 4)</t>
         </is>
@@ -572,13 +593,19 @@
           <t>verse</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(16270, 15, 510)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>progFullColors(16270, 15, 510)</t>
         </is>
@@ -593,13 +620,19 @@
           <t>bridge</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(14240, 4, 20)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progPalette(14240, 4, 20)</t>
         </is>
@@ -614,13 +647,19 @@
           <t>pause</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(1015, 25)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progBlack(1015, 25)</t>
         </is>
@@ -635,13 +674,19 @@
           <t>snareauftakt</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1015, 30, 65, 255, 255, 255)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1015, 30, 65, 255, 255, 255)</t>
         </is>
@@ -656,13 +701,19 @@
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(16275, 1015, 35, 20, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16275, 1015, 35, 20, 26, 5, true, 3)</t>
         </is>
@@ -677,13 +728,19 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(16270, 40, 510, false)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(16270, 40, 510, false)</t>
         </is>
@@ -698,13 +755,19 @@
           <t>bridge</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(14235, 3, 45)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progPalette(14235, 3, 45)</t>
         </is>
@@ -719,13 +782,19 @@
           <t>pause</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(1020, 50)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progBlack(1020, 50)</t>
         </is>
@@ -740,13 +809,19 @@
           <t>snareauftakt</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1015, 55, 65, 255, 255, 255)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1015, 55, 65, 255, 255, 255)</t>
         </is>
@@ -761,13 +836,19 @@
           <t>chorus 2</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(16270, 8, 60)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(16270, 8, 60)</t>
         </is>
@@ -782,13 +863,19 @@
           <t>SOLO</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(16270, 65, 50, true, true)   (Matrix: progOutline(16270, 65, 75))</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(16270, 65, 50, true, true)   (Matrix: progOutline(16270, 65, 75))</t>
         </is>
@@ -803,13 +890,19 @@
           <t>love on the run</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(16275, 70, 50, true, false)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(16275, 70, 50, true, false)</t>
         </is>
@@ -824,13 +917,19 @@
           <t>pause</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(1015, 75)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>progBlack(1015, 75)</t>
         </is>
@@ -845,13 +944,19 @@
           <t>snareauftakt</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1015, 80, 65, 255, 255, 255)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1015, 80, 65, 255, 255, 255)</t>
         </is>
@@ -866,13 +971,19 @@
           <t>chorus 3</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(16275, 510, 85, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16275, 510, 85, 5, 26, 5, true, 3)</t>
         </is>
@@ -887,13 +998,19 @@
           <t>chorus 4</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(16270, 8, 90)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(16270, 8, 90)</t>
         </is>
@@ -908,13 +1025,19 @@
           <t>outro F</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1015, 95, 95, 255, 255, 255)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1015, 95, 95, 255, 255, 255)</t>
         </is>
@@ -929,13 +1052,19 @@
           <t>outro G</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1020, 105, 65, 255, 255, 255)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1020, 105, 65, 255, 255, 255)</t>
         </is>
@@ -950,13 +1079,19 @@
           <t>outro A</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+! nur im Excel - der alte Code geht hier schon in Schwarz</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>! nur im Excel - der alte Code geht hier schon in Schwarz</t>
         </is>
@@ -976,10 +1111,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>0</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/TellItToMyHeart_v1/quelle/struktur.xlsx
+++ b/songs/TellItToMyHeart_v1/quelle/struktur.xlsx
@@ -8,26 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_DATEN\PlatformIO\Projects\LED-GIT_on_YULC\songs\TellItToMyHeart_v1\quelle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF8EEBA-7C4C-4917-911E-932BEDE7A9DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91745CD-E5D6-4493-82F1-349E7F2F1AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="5988" windowWidth="34560" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Struktur" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -36,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="53">
   <si>
     <t>Tell It To My Heart</t>
   </si>
@@ -44,19 +33,10 @@
     <t>Taylor Dayne</t>
   </si>
   <si>
-    <t>cakewalk</t>
-  </si>
-  <si>
     <t>Midi-StartNummer</t>
   </si>
   <si>
-    <t>takt</t>
-  </si>
-  <si>
     <t>BPM</t>
-  </si>
-  <si>
-    <t>minus 1 !!</t>
   </si>
   <si>
     <t>StartBit</t>
@@ -126,7 +106,7 @@
   </si>
   <si>
     <t>progSternNeu(16272, 1017, 35, 20, 26, 5, true, 3)
-Ausgabe: Blinder bei Takt 31,5 = 7119 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 31,75 = 7627 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 32 = 8136 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus
+Ausgabe: Blinder bei Takt 32,5 = 7119 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 32,75 = 7627 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 33 = 8136 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus
 Alter Effekt: drehender, wandernder Stern, Farbwechsel alle 2 Beats. Ende des vierten Takts drei kurze Blinder auf drei Vierteln hintereinander.</t>
   </si>
   <si>
@@ -136,7 +116,7 @@
     <t>2. Blinder, eine Viertel später, gleiche Form</t>
   </si>
   <si>
-    <t>3. Blinder auf die 1 von Takt 32, gleiche Form</t>
+    <t>3. Blinder auf die 1 des nächsten Takts, gleiche Form</t>
   </si>
   <si>
     <t>verse 2</t>
@@ -163,11 +143,8 @@
   </si>
   <si>
     <t>progFastBlingBling(16271, 8, 60)
-Ausgabe: Blinder bei Takt 55,5 = 7119 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 55,75 = 7627 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 56 = 8136 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus
+Ausgabe: Blinder bei Takt 56,5 = 7119 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 56,75 = 7627 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 57 = 8136 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus
 Alter Effekt: schnelle Einzelblitze. Ende des vierten Takts drei kurze Blinder auf drei Vierteln hintereinander.</t>
-  </si>
-  <si>
-    <t>3. Blinder auf die 1 von Takt 56, gleiche Form</t>
   </si>
   <si>
     <t>SOLO</t>
@@ -196,22 +173,16 @@
   </si>
   <si>
     <t>SCENE_FIRE, Farben SCHEME_FIRE
-Ausgabe: Blinder bei Takt 80,5 = 7119 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 80,75 = 7627 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 81 = 8136 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 84,5 = 15254 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 84,75 = 15763 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus
+Ausgabe: Blinder bei Takt 81,5 = 7119 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 81,75 = 7627 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 82 = 8136 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 85,5 = 15254 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 85,75 = 15763 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus
 Feuer auf allen Geräten in Rot, Orange und Gelb. Ende des vierten Takts drei kurze Blinder auf drei Vierteln; auf den letzten zwei Vierteln noch zwei, der dritte fällt auf die 1 von chorus 4.</t>
   </si>
   <si>
-    <t>3. Blinder auf die 1 von Takt 81, gleiche Form</t>
-  </si>
-  <si>
     <t>chorus 4</t>
   </si>
   <si>
     <t>SCENE_SPARKLE
-Ausgabe: Blinder bei Takt 85 = 0 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 88,5 = 7119 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 88,75 = 7627 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 89 = 8136 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus
+Ausgabe: Blinder bei Takt 86 = 0 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 89,5 = 7119 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 89,75 = 7627 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus, Blinder bei Takt 90 = 8136 ms, 305 ms lang, Blinder blendet 0 ms ein, 102 ms voll, 203 ms aus
 Schnelle Einzelblitze auf allen Geräten. Auf die 1 der dritte Blinder der Gruppe aus chorus 3; Ende des vierten Takts noch einmal drei kurze Blinder auf drei Vierteln.</t>
-  </si>
-  <si>
-    <t>3. Blinder auf die 1 von Takt 89, gleiche Form</t>
   </si>
   <si>
     <t>outro F</t>
@@ -636,38 +607,32 @@
       <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="9" t="s">
-        <v>2</v>
-      </c>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2">
         <v>21</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="G2" s="9" t="s">
-        <v>4</v>
-      </c>
+      <c r="G2" s="9"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2">
         <v>118</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="G3" s="9" t="s">
-        <v>6</v>
-      </c>
+      <c r="G3" s="9"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2">
         <v>0.375</v>
@@ -676,36 +641,36 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43.2" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="5"/>
@@ -714,7 +679,7 @@
     </row>
     <row r="7" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="6"/>
@@ -725,7 +690,7 @@
     </row>
     <row r="8" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
@@ -736,7 +701,7 @@
     </row>
     <row r="9" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
@@ -747,7 +712,7 @@
     </row>
     <row r="10" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
@@ -758,7 +723,7 @@
     </row>
     <row r="11" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
@@ -769,7 +734,7 @@
     </row>
     <row r="12" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
@@ -780,7 +745,7 @@
     </row>
     <row r="13" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
@@ -791,7 +756,7 @@
     </row>
     <row r="14" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
@@ -802,7 +767,7 @@
     </row>
     <row r="15" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="6"/>
@@ -813,7 +778,7 @@
     </row>
     <row r="16" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="6"/>
@@ -824,7 +789,7 @@
     </row>
     <row r="17" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="6"/>
@@ -835,7 +800,7 @@
     </row>
     <row r="18" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="6"/>
@@ -846,7 +811,7 @@
     </row>
     <row r="19" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="6"/>
@@ -857,7 +822,7 @@
     </row>
     <row r="20" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="6"/>
@@ -868,7 +833,7 @@
     </row>
     <row r="21" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="6"/>
@@ -879,13 +844,13 @@
     </row>
     <row r="22" spans="1:7" ht="28.8" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="5"/>
@@ -894,7 +859,7 @@
     </row>
     <row r="23" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="6"/>
@@ -905,7 +870,7 @@
     </row>
     <row r="24" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="6"/>
@@ -916,7 +881,7 @@
     </row>
     <row r="25" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="6"/>
@@ -927,7 +892,7 @@
     </row>
     <row r="26" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="6"/>
@@ -938,7 +903,7 @@
     </row>
     <row r="27" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="6"/>
@@ -949,7 +914,7 @@
     </row>
     <row r="28" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="6"/>
@@ -960,7 +925,7 @@
     </row>
     <row r="29" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="6"/>
@@ -971,7 +936,7 @@
     </row>
     <row r="30" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="6"/>
@@ -982,7 +947,7 @@
     </row>
     <row r="31" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="6"/>
@@ -993,7 +958,7 @@
     </row>
     <row r="32" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="6"/>
@@ -1004,7 +969,7 @@
     </row>
     <row r="33" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="6"/>
@@ -1015,7 +980,7 @@
     </row>
     <row r="34" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="6"/>
@@ -1026,7 +991,7 @@
     </row>
     <row r="35" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
-        <v>7.25</v>
+        <v>8.25</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="6"/>
@@ -1037,7 +1002,7 @@
     </row>
     <row r="36" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="6"/>
@@ -1048,7 +1013,7 @@
     </row>
     <row r="37" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
-        <v>7.75</v>
+        <v>8.75</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="6"/>
@@ -1059,7 +1024,7 @@
     </row>
     <row r="38" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="6"/>
@@ -1070,7 +1035,7 @@
     </row>
     <row r="39" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="6"/>
@@ -1081,7 +1046,7 @@
     </row>
     <row r="40" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="6"/>
@@ -1092,7 +1057,7 @@
     </row>
     <row r="41" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
-        <v>8.75</v>
+        <v>9.75</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="6"/>
@@ -1103,7 +1068,7 @@
     </row>
     <row r="42" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="6"/>
@@ -1114,7 +1079,7 @@
     </row>
     <row r="43" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
-        <v>9.25</v>
+        <v>10.25</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="6"/>
@@ -1125,7 +1090,7 @@
     </row>
     <row r="44" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="6"/>
@@ -1136,7 +1101,7 @@
     </row>
     <row r="45" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
-        <v>9.75</v>
+        <v>10.75</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="6"/>
@@ -1147,7 +1112,7 @@
     </row>
     <row r="46" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="6"/>
@@ -1158,7 +1123,7 @@
     </row>
     <row r="47" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
-        <v>10.25</v>
+        <v>11.25</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="6"/>
@@ -1169,7 +1134,7 @@
     </row>
     <row r="48" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="6"/>
@@ -1180,7 +1145,7 @@
     </row>
     <row r="49" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
-        <v>10.75</v>
+        <v>11.75</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="6"/>
@@ -1191,7 +1156,7 @@
     </row>
     <row r="50" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="6"/>
@@ -1202,7 +1167,7 @@
     </row>
     <row r="51" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
-        <v>11.25</v>
+        <v>12.25</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="6"/>
@@ -1213,7 +1178,7 @@
     </row>
     <row r="52" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="6"/>
@@ -1224,7 +1189,7 @@
     </row>
     <row r="53" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
-        <v>11.75</v>
+        <v>12.75</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="6"/>
@@ -1235,13 +1200,13 @@
     </row>
     <row r="54" spans="1:7" ht="28.8" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="5"/>
@@ -1250,7 +1215,7 @@
     </row>
     <row r="55" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
-        <v>12.25</v>
+        <v>13.25</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="6"/>
@@ -1261,7 +1226,7 @@
     </row>
     <row r="56" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="6"/>
@@ -1272,7 +1237,7 @@
     </row>
     <row r="57" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
-        <v>12.75</v>
+        <v>13.75</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="6"/>
@@ -1283,7 +1248,7 @@
     </row>
     <row r="58" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="6"/>
@@ -1294,7 +1259,7 @@
     </row>
     <row r="59" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
-        <v>13.25</v>
+        <v>14.25</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -1305,7 +1270,7 @@
     </row>
     <row r="60" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -1316,7 +1281,7 @@
     </row>
     <row r="61" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
-        <v>13.75</v>
+        <v>14.75</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -1327,7 +1292,7 @@
     </row>
     <row r="62" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="6"/>
@@ -1338,7 +1303,7 @@
     </row>
     <row r="63" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
-        <v>14.25</v>
+        <v>15.25</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="6"/>
@@ -1349,7 +1314,7 @@
     </row>
     <row r="64" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="6"/>
@@ -1360,7 +1325,7 @@
     </row>
     <row r="65" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
-        <v>14.75</v>
+        <v>15.75</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="6"/>
@@ -1371,7 +1336,7 @@
     </row>
     <row r="66" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B66" s="5"/>
       <c r="C66" s="6"/>
@@ -1382,7 +1347,7 @@
     </row>
     <row r="67" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
-        <v>15.25</v>
+        <v>16.25</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="6"/>
@@ -1393,7 +1358,7 @@
     </row>
     <row r="68" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="6"/>
@@ -1404,7 +1369,7 @@
     </row>
     <row r="69" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
-        <v>15.75</v>
+        <v>16.75</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="6"/>
@@ -1415,7 +1380,7 @@
     </row>
     <row r="70" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="6"/>
@@ -1426,7 +1391,7 @@
     </row>
     <row r="71" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
-        <v>16.25</v>
+        <v>17.25</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="6"/>
@@ -1437,7 +1402,7 @@
     </row>
     <row r="72" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="6"/>
@@ -1448,7 +1413,7 @@
     </row>
     <row r="73" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
-        <v>16.75</v>
+        <v>17.75</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -1459,7 +1424,7 @@
     </row>
     <row r="74" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="6"/>
@@ -1470,7 +1435,7 @@
     </row>
     <row r="75" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
-        <v>17.25</v>
+        <v>18.25</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="6"/>
@@ -1481,7 +1446,7 @@
     </row>
     <row r="76" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="6"/>
@@ -1492,7 +1457,7 @@
     </row>
     <row r="77" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
-        <v>17.75</v>
+        <v>18.75</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -1503,7 +1468,7 @@
     </row>
     <row r="78" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="6"/>
@@ -1514,7 +1479,7 @@
     </row>
     <row r="79" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
-        <v>18.25</v>
+        <v>19.25</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="6"/>
@@ -1525,7 +1490,7 @@
     </row>
     <row r="80" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="B80" s="5"/>
       <c r="C80" s="6"/>
@@ -1536,7 +1501,7 @@
     </row>
     <row r="81" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
-        <v>18.75</v>
+        <v>19.75</v>
       </c>
       <c r="B81" s="5"/>
       <c r="C81" s="6"/>
@@ -1547,7 +1512,7 @@
     </row>
     <row r="82" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B82" s="5"/>
       <c r="C82" s="6"/>
@@ -1558,7 +1523,7 @@
     </row>
     <row r="83" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
-        <v>19.25</v>
+        <v>20.25</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="6"/>
@@ -1569,7 +1534,7 @@
     </row>
     <row r="84" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="B84" s="5"/>
       <c r="C84" s="6"/>
@@ -1580,7 +1545,7 @@
     </row>
     <row r="85" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
-        <v>19.75</v>
+        <v>20.75</v>
       </c>
       <c r="B85" s="5"/>
       <c r="C85" s="6"/>
@@ -1591,13 +1556,13 @@
     </row>
     <row r="86" spans="1:7" ht="28.8" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="5"/>
@@ -1606,7 +1571,7 @@
     </row>
     <row r="87" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
-        <v>20.25</v>
+        <v>21.25</v>
       </c>
       <c r="B87" s="5"/>
       <c r="C87" s="6"/>
@@ -1617,7 +1582,7 @@
     </row>
     <row r="88" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="B88" s="5"/>
       <c r="C88" s="6"/>
@@ -1628,7 +1593,7 @@
     </row>
     <row r="89" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
-        <v>20.75</v>
+        <v>21.75</v>
       </c>
       <c r="B89" s="5"/>
       <c r="C89" s="6"/>
@@ -1639,7 +1604,7 @@
     </row>
     <row r="90" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B90" s="5"/>
       <c r="C90" s="6"/>
@@ -1650,7 +1615,7 @@
     </row>
     <row r="91" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
-        <v>21.25</v>
+        <v>22.25</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="6"/>
@@ -1661,7 +1626,7 @@
     </row>
     <row r="92" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="B92" s="5"/>
       <c r="C92" s="6"/>
@@ -1672,7 +1637,7 @@
     </row>
     <row r="93" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
-        <v>21.75</v>
+        <v>22.75</v>
       </c>
       <c r="B93" s="5"/>
       <c r="C93" s="6"/>
@@ -1683,7 +1648,7 @@
     </row>
     <row r="94" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B94" s="5"/>
       <c r="C94" s="6"/>
@@ -1694,7 +1659,7 @@
     </row>
     <row r="95" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
-        <v>22.25</v>
+        <v>23.25</v>
       </c>
       <c r="B95" s="5"/>
       <c r="C95" s="6"/>
@@ -1705,7 +1670,7 @@
     </row>
     <row r="96" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="B96" s="5"/>
       <c r="C96" s="6"/>
@@ -1716,7 +1681,7 @@
     </row>
     <row r="97" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
-        <v>22.75</v>
+        <v>23.75</v>
       </c>
       <c r="B97" s="5"/>
       <c r="C97" s="6"/>
@@ -1727,7 +1692,7 @@
     </row>
     <row r="98" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="6"/>
@@ -1738,7 +1703,7 @@
     </row>
     <row r="99" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
-        <v>23.25</v>
+        <v>24.25</v>
       </c>
       <c r="B99" s="5"/>
       <c r="C99" s="6"/>
@@ -1749,7 +1714,7 @@
     </row>
     <row r="100" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="B100" s="5"/>
       <c r="C100" s="6"/>
@@ -1760,7 +1725,7 @@
     </row>
     <row r="101" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
-        <v>23.75</v>
+        <v>24.75</v>
       </c>
       <c r="B101" s="5"/>
       <c r="C101" s="6"/>
@@ -1771,7 +1736,7 @@
     </row>
     <row r="102" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B102" s="5"/>
       <c r="C102" s="6"/>
@@ -1782,7 +1747,7 @@
     </row>
     <row r="103" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
-        <v>24.25</v>
+        <v>25.25</v>
       </c>
       <c r="B103" s="5"/>
       <c r="C103" s="6"/>
@@ -1793,7 +1758,7 @@
     </row>
     <row r="104" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
       <c r="B104" s="5"/>
       <c r="C104" s="6"/>
@@ -1804,7 +1769,7 @@
     </row>
     <row r="105" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
-        <v>24.75</v>
+        <v>25.75</v>
       </c>
       <c r="B105" s="5"/>
       <c r="C105" s="6"/>
@@ -1815,7 +1780,7 @@
     </row>
     <row r="106" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B106" s="5"/>
       <c r="C106" s="6"/>
@@ -1826,7 +1791,7 @@
     </row>
     <row r="107" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
-        <v>25.25</v>
+        <v>26.25</v>
       </c>
       <c r="B107" s="5"/>
       <c r="C107" s="6"/>
@@ -1837,7 +1802,7 @@
     </row>
     <row r="108" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="B108" s="5"/>
       <c r="C108" s="6"/>
@@ -1848,7 +1813,7 @@
     </row>
     <row r="109" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
-        <v>25.75</v>
+        <v>26.75</v>
       </c>
       <c r="B109" s="5"/>
       <c r="C109" s="6"/>
@@ -1859,7 +1824,7 @@
     </row>
     <row r="110" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B110" s="5"/>
       <c r="C110" s="6"/>
@@ -1870,7 +1835,7 @@
     </row>
     <row r="111" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
-        <v>26.25</v>
+        <v>27.25</v>
       </c>
       <c r="B111" s="5"/>
       <c r="C111" s="6"/>
@@ -1881,7 +1846,7 @@
     </row>
     <row r="112" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
-        <v>26.5</v>
+        <v>27.5</v>
       </c>
       <c r="B112" s="5"/>
       <c r="C112" s="6"/>
@@ -1892,7 +1857,7 @@
     </row>
     <row r="113" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
-        <v>26.75</v>
+        <v>27.75</v>
       </c>
       <c r="B113" s="5"/>
       <c r="C113" s="6"/>
@@ -1903,13 +1868,13 @@
     </row>
     <row r="114" spans="1:7" ht="28.8" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D114" s="6"/>
       <c r="E114" s="5"/>
@@ -1918,7 +1883,7 @@
     </row>
     <row r="115" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
-        <v>27.25</v>
+        <v>28.25</v>
       </c>
       <c r="B115" s="5"/>
       <c r="C115" s="6"/>
@@ -1929,13 +1894,13 @@
     </row>
     <row r="116" spans="1:7" ht="28.8" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="5"/>
@@ -1944,7 +1909,7 @@
     </row>
     <row r="117" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
-        <v>27.75</v>
+        <v>28.75</v>
       </c>
       <c r="B117" s="5"/>
       <c r="C117" s="6"/>
@@ -1955,13 +1920,13 @@
     </row>
     <row r="118" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="5"/>
@@ -1970,7 +1935,7 @@
     </row>
     <row r="119" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
-        <v>28.25</v>
+        <v>29.25</v>
       </c>
       <c r="B119" s="5"/>
       <c r="C119" s="6"/>
@@ -1981,7 +1946,7 @@
     </row>
     <row r="120" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
-        <v>28.5</v>
+        <v>29.5</v>
       </c>
       <c r="B120" s="5"/>
       <c r="C120" s="6"/>
@@ -1992,7 +1957,7 @@
     </row>
     <row r="121" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
-        <v>28.75</v>
+        <v>29.75</v>
       </c>
       <c r="B121" s="5"/>
       <c r="C121" s="6"/>
@@ -2003,7 +1968,7 @@
     </row>
     <row r="122" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B122" s="5"/>
       <c r="C122" s="6"/>
@@ -2014,7 +1979,7 @@
     </row>
     <row r="123" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
-        <v>29.25</v>
+        <v>30.25</v>
       </c>
       <c r="B123" s="5"/>
       <c r="C123" s="6"/>
@@ -2025,7 +1990,7 @@
     </row>
     <row r="124" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
-        <v>29.5</v>
+        <v>30.5</v>
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="6"/>
@@ -2036,7 +2001,7 @@
     </row>
     <row r="125" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
-        <v>29.75</v>
+        <v>30.75</v>
       </c>
       <c r="B125" s="5"/>
       <c r="C125" s="6"/>
@@ -2047,7 +2012,7 @@
     </row>
     <row r="126" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B126" s="5"/>
       <c r="C126" s="6"/>
@@ -2058,7 +2023,7 @@
     </row>
     <row r="127" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
-        <v>30.25</v>
+        <v>31.25</v>
       </c>
       <c r="B127" s="5"/>
       <c r="C127" s="6"/>
@@ -2069,7 +2034,7 @@
     </row>
     <row r="128" spans="1:7" ht="28.8" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
-        <v>30.5</v>
+        <v>31.5</v>
       </c>
       <c r="B128" s="5"/>
       <c r="C128" s="6"/>
@@ -2080,7 +2045,7 @@
     </row>
     <row r="129" spans="1:7" ht="28.8" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
-        <v>30.75</v>
+        <v>31.75</v>
       </c>
       <c r="B129" s="5"/>
       <c r="C129" s="6"/>
@@ -2091,7 +2056,7 @@
     </row>
     <row r="130" spans="1:7" ht="28.8" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B130" s="5"/>
       <c r="C130" s="6"/>
@@ -2102,7 +2067,7 @@
     </row>
     <row r="131" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
-        <v>31.25</v>
+        <v>32.25</v>
       </c>
       <c r="B131" s="5"/>
       <c r="C131" s="6"/>
@@ -2113,11 +2078,11 @@
     </row>
     <row r="132" spans="1:7" ht="43.2" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
-        <v>31.5</v>
+        <v>32.5</v>
       </c>
       <c r="B132" s="5"/>
       <c r="C132" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D132" s="6"/>
       <c r="E132" s="5"/>
@@ -2126,11 +2091,11 @@
     </row>
     <row r="133" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
-        <v>31.75</v>
+        <v>32.75</v>
       </c>
       <c r="B133" s="5"/>
       <c r="C133" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D133" s="6"/>
       <c r="E133" s="5"/>
@@ -2139,11 +2104,11 @@
     </row>
     <row r="134" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B134" s="5"/>
       <c r="C134" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D134" s="6"/>
       <c r="E134" s="5"/>
@@ -2152,7 +2117,7 @@
     </row>
     <row r="135" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
-        <v>32.25</v>
+        <v>33.25</v>
       </c>
       <c r="B135" s="5"/>
       <c r="C135" s="6"/>
@@ -2163,7 +2128,7 @@
     </row>
     <row r="136" spans="1:7" ht="43.2" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
-        <v>32.5</v>
+        <v>33.5</v>
       </c>
       <c r="B136" s="5"/>
       <c r="C136" s="6"/>
@@ -2174,7 +2139,7 @@
     </row>
     <row r="137" spans="1:7" ht="43.2" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
-        <v>32.75</v>
+        <v>33.75</v>
       </c>
       <c r="B137" s="5"/>
       <c r="C137" s="6"/>
@@ -2185,7 +2150,7 @@
     </row>
     <row r="138" spans="1:7" ht="43.2" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B138" s="5"/>
       <c r="C138" s="6"/>
@@ -2196,7 +2161,7 @@
     </row>
     <row r="139" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
-        <v>33.25</v>
+        <v>34.25</v>
       </c>
       <c r="B139" s="5"/>
       <c r="C139" s="6"/>
@@ -2207,7 +2172,7 @@
     </row>
     <row r="140" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
       <c r="B140" s="5"/>
       <c r="C140" s="6"/>
@@ -2218,7 +2183,7 @@
     </row>
     <row r="141" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
-        <v>33.75</v>
+        <v>34.75</v>
       </c>
       <c r="B141" s="5"/>
       <c r="C141" s="6"/>
@@ -2229,7 +2194,7 @@
     </row>
     <row r="142" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B142" s="5"/>
       <c r="C142" s="6"/>
@@ -2240,7 +2205,7 @@
     </row>
     <row r="143" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
-        <v>34.25</v>
+        <v>35.25</v>
       </c>
       <c r="B143" s="5"/>
       <c r="C143" s="6"/>
@@ -2251,7 +2216,7 @@
     </row>
     <row r="144" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="B144" s="5"/>
       <c r="C144" s="6"/>
@@ -2262,7 +2227,7 @@
     </row>
     <row r="145" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
-        <v>34.75</v>
+        <v>35.75</v>
       </c>
       <c r="B145" s="5"/>
       <c r="C145" s="6"/>
@@ -2273,7 +2238,7 @@
     </row>
     <row r="146" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B146" s="5"/>
       <c r="C146" s="6"/>
@@ -2284,7 +2249,7 @@
     </row>
     <row r="147" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
-        <v>35.25</v>
+        <v>36.25</v>
       </c>
       <c r="B147" s="5"/>
       <c r="C147" s="6"/>
@@ -2295,7 +2260,7 @@
     </row>
     <row r="148" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
       <c r="B148" s="5"/>
       <c r="C148" s="6"/>
@@ -2306,7 +2271,7 @@
     </row>
     <row r="149" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
-        <v>35.75</v>
+        <v>36.75</v>
       </c>
       <c r="B149" s="5"/>
       <c r="C149" s="6"/>
@@ -2317,13 +2282,13 @@
     </row>
     <row r="150" spans="1:7" ht="28.8" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D150" s="6"/>
       <c r="E150" s="5"/>
@@ -2332,7 +2297,7 @@
     </row>
     <row r="151" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
-        <v>36.25</v>
+        <v>37.25</v>
       </c>
       <c r="B151" s="5"/>
       <c r="C151" s="6"/>
@@ -2343,7 +2308,7 @@
     </row>
     <row r="152" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
-        <v>36.5</v>
+        <v>37.5</v>
       </c>
       <c r="B152" s="5"/>
       <c r="C152" s="6"/>
@@ -2354,7 +2319,7 @@
     </row>
     <row r="153" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
-        <v>36.75</v>
+        <v>37.75</v>
       </c>
       <c r="B153" s="5"/>
       <c r="C153" s="6"/>
@@ -2365,7 +2330,7 @@
     </row>
     <row r="154" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B154" s="5"/>
       <c r="C154" s="6"/>
@@ -2376,7 +2341,7 @@
     </row>
     <row r="155" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
-        <v>37.25</v>
+        <v>38.25</v>
       </c>
       <c r="B155" s="5"/>
       <c r="C155" s="6"/>
@@ -2387,7 +2352,7 @@
     </row>
     <row r="156" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
-        <v>37.5</v>
+        <v>38.5</v>
       </c>
       <c r="B156" s="5"/>
       <c r="C156" s="6"/>
@@ -2398,7 +2363,7 @@
     </row>
     <row r="157" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
-        <v>37.75</v>
+        <v>38.75</v>
       </c>
       <c r="B157" s="5"/>
       <c r="C157" s="6"/>
@@ -2409,7 +2374,7 @@
     </row>
     <row r="158" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B158" s="5"/>
       <c r="C158" s="6"/>
@@ -2420,7 +2385,7 @@
     </row>
     <row r="159" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
-        <v>38.25</v>
+        <v>39.25</v>
       </c>
       <c r="B159" s="5"/>
       <c r="C159" s="6"/>
@@ -2431,7 +2396,7 @@
     </row>
     <row r="160" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
-        <v>38.5</v>
+        <v>39.5</v>
       </c>
       <c r="B160" s="5"/>
       <c r="C160" s="6"/>
@@ -2442,7 +2407,7 @@
     </row>
     <row r="161" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
-        <v>38.75</v>
+        <v>39.75</v>
       </c>
       <c r="B161" s="5"/>
       <c r="C161" s="6"/>
@@ -2453,7 +2418,7 @@
     </row>
     <row r="162" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B162" s="5"/>
       <c r="C162" s="6"/>
@@ -2464,7 +2429,7 @@
     </row>
     <row r="163" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
-        <v>39.25</v>
+        <v>40.25</v>
       </c>
       <c r="B163" s="5"/>
       <c r="C163" s="6"/>
@@ -2475,7 +2440,7 @@
     </row>
     <row r="164" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
       <c r="B164" s="5"/>
       <c r="C164" s="6"/>
@@ -2486,7 +2451,7 @@
     </row>
     <row r="165" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
-        <v>39.75</v>
+        <v>40.75</v>
       </c>
       <c r="B165" s="5"/>
       <c r="C165" s="6"/>
@@ -2497,7 +2462,7 @@
     </row>
     <row r="166" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B166" s="5"/>
       <c r="C166" s="6"/>
@@ -2508,7 +2473,7 @@
     </row>
     <row r="167" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
-        <v>40.25</v>
+        <v>41.25</v>
       </c>
       <c r="B167" s="5"/>
       <c r="C167" s="6"/>
@@ -2519,7 +2484,7 @@
     </row>
     <row r="168" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
-        <v>40.5</v>
+        <v>41.5</v>
       </c>
       <c r="B168" s="5"/>
       <c r="C168" s="6"/>
@@ -2530,7 +2495,7 @@
     </row>
     <row r="169" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
-        <v>40.75</v>
+        <v>41.75</v>
       </c>
       <c r="B169" s="5"/>
       <c r="C169" s="6"/>
@@ -2541,7 +2506,7 @@
     </row>
     <row r="170" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B170" s="5"/>
       <c r="C170" s="6"/>
@@ -2552,7 +2517,7 @@
     </row>
     <row r="171" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
-        <v>41.25</v>
+        <v>42.25</v>
       </c>
       <c r="B171" s="5"/>
       <c r="C171" s="6"/>
@@ -2563,7 +2528,7 @@
     </row>
     <row r="172" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
-        <v>41.5</v>
+        <v>42.5</v>
       </c>
       <c r="B172" s="5"/>
       <c r="C172" s="6"/>
@@ -2574,7 +2539,7 @@
     </row>
     <row r="173" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
-        <v>41.75</v>
+        <v>42.75</v>
       </c>
       <c r="B173" s="5"/>
       <c r="C173" s="6"/>
@@ -2585,7 +2550,7 @@
     </row>
     <row r="174" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B174" s="5"/>
       <c r="C174" s="6"/>
@@ -2596,7 +2561,7 @@
     </row>
     <row r="175" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
-        <v>42.25</v>
+        <v>43.25</v>
       </c>
       <c r="B175" s="5"/>
       <c r="C175" s="6"/>
@@ -2607,7 +2572,7 @@
     </row>
     <row r="176" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
-        <v>42.5</v>
+        <v>43.5</v>
       </c>
       <c r="B176" s="5"/>
       <c r="C176" s="6"/>
@@ -2618,7 +2583,7 @@
     </row>
     <row r="177" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
-        <v>42.75</v>
+        <v>43.75</v>
       </c>
       <c r="B177" s="5"/>
       <c r="C177" s="6"/>
@@ -2629,7 +2594,7 @@
     </row>
     <row r="178" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B178" s="5"/>
       <c r="C178" s="6"/>
@@ -2640,7 +2605,7 @@
     </row>
     <row r="179" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
-        <v>43.25</v>
+        <v>44.25</v>
       </c>
       <c r="B179" s="5"/>
       <c r="C179" s="6"/>
@@ -2651,7 +2616,7 @@
     </row>
     <row r="180" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A180" s="4">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
       <c r="B180" s="5"/>
       <c r="C180" s="6"/>
@@ -2662,7 +2627,7 @@
     </row>
     <row r="181" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
-        <v>43.75</v>
+        <v>44.75</v>
       </c>
       <c r="B181" s="5"/>
       <c r="C181" s="6"/>
@@ -2673,13 +2638,13 @@
     </row>
     <row r="182" spans="1:7" ht="28.8" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A182" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D182" s="6"/>
       <c r="E182" s="5"/>
@@ -2688,7 +2653,7 @@
     </row>
     <row r="183" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
-        <v>44.25</v>
+        <v>45.25</v>
       </c>
       <c r="B183" s="5"/>
       <c r="C183" s="6"/>
@@ -2699,7 +2664,7 @@
     </row>
     <row r="184" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
-        <v>44.5</v>
+        <v>45.5</v>
       </c>
       <c r="B184" s="5"/>
       <c r="C184" s="6"/>
@@ -2710,7 +2675,7 @@
     </row>
     <row r="185" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
-        <v>44.75</v>
+        <v>45.75</v>
       </c>
       <c r="B185" s="5"/>
       <c r="C185" s="6"/>
@@ -2721,7 +2686,7 @@
     </row>
     <row r="186" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A186" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B186" s="5"/>
       <c r="C186" s="6"/>
@@ -2732,7 +2697,7 @@
     </row>
     <row r="187" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
-        <v>45.25</v>
+        <v>46.25</v>
       </c>
       <c r="B187" s="5"/>
       <c r="C187" s="6"/>
@@ -2743,7 +2708,7 @@
     </row>
     <row r="188" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
-        <v>45.5</v>
+        <v>46.5</v>
       </c>
       <c r="B188" s="5"/>
       <c r="C188" s="6"/>
@@ -2754,7 +2719,7 @@
     </row>
     <row r="189" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
-        <v>45.75</v>
+        <v>46.75</v>
       </c>
       <c r="B189" s="5"/>
       <c r="C189" s="6"/>
@@ -2765,7 +2730,7 @@
     </row>
     <row r="190" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B190" s="5"/>
       <c r="C190" s="6"/>
@@ -2776,7 +2741,7 @@
     </row>
     <row r="191" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
-        <v>46.25</v>
+        <v>47.25</v>
       </c>
       <c r="B191" s="5"/>
       <c r="C191" s="6"/>
@@ -2787,7 +2752,7 @@
     </row>
     <row r="192" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
-        <v>46.5</v>
+        <v>47.5</v>
       </c>
       <c r="B192" s="5"/>
       <c r="C192" s="6"/>
@@ -2798,7 +2763,7 @@
     </row>
     <row r="193" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
-        <v>46.75</v>
+        <v>47.75</v>
       </c>
       <c r="B193" s="5"/>
       <c r="C193" s="6"/>
@@ -2809,7 +2774,7 @@
     </row>
     <row r="194" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B194" s="5"/>
       <c r="C194" s="6"/>
@@ -2820,7 +2785,7 @@
     </row>
     <row r="195" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
-        <v>47.25</v>
+        <v>48.25</v>
       </c>
       <c r="B195" s="5"/>
       <c r="C195" s="6"/>
@@ -2831,7 +2796,7 @@
     </row>
     <row r="196" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A196" s="4">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="B196" s="5"/>
       <c r="C196" s="6"/>
@@ -2842,7 +2807,7 @@
     </row>
     <row r="197" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
-        <v>47.75</v>
+        <v>48.75</v>
       </c>
       <c r="B197" s="5"/>
       <c r="C197" s="6"/>
@@ -2853,7 +2818,7 @@
     </row>
     <row r="198" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B198" s="5"/>
       <c r="C198" s="6"/>
@@ -2864,7 +2829,7 @@
     </row>
     <row r="199" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
-        <v>48.25</v>
+        <v>49.25</v>
       </c>
       <c r="B199" s="5"/>
       <c r="C199" s="6"/>
@@ -2875,7 +2840,7 @@
     </row>
     <row r="200" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A200" s="4">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="B200" s="5"/>
       <c r="C200" s="6"/>
@@ -2886,7 +2851,7 @@
     </row>
     <row r="201" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
-        <v>48.75</v>
+        <v>49.75</v>
       </c>
       <c r="B201" s="5"/>
       <c r="C201" s="6"/>
@@ -2897,7 +2862,7 @@
     </row>
     <row r="202" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B202" s="5"/>
       <c r="C202" s="6"/>
@@ -2908,7 +2873,7 @@
     </row>
     <row r="203" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
-        <v>49.25</v>
+        <v>50.25</v>
       </c>
       <c r="B203" s="5"/>
       <c r="C203" s="6"/>
@@ -2919,7 +2884,7 @@
     </row>
     <row r="204" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A204" s="4">
-        <v>49.5</v>
+        <v>50.5</v>
       </c>
       <c r="B204" s="5"/>
       <c r="C204" s="6"/>
@@ -2930,7 +2895,7 @@
     </row>
     <row r="205" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
-        <v>49.75</v>
+        <v>50.75</v>
       </c>
       <c r="B205" s="5"/>
       <c r="C205" s="6"/>
@@ -2941,7 +2906,7 @@
     </row>
     <row r="206" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B206" s="5"/>
       <c r="C206" s="6"/>
@@ -2952,7 +2917,7 @@
     </row>
     <row r="207" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A207" s="4">
-        <v>50.25</v>
+        <v>51.25</v>
       </c>
       <c r="B207" s="5"/>
       <c r="C207" s="6"/>
@@ -2963,7 +2928,7 @@
     </row>
     <row r="208" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A208" s="4">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="B208" s="5"/>
       <c r="C208" s="6"/>
@@ -2974,7 +2939,7 @@
     </row>
     <row r="209" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
-        <v>50.75</v>
+        <v>51.75</v>
       </c>
       <c r="B209" s="5"/>
       <c r="C209" s="6"/>
@@ -2985,13 +2950,13 @@
     </row>
     <row r="210" spans="1:7" ht="28.8" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D210" s="6"/>
       <c r="E210" s="5"/>
@@ -3000,7 +2965,7 @@
     </row>
     <row r="211" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A211" s="4">
-        <v>51.25</v>
+        <v>52.25</v>
       </c>
       <c r="B211" s="5"/>
       <c r="C211" s="6"/>
@@ -3011,13 +2976,13 @@
     </row>
     <row r="212" spans="1:7" ht="28.8" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D212" s="6"/>
       <c r="E212" s="5"/>
@@ -3026,7 +2991,7 @@
     </row>
     <row r="213" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
-        <v>51.75</v>
+        <v>52.75</v>
       </c>
       <c r="B213" s="5"/>
       <c r="C213" s="6"/>
@@ -3037,13 +3002,13 @@
     </row>
     <row r="214" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D214" s="6"/>
       <c r="E214" s="5"/>
@@ -3052,7 +3017,7 @@
     </row>
     <row r="215" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A215" s="4">
-        <v>52.25</v>
+        <v>53.25</v>
       </c>
       <c r="B215" s="5"/>
       <c r="C215" s="6"/>
@@ -3063,7 +3028,7 @@
     </row>
     <row r="216" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="B216" s="5"/>
       <c r="C216" s="6"/>
@@ -3074,7 +3039,7 @@
     </row>
     <row r="217" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
-        <v>52.75</v>
+        <v>53.75</v>
       </c>
       <c r="B217" s="5"/>
       <c r="C217" s="6"/>
@@ -3085,7 +3050,7 @@
     </row>
     <row r="218" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B218" s="5"/>
       <c r="C218" s="6"/>
@@ -3096,7 +3061,7 @@
     </row>
     <row r="219" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
-        <v>53.25</v>
+        <v>54.25</v>
       </c>
       <c r="B219" s="5"/>
       <c r="C219" s="6"/>
@@ -3107,7 +3072,7 @@
     </row>
     <row r="220" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A220" s="4">
-        <v>53.5</v>
+        <v>54.5</v>
       </c>
       <c r="B220" s="5"/>
       <c r="C220" s="6"/>
@@ -3118,7 +3083,7 @@
     </row>
     <row r="221" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A221" s="4">
-        <v>53.75</v>
+        <v>54.75</v>
       </c>
       <c r="B221" s="5"/>
       <c r="C221" s="6"/>
@@ -3129,7 +3094,7 @@
     </row>
     <row r="222" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B222" s="5"/>
       <c r="C222" s="6"/>
@@ -3140,7 +3105,7 @@
     </row>
     <row r="223" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
-        <v>54.25</v>
+        <v>55.25</v>
       </c>
       <c r="B223" s="5"/>
       <c r="C223" s="6"/>
@@ -3151,7 +3116,7 @@
     </row>
     <row r="224" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A224" s="4">
-        <v>54.5</v>
+        <v>55.5</v>
       </c>
       <c r="B224" s="5"/>
       <c r="C224" s="6"/>
@@ -3162,7 +3127,7 @@
     </row>
     <row r="225" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A225" s="4">
-        <v>54.75</v>
+        <v>55.75</v>
       </c>
       <c r="B225" s="5"/>
       <c r="C225" s="6"/>
@@ -3173,7 +3138,7 @@
     </row>
     <row r="226" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B226" s="5"/>
       <c r="C226" s="6"/>
@@ -3184,7 +3149,7 @@
     </row>
     <row r="227" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A227" s="4">
-        <v>55.25</v>
+        <v>56.25</v>
       </c>
       <c r="B227" s="5"/>
       <c r="C227" s="6"/>
@@ -3195,11 +3160,11 @@
     </row>
     <row r="228" spans="1:7" ht="43.2" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A228" s="4">
-        <v>55.5</v>
+        <v>56.5</v>
       </c>
       <c r="B228" s="5"/>
       <c r="C228" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D228" s="6"/>
       <c r="E228" s="5"/>
@@ -3208,11 +3173,11 @@
     </row>
     <row r="229" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A229" s="4">
-        <v>55.75</v>
+        <v>56.75</v>
       </c>
       <c r="B229" s="5"/>
       <c r="C229" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D229" s="6"/>
       <c r="E229" s="5"/>
@@ -3221,11 +3186,11 @@
     </row>
     <row r="230" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A230" s="4">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B230" s="5"/>
       <c r="C230" s="6" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D230" s="6"/>
       <c r="E230" s="5"/>
@@ -3234,7 +3199,7 @@
     </row>
     <row r="231" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
-        <v>56.25</v>
+        <v>57.25</v>
       </c>
       <c r="B231" s="5"/>
       <c r="C231" s="6"/>
@@ -3245,7 +3210,7 @@
     </row>
     <row r="232" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A232" s="4">
-        <v>56.5</v>
+        <v>57.5</v>
       </c>
       <c r="B232" s="5"/>
       <c r="C232" s="6"/>
@@ -3256,7 +3221,7 @@
     </row>
     <row r="233" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
-        <v>56.75</v>
+        <v>57.75</v>
       </c>
       <c r="B233" s="5"/>
       <c r="C233" s="6"/>
@@ -3267,7 +3232,7 @@
     </row>
     <row r="234" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B234" s="5"/>
       <c r="C234" s="6"/>
@@ -3278,7 +3243,7 @@
     </row>
     <row r="235" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
-        <v>57.25</v>
+        <v>58.25</v>
       </c>
       <c r="B235" s="5"/>
       <c r="C235" s="6"/>
@@ -3289,7 +3254,7 @@
     </row>
     <row r="236" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A236" s="4">
-        <v>57.5</v>
+        <v>58.5</v>
       </c>
       <c r="B236" s="5"/>
       <c r="C236" s="6"/>
@@ -3300,7 +3265,7 @@
     </row>
     <row r="237" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
-        <v>57.75</v>
+        <v>58.75</v>
       </c>
       <c r="B237" s="5"/>
       <c r="C237" s="6"/>
@@ -3311,7 +3276,7 @@
     </row>
     <row r="238" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B238" s="5"/>
       <c r="C238" s="6"/>
@@ -3322,7 +3287,7 @@
     </row>
     <row r="239" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
-        <v>58.25</v>
+        <v>59.25</v>
       </c>
       <c r="B239" s="5"/>
       <c r="C239" s="6"/>
@@ -3333,7 +3298,7 @@
     </row>
     <row r="240" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
-        <v>58.5</v>
+        <v>59.5</v>
       </c>
       <c r="B240" s="5"/>
       <c r="C240" s="6"/>
@@ -3344,7 +3309,7 @@
     </row>
     <row r="241" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
-        <v>58.75</v>
+        <v>59.75</v>
       </c>
       <c r="B241" s="5"/>
       <c r="C241" s="6"/>
@@ -3355,7 +3320,7 @@
     </row>
     <row r="242" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B242" s="5"/>
       <c r="C242" s="6"/>
@@ -3366,7 +3331,7 @@
     </row>
     <row r="243" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
-        <v>59.25</v>
+        <v>60.25</v>
       </c>
       <c r="B243" s="5"/>
       <c r="C243" s="6"/>
@@ -3377,7 +3342,7 @@
     </row>
     <row r="244" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A244" s="4">
-        <v>59.5</v>
+        <v>60.5</v>
       </c>
       <c r="B244" s="5"/>
       <c r="C244" s="6"/>
@@ -3388,7 +3353,7 @@
     </row>
     <row r="245" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
-        <v>59.75</v>
+        <v>60.75</v>
       </c>
       <c r="B245" s="5"/>
       <c r="C245" s="6"/>
@@ -3399,13 +3364,13 @@
     </row>
     <row r="246" spans="1:7" ht="28.8" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D246" s="6"/>
       <c r="E246" s="5"/>
@@ -3414,7 +3379,7 @@
     </row>
     <row r="247" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
-        <v>60.25</v>
+        <v>61.25</v>
       </c>
       <c r="B247" s="5"/>
       <c r="C247" s="6"/>
@@ -3425,7 +3390,7 @@
     </row>
     <row r="248" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A248" s="4">
-        <v>60.5</v>
+        <v>61.5</v>
       </c>
       <c r="B248" s="5"/>
       <c r="C248" s="6"/>
@@ -3436,7 +3401,7 @@
     </row>
     <row r="249" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
-        <v>60.75</v>
+        <v>61.75</v>
       </c>
       <c r="B249" s="5"/>
       <c r="C249" s="6"/>
@@ -3447,7 +3412,7 @@
     </row>
     <row r="250" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B250" s="5"/>
       <c r="C250" s="6"/>
@@ -3458,7 +3423,7 @@
     </row>
     <row r="251" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
-        <v>61.25</v>
+        <v>62.25</v>
       </c>
       <c r="B251" s="5"/>
       <c r="C251" s="6"/>
@@ -3469,7 +3434,7 @@
     </row>
     <row r="252" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A252" s="4">
-        <v>61.5</v>
+        <v>62.5</v>
       </c>
       <c r="B252" s="5"/>
       <c r="C252" s="6"/>
@@ -3480,7 +3445,7 @@
     </row>
     <row r="253" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A253" s="4">
-        <v>61.75</v>
+        <v>62.75</v>
       </c>
       <c r="B253" s="5"/>
       <c r="C253" s="6"/>
@@ -3491,7 +3456,7 @@
     </row>
     <row r="254" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B254" s="5"/>
       <c r="C254" s="6"/>
@@ -3502,7 +3467,7 @@
     </row>
     <row r="255" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
-        <v>62.25</v>
+        <v>63.25</v>
       </c>
       <c r="B255" s="5"/>
       <c r="C255" s="6"/>
@@ -3513,7 +3478,7 @@
     </row>
     <row r="256" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A256" s="4">
-        <v>62.5</v>
+        <v>63.5</v>
       </c>
       <c r="B256" s="5"/>
       <c r="C256" s="6"/>
@@ -3524,7 +3489,7 @@
     </row>
     <row r="257" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A257" s="4">
-        <v>62.75</v>
+        <v>63.75</v>
       </c>
       <c r="B257" s="5"/>
       <c r="C257" s="6"/>
@@ -3535,7 +3500,7 @@
     </row>
     <row r="258" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B258" s="5"/>
       <c r="C258" s="6"/>
@@ -3546,7 +3511,7 @@
     </row>
     <row r="259" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A259" s="4">
-        <v>63.25</v>
+        <v>64.25</v>
       </c>
       <c r="B259" s="5"/>
       <c r="C259" s="6"/>
@@ -3557,7 +3522,7 @@
     </row>
     <row r="260" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A260" s="4">
-        <v>63.5</v>
+        <v>64.5</v>
       </c>
       <c r="B260" s="5"/>
       <c r="C260" s="6"/>
@@ -3568,7 +3533,7 @@
     </row>
     <row r="261" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
-        <v>63.75</v>
+        <v>64.75</v>
       </c>
       <c r="B261" s="5"/>
       <c r="C261" s="6"/>
@@ -3579,7 +3544,7 @@
     </row>
     <row r="262" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B262" s="5"/>
       <c r="C262" s="6"/>
@@ -3590,7 +3555,7 @@
     </row>
     <row r="263" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
-        <v>64.25</v>
+        <v>65.25</v>
       </c>
       <c r="B263" s="5"/>
       <c r="C263" s="6"/>
@@ -3601,7 +3566,7 @@
     </row>
     <row r="264" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
-        <v>64.5</v>
+        <v>65.5</v>
       </c>
       <c r="B264" s="5"/>
       <c r="C264" s="6"/>
@@ -3612,7 +3577,7 @@
     </row>
     <row r="265" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
-        <v>64.75</v>
+        <v>65.75</v>
       </c>
       <c r="B265" s="5"/>
       <c r="C265" s="6"/>
@@ -3623,7 +3588,7 @@
     </row>
     <row r="266" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B266" s="5"/>
       <c r="C266" s="6"/>
@@ -3634,7 +3599,7 @@
     </row>
     <row r="267" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
-        <v>65.25</v>
+        <v>66.25</v>
       </c>
       <c r="B267" s="5"/>
       <c r="C267" s="6"/>
@@ -3645,7 +3610,7 @@
     </row>
     <row r="268" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A268" s="4">
-        <v>65.5</v>
+        <v>66.5</v>
       </c>
       <c r="B268" s="5"/>
       <c r="C268" s="6"/>
@@ -3656,7 +3621,7 @@
     </row>
     <row r="269" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A269" s="4">
-        <v>65.75</v>
+        <v>66.75</v>
       </c>
       <c r="B269" s="5"/>
       <c r="C269" s="6"/>
@@ -3667,7 +3632,7 @@
     </row>
     <row r="270" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B270" s="5"/>
       <c r="C270" s="6"/>
@@ -3678,7 +3643,7 @@
     </row>
     <row r="271" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A271" s="4">
-        <v>66.25</v>
+        <v>67.25</v>
       </c>
       <c r="B271" s="5"/>
       <c r="C271" s="6"/>
@@ -3689,7 +3654,7 @@
     </row>
     <row r="272" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
-        <v>66.5</v>
+        <v>67.5</v>
       </c>
       <c r="B272" s="5"/>
       <c r="C272" s="6"/>
@@ -3700,7 +3665,7 @@
     </row>
     <row r="273" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A273" s="4">
-        <v>66.75</v>
+        <v>67.75</v>
       </c>
       <c r="B273" s="5"/>
       <c r="C273" s="6"/>
@@ -3711,7 +3676,7 @@
     </row>
     <row r="274" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A274" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B274" s="5"/>
       <c r="C274" s="6"/>
@@ -3722,7 +3687,7 @@
     </row>
     <row r="275" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A275" s="4">
-        <v>67.25</v>
+        <v>68.25</v>
       </c>
       <c r="B275" s="5"/>
       <c r="C275" s="6"/>
@@ -3733,7 +3698,7 @@
     </row>
     <row r="276" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A276" s="4">
-        <v>67.5</v>
+        <v>68.5</v>
       </c>
       <c r="B276" s="5"/>
       <c r="C276" s="6"/>
@@ -3744,7 +3709,7 @@
     </row>
     <row r="277" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
-        <v>67.75</v>
+        <v>68.75</v>
       </c>
       <c r="B277" s="5"/>
       <c r="C277" s="6"/>
@@ -3755,13 +3720,13 @@
     </row>
     <row r="278" spans="1:7" ht="28.8" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D278" s="6"/>
       <c r="E278" s="5"/>
@@ -3770,7 +3735,7 @@
     </row>
     <row r="279" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A279" s="4">
-        <v>68.25</v>
+        <v>69.25</v>
       </c>
       <c r="B279" s="5"/>
       <c r="C279" s="6"/>
@@ -3781,7 +3746,7 @@
     </row>
     <row r="280" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A280" s="4">
-        <v>68.5</v>
+        <v>69.5</v>
       </c>
       <c r="B280" s="5"/>
       <c r="C280" s="6"/>
@@ -3792,7 +3757,7 @@
     </row>
     <row r="281" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A281" s="4">
-        <v>68.75</v>
+        <v>69.75</v>
       </c>
       <c r="B281" s="5"/>
       <c r="C281" s="6"/>
@@ -3803,7 +3768,7 @@
     </row>
     <row r="282" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B282" s="5"/>
       <c r="C282" s="6"/>
@@ -3814,7 +3779,7 @@
     </row>
     <row r="283" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A283" s="4">
-        <v>69.25</v>
+        <v>70.25</v>
       </c>
       <c r="B283" s="5"/>
       <c r="C283" s="6"/>
@@ -3825,7 +3790,7 @@
     </row>
     <row r="284" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A284" s="4">
-        <v>69.5</v>
+        <v>70.5</v>
       </c>
       <c r="B284" s="5"/>
       <c r="C284" s="6"/>
@@ -3836,7 +3801,7 @@
     </row>
     <row r="285" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A285" s="4">
-        <v>69.75</v>
+        <v>70.75</v>
       </c>
       <c r="B285" s="5"/>
       <c r="C285" s="6"/>
@@ -3847,7 +3812,7 @@
     </row>
     <row r="286" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A286" s="4">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B286" s="5"/>
       <c r="C286" s="6"/>
@@ -3858,7 +3823,7 @@
     </row>
     <row r="287" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A287" s="4">
-        <v>70.25</v>
+        <v>71.25</v>
       </c>
       <c r="B287" s="5"/>
       <c r="C287" s="6"/>
@@ -3869,7 +3834,7 @@
     </row>
     <row r="288" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A288" s="4">
-        <v>70.5</v>
+        <v>71.5</v>
       </c>
       <c r="B288" s="5"/>
       <c r="C288" s="6"/>
@@ -3880,7 +3845,7 @@
     </row>
     <row r="289" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A289" s="4">
-        <v>70.75</v>
+        <v>71.75</v>
       </c>
       <c r="B289" s="5"/>
       <c r="C289" s="6"/>
@@ -3891,7 +3856,7 @@
     </row>
     <row r="290" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B290" s="5"/>
       <c r="C290" s="6"/>
@@ -3902,7 +3867,7 @@
     </row>
     <row r="291" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A291" s="4">
-        <v>71.25</v>
+        <v>72.25</v>
       </c>
       <c r="B291" s="5"/>
       <c r="C291" s="6"/>
@@ -3913,7 +3878,7 @@
     </row>
     <row r="292" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A292" s="4">
-        <v>71.5</v>
+        <v>72.5</v>
       </c>
       <c r="B292" s="5"/>
       <c r="C292" s="6"/>
@@ -3924,7 +3889,7 @@
     </row>
     <row r="293" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A293" s="4">
-        <v>71.75</v>
+        <v>72.75</v>
       </c>
       <c r="B293" s="5"/>
       <c r="C293" s="6"/>
@@ -3935,7 +3900,7 @@
     </row>
     <row r="294" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B294" s="5"/>
       <c r="C294" s="6"/>
@@ -3946,7 +3911,7 @@
     </row>
     <row r="295" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A295" s="4">
-        <v>72.25</v>
+        <v>73.25</v>
       </c>
       <c r="B295" s="5"/>
       <c r="C295" s="6"/>
@@ -3957,7 +3922,7 @@
     </row>
     <row r="296" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A296" s="4">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="B296" s="5"/>
       <c r="C296" s="6"/>
@@ -3968,7 +3933,7 @@
     </row>
     <row r="297" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A297" s="4">
-        <v>72.75</v>
+        <v>73.75</v>
       </c>
       <c r="B297" s="5"/>
       <c r="C297" s="6"/>
@@ -3979,7 +3944,7 @@
     </row>
     <row r="298" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A298" s="4">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B298" s="5"/>
       <c r="C298" s="6"/>
@@ -3990,7 +3955,7 @@
     </row>
     <row r="299" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A299" s="4">
-        <v>73.25</v>
+        <v>74.25</v>
       </c>
       <c r="B299" s="5"/>
       <c r="C299" s="6"/>
@@ -4001,7 +3966,7 @@
     </row>
     <row r="300" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A300" s="4">
-        <v>73.5</v>
+        <v>74.5</v>
       </c>
       <c r="B300" s="5"/>
       <c r="C300" s="6"/>
@@ -4012,7 +3977,7 @@
     </row>
     <row r="301" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A301" s="4">
-        <v>73.75</v>
+        <v>74.75</v>
       </c>
       <c r="B301" s="5"/>
       <c r="C301" s="6"/>
@@ -4023,7 +3988,7 @@
     </row>
     <row r="302" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A302" s="4">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B302" s="5"/>
       <c r="C302" s="6"/>
@@ -4034,7 +3999,7 @@
     </row>
     <row r="303" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A303" s="4">
-        <v>74.25</v>
+        <v>75.25</v>
       </c>
       <c r="B303" s="5"/>
       <c r="C303" s="6"/>
@@ -4045,7 +4010,7 @@
     </row>
     <row r="304" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A304" s="4">
-        <v>74.5</v>
+        <v>75.5</v>
       </c>
       <c r="B304" s="5"/>
       <c r="C304" s="6"/>
@@ -4056,7 +4021,7 @@
     </row>
     <row r="305" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A305" s="4">
-        <v>74.75</v>
+        <v>75.75</v>
       </c>
       <c r="B305" s="5"/>
       <c r="C305" s="6"/>
@@ -4067,7 +4032,7 @@
     </row>
     <row r="306" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B306" s="5"/>
       <c r="C306" s="6"/>
@@ -4078,7 +4043,7 @@
     </row>
     <row r="307" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A307" s="4">
-        <v>75.25</v>
+        <v>76.25</v>
       </c>
       <c r="B307" s="5"/>
       <c r="C307" s="6"/>
@@ -4089,7 +4054,7 @@
     </row>
     <row r="308" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A308" s="4">
-        <v>75.5</v>
+        <v>76.5</v>
       </c>
       <c r="B308" s="5"/>
       <c r="C308" s="6"/>
@@ -4100,7 +4065,7 @@
     </row>
     <row r="309" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A309" s="4">
-        <v>75.75</v>
+        <v>76.75</v>
       </c>
       <c r="B309" s="5"/>
       <c r="C309" s="6"/>
@@ -4111,13 +4076,13 @@
     </row>
     <row r="310" spans="1:7" ht="28.8" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A310" s="4">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D310" s="6"/>
       <c r="E310" s="5"/>
@@ -4126,7 +4091,7 @@
     </row>
     <row r="311" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A311" s="4">
-        <v>76.25</v>
+        <v>77.25</v>
       </c>
       <c r="B311" s="5"/>
       <c r="C311" s="6"/>
@@ -4137,13 +4102,13 @@
     </row>
     <row r="312" spans="1:7" ht="28.8" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A312" s="4">
-        <v>76.5</v>
+        <v>77.5</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D312" s="6"/>
       <c r="E312" s="5"/>
@@ -4152,7 +4117,7 @@
     </row>
     <row r="313" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A313" s="4">
-        <v>76.75</v>
+        <v>77.75</v>
       </c>
       <c r="B313" s="5"/>
       <c r="C313" s="6"/>
@@ -4163,13 +4128,13 @@
     </row>
     <row r="314" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="4">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D314" s="6"/>
       <c r="E314" s="5"/>
@@ -4178,7 +4143,7 @@
     </row>
     <row r="315" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A315" s="4">
-        <v>77.25</v>
+        <v>78.25</v>
       </c>
       <c r="B315" s="5"/>
       <c r="C315" s="6"/>
@@ -4189,7 +4154,7 @@
     </row>
     <row r="316" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A316" s="4">
-        <v>77.5</v>
+        <v>78.5</v>
       </c>
       <c r="B316" s="5"/>
       <c r="C316" s="6"/>
@@ -4200,7 +4165,7 @@
     </row>
     <row r="317" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A317" s="4">
-        <v>77.75</v>
+        <v>78.75</v>
       </c>
       <c r="B317" s="5"/>
       <c r="C317" s="6"/>
@@ -4211,7 +4176,7 @@
     </row>
     <row r="318" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A318" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B318" s="5"/>
       <c r="C318" s="6"/>
@@ -4222,7 +4187,7 @@
     </row>
     <row r="319" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A319" s="4">
-        <v>78.25</v>
+        <v>79.25</v>
       </c>
       <c r="B319" s="5"/>
       <c r="C319" s="6"/>
@@ -4233,7 +4198,7 @@
     </row>
     <row r="320" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A320" s="4">
-        <v>78.5</v>
+        <v>79.5</v>
       </c>
       <c r="B320" s="5"/>
       <c r="C320" s="6"/>
@@ -4244,7 +4209,7 @@
     </row>
     <row r="321" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A321" s="4">
-        <v>78.75</v>
+        <v>79.75</v>
       </c>
       <c r="B321" s="5"/>
       <c r="C321" s="6"/>
@@ -4255,7 +4220,7 @@
     </row>
     <row r="322" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A322" s="4">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B322" s="5"/>
       <c r="C322" s="6"/>
@@ -4266,7 +4231,7 @@
     </row>
     <row r="323" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A323" s="4">
-        <v>79.25</v>
+        <v>80.25</v>
       </c>
       <c r="B323" s="5"/>
       <c r="C323" s="6"/>
@@ -4277,7 +4242,7 @@
     </row>
     <row r="324" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A324" s="4">
-        <v>79.5</v>
+        <v>80.5</v>
       </c>
       <c r="B324" s="5"/>
       <c r="C324" s="6"/>
@@ -4288,7 +4253,7 @@
     </row>
     <row r="325" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A325" s="4">
-        <v>79.75</v>
+        <v>80.75</v>
       </c>
       <c r="B325" s="5"/>
       <c r="C325" s="6"/>
@@ -4299,7 +4264,7 @@
     </row>
     <row r="326" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A326" s="4">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B326" s="5"/>
       <c r="C326" s="6"/>
@@ -4310,7 +4275,7 @@
     </row>
     <row r="327" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A327" s="4">
-        <v>80.25</v>
+        <v>81.25</v>
       </c>
       <c r="B327" s="5"/>
       <c r="C327" s="6"/>
@@ -4321,11 +4286,11 @@
     </row>
     <row r="328" spans="1:7" ht="43.2" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A328" s="4">
-        <v>80.5</v>
+        <v>81.5</v>
       </c>
       <c r="B328" s="5"/>
       <c r="C328" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D328" s="6"/>
       <c r="E328" s="5"/>
@@ -4334,11 +4299,11 @@
     </row>
     <row r="329" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A329" s="4">
-        <v>80.75</v>
+        <v>81.75</v>
       </c>
       <c r="B329" s="5"/>
       <c r="C329" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D329" s="6"/>
       <c r="E329" s="5"/>
@@ -4347,11 +4312,11 @@
     </row>
     <row r="330" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A330" s="4">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B330" s="5"/>
       <c r="C330" s="6" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="D330" s="6"/>
       <c r="E330" s="5"/>
@@ -4360,7 +4325,7 @@
     </row>
     <row r="331" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A331" s="4">
-        <v>81.25</v>
+        <v>82.25</v>
       </c>
       <c r="B331" s="5"/>
       <c r="C331" s="6"/>
@@ -4371,7 +4336,7 @@
     </row>
     <row r="332" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A332" s="4">
-        <v>81.5</v>
+        <v>82.5</v>
       </c>
       <c r="B332" s="5"/>
       <c r="C332" s="6"/>
@@ -4382,7 +4347,7 @@
     </row>
     <row r="333" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A333" s="4">
-        <v>81.75</v>
+        <v>82.75</v>
       </c>
       <c r="B333" s="5"/>
       <c r="C333" s="6"/>
@@ -4393,7 +4358,7 @@
     </row>
     <row r="334" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A334" s="4">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B334" s="5"/>
       <c r="C334" s="6"/>
@@ -4404,7 +4369,7 @@
     </row>
     <row r="335" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A335" s="4">
-        <v>82.25</v>
+        <v>83.25</v>
       </c>
       <c r="B335" s="5"/>
       <c r="C335" s="6"/>
@@ -4415,7 +4380,7 @@
     </row>
     <row r="336" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A336" s="4">
-        <v>82.5</v>
+        <v>83.5</v>
       </c>
       <c r="B336" s="5"/>
       <c r="C336" s="6"/>
@@ -4426,7 +4391,7 @@
     </row>
     <row r="337" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A337" s="4">
-        <v>82.75</v>
+        <v>83.75</v>
       </c>
       <c r="B337" s="5"/>
       <c r="C337" s="6"/>
@@ -4437,7 +4402,7 @@
     </row>
     <row r="338" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A338" s="4">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B338" s="5"/>
       <c r="C338" s="6"/>
@@ -4448,7 +4413,7 @@
     </row>
     <row r="339" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A339" s="4">
-        <v>83.25</v>
+        <v>84.25</v>
       </c>
       <c r="B339" s="5"/>
       <c r="C339" s="6"/>
@@ -4459,7 +4424,7 @@
     </row>
     <row r="340" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A340" s="4">
-        <v>83.5</v>
+        <v>84.5</v>
       </c>
       <c r="B340" s="5"/>
       <c r="C340" s="6"/>
@@ -4470,7 +4435,7 @@
     </row>
     <row r="341" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A341" s="4">
-        <v>83.75</v>
+        <v>84.75</v>
       </c>
       <c r="B341" s="5"/>
       <c r="C341" s="6"/>
@@ -4481,7 +4446,7 @@
     </row>
     <row r="342" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A342" s="4">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B342" s="5"/>
       <c r="C342" s="6"/>
@@ -4492,7 +4457,7 @@
     </row>
     <row r="343" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A343" s="4">
-        <v>84.25</v>
+        <v>85.25</v>
       </c>
       <c r="B343" s="5"/>
       <c r="C343" s="6"/>
@@ -4503,11 +4468,11 @@
     </row>
     <row r="344" spans="1:7" ht="43.2" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A344" s="4">
-        <v>84.5</v>
+        <v>85.5</v>
       </c>
       <c r="B344" s="5"/>
       <c r="C344" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D344" s="6"/>
       <c r="E344" s="5"/>
@@ -4516,11 +4481,11 @@
     </row>
     <row r="345" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A345" s="4">
-        <v>84.75</v>
+        <v>85.75</v>
       </c>
       <c r="B345" s="5"/>
       <c r="C345" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D345" s="6"/>
       <c r="E345" s="5"/>
@@ -4529,13 +4494,13 @@
     </row>
     <row r="346" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="4">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C346" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D346" s="6"/>
       <c r="E346" s="5"/>
@@ -4544,7 +4509,7 @@
     </row>
     <row r="347" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A347" s="4">
-        <v>85.25</v>
+        <v>86.25</v>
       </c>
       <c r="B347" s="5"/>
       <c r="C347" s="6"/>
@@ -4555,7 +4520,7 @@
     </row>
     <row r="348" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A348" s="4">
-        <v>85.5</v>
+        <v>86.5</v>
       </c>
       <c r="B348" s="5"/>
       <c r="C348" s="6"/>
@@ -4566,7 +4531,7 @@
     </row>
     <row r="349" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A349" s="4">
-        <v>85.75</v>
+        <v>86.75</v>
       </c>
       <c r="B349" s="5"/>
       <c r="C349" s="6"/>
@@ -4577,7 +4542,7 @@
     </row>
     <row r="350" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A350" s="4">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B350" s="5"/>
       <c r="C350" s="6"/>
@@ -4588,7 +4553,7 @@
     </row>
     <row r="351" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A351" s="4">
-        <v>86.25</v>
+        <v>87.25</v>
       </c>
       <c r="B351" s="5"/>
       <c r="C351" s="6"/>
@@ -4599,7 +4564,7 @@
     </row>
     <row r="352" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A352" s="4">
-        <v>86.5</v>
+        <v>87.5</v>
       </c>
       <c r="B352" s="5"/>
       <c r="C352" s="6"/>
@@ -4610,7 +4575,7 @@
     </row>
     <row r="353" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A353" s="4">
-        <v>86.75</v>
+        <v>87.75</v>
       </c>
       <c r="B353" s="5"/>
       <c r="C353" s="6"/>
@@ -4621,7 +4586,7 @@
     </row>
     <row r="354" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A354" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B354" s="5"/>
       <c r="C354" s="6"/>
@@ -4632,7 +4597,7 @@
     </row>
     <row r="355" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A355" s="4">
-        <v>87.25</v>
+        <v>88.25</v>
       </c>
       <c r="B355" s="5"/>
       <c r="C355" s="6"/>
@@ -4643,7 +4608,7 @@
     </row>
     <row r="356" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A356" s="4">
-        <v>87.5</v>
+        <v>88.5</v>
       </c>
       <c r="B356" s="5"/>
       <c r="C356" s="6"/>
@@ -4654,7 +4619,7 @@
     </row>
     <row r="357" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A357" s="4">
-        <v>87.75</v>
+        <v>88.75</v>
       </c>
       <c r="B357" s="5"/>
       <c r="C357" s="6"/>
@@ -4665,7 +4630,7 @@
     </row>
     <row r="358" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A358" s="4">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B358" s="5"/>
       <c r="C358" s="6"/>
@@ -4676,7 +4641,7 @@
     </row>
     <row r="359" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A359" s="4">
-        <v>88.25</v>
+        <v>89.25</v>
       </c>
       <c r="B359" s="5"/>
       <c r="C359" s="6"/>
@@ -4687,11 +4652,11 @@
     </row>
     <row r="360" spans="1:7" ht="43.2" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A360" s="4">
-        <v>88.5</v>
+        <v>89.5</v>
       </c>
       <c r="B360" s="5"/>
       <c r="C360" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D360" s="6"/>
       <c r="E360" s="5"/>
@@ -4700,11 +4665,11 @@
     </row>
     <row r="361" spans="1:7" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A361" s="4">
-        <v>88.75</v>
+        <v>89.75</v>
       </c>
       <c r="B361" s="5"/>
       <c r="C361" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D361" s="6"/>
       <c r="E361" s="5"/>
@@ -4713,11 +4678,11 @@
     </row>
     <row r="362" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A362" s="4">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B362" s="5"/>
       <c r="C362" s="6" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D362" s="6"/>
       <c r="E362" s="5"/>
@@ -4726,7 +4691,7 @@
     </row>
     <row r="363" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A363" s="4">
-        <v>89.25</v>
+        <v>90.25</v>
       </c>
       <c r="B363" s="5"/>
       <c r="C363" s="6"/>
@@ -4737,7 +4702,7 @@
     </row>
     <row r="364" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A364" s="4">
-        <v>89.5</v>
+        <v>90.5</v>
       </c>
       <c r="B364" s="5"/>
       <c r="C364" s="6"/>
@@ -4748,7 +4713,7 @@
     </row>
     <row r="365" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A365" s="4">
-        <v>89.75</v>
+        <v>90.75</v>
       </c>
       <c r="B365" s="5"/>
       <c r="C365" s="6"/>
@@ -4759,7 +4724,7 @@
     </row>
     <row r="366" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A366" s="4">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B366" s="5"/>
       <c r="C366" s="6"/>
@@ -4770,7 +4735,7 @@
     </row>
     <row r="367" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A367" s="4">
-        <v>90.25</v>
+        <v>91.25</v>
       </c>
       <c r="B367" s="5"/>
       <c r="C367" s="6"/>
@@ -4781,7 +4746,7 @@
     </row>
     <row r="368" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A368" s="4">
-        <v>90.5</v>
+        <v>91.5</v>
       </c>
       <c r="B368" s="5"/>
       <c r="C368" s="6"/>
@@ -4792,7 +4757,7 @@
     </row>
     <row r="369" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A369" s="4">
-        <v>90.75</v>
+        <v>91.75</v>
       </c>
       <c r="B369" s="5"/>
       <c r="C369" s="6"/>
@@ -4803,7 +4768,7 @@
     </row>
     <row r="370" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A370" s="4">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B370" s="5"/>
       <c r="C370" s="6"/>
@@ -4814,7 +4779,7 @@
     </row>
     <row r="371" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A371" s="4">
-        <v>91.25</v>
+        <v>92.25</v>
       </c>
       <c r="B371" s="5"/>
       <c r="C371" s="6"/>
@@ -4825,7 +4790,7 @@
     </row>
     <row r="372" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A372" s="4">
-        <v>91.5</v>
+        <v>92.5</v>
       </c>
       <c r="B372" s="5"/>
       <c r="C372" s="6"/>
@@ -4836,7 +4801,7 @@
     </row>
     <row r="373" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A373" s="4">
-        <v>91.75</v>
+        <v>92.75</v>
       </c>
       <c r="B373" s="5"/>
       <c r="C373" s="6"/>
@@ -4847,7 +4812,7 @@
     </row>
     <row r="374" spans="1:7" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A374" s="4">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B374" s="5"/>
       <c r="C374" s="6"/>
@@ -4858,7 +4823,7 @@
     </row>
     <row r="375" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A375" s="4">
-        <v>92.25</v>
+        <v>93.25</v>
       </c>
       <c r="B375" s="5"/>
       <c r="C375" s="6"/>
@@ -4869,7 +4834,7 @@
     </row>
     <row r="376" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A376" s="4">
-        <v>92.5</v>
+        <v>93.5</v>
       </c>
       <c r="B376" s="5"/>
       <c r="C376" s="6"/>
@@ -4880,7 +4845,7 @@
     </row>
     <row r="377" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A377" s="4">
-        <v>92.75</v>
+        <v>93.75</v>
       </c>
       <c r="B377" s="5"/>
       <c r="C377" s="6"/>
@@ -4891,13 +4856,13 @@
     </row>
     <row r="378" spans="1:7" ht="28.8" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A378" s="4">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B378" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C378" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D378" s="6"/>
       <c r="E378" s="5"/>
@@ -4906,7 +4871,7 @@
     </row>
     <row r="379" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A379" s="4">
-        <v>93.25</v>
+        <v>94.25</v>
       </c>
       <c r="B379" s="5"/>
       <c r="C379" s="6"/>
@@ -4917,13 +4882,13 @@
     </row>
     <row r="380" spans="1:7" ht="28.8" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A380" s="4">
-        <v>93.5</v>
+        <v>94.5</v>
       </c>
       <c r="B380" s="5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C380" s="6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D380" s="6"/>
       <c r="E380" s="5"/>
@@ -4932,7 +4897,7 @@
     </row>
     <row r="381" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A381" s="4">
-        <v>93.75</v>
+        <v>94.75</v>
       </c>
       <c r="B381" s="5"/>
       <c r="C381" s="6"/>
@@ -4943,13 +4908,13 @@
     </row>
     <row r="382" spans="1:7" ht="28.8" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A382" s="4">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B382" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C382" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D382" s="6"/>
       <c r="E382" s="5"/>
@@ -4958,7 +4923,7 @@
     </row>
     <row r="383" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A383" s="4">
-        <v>94.25</v>
+        <v>95.25</v>
       </c>
       <c r="B383" s="5"/>
       <c r="C383" s="6"/>
@@ -4969,7 +4934,7 @@
     </row>
     <row r="384" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A384" s="4">
-        <v>94.5</v>
+        <v>95.5</v>
       </c>
       <c r="B384" s="5"/>
       <c r="C384" s="6"/>
@@ -4980,7 +4945,7 @@
     </row>
     <row r="385" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A385" s="4">
-        <v>94.75</v>
+        <v>95.75</v>
       </c>
       <c r="B385" s="5"/>
       <c r="C385" s="6"/>
@@ -4991,7 +4956,7 @@
     </row>
     <row r="386" spans="1:7" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A386" s="4">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B386" s="5"/>
       <c r="C386" s="6"/>
@@ -5002,7 +4967,7 @@
     </row>
     <row r="387" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A387" s="4">
-        <v>95.25</v>
+        <v>96.25</v>
       </c>
       <c r="B387" s="5"/>
       <c r="C387" s="6"/>
@@ -5013,7 +4978,7 @@
     </row>
     <row r="388" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A388" s="4">
-        <v>95.5</v>
+        <v>96.5</v>
       </c>
       <c r="B388" s="5"/>
       <c r="C388" s="6"/>
@@ -5024,7 +4989,7 @@
     </row>
     <row r="389" spans="1:7" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A389" s="4">
-        <v>95.75</v>
+        <v>96.75</v>
       </c>
       <c r="B389" s="5"/>
       <c r="C389" s="6"/>
@@ -5035,13 +5000,13 @@
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A390" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B390" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C390" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E390">
         <v>0</v>

--- a/songs/TellItToMyHeart_v1/quelle/struktur.xlsx
+++ b/songs/TellItToMyHeart_v1/quelle/struktur.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>progBlack(7373, 5)
+          <t>progBlack(7373, 3)
 Alles schwarz bis zum Einsatz (die Matrix zeigt den Titel-Lauftext).</t>
         </is>
       </c>
@@ -742,7 +742,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(16271, 1017, 10, 5, 26, 5, false, 4)
+          <t>progSternNeu(16271, 1017, 4, 5, 26, 5, false, 4)
 Alter Effekt: drehender Stern, fest in der Mitte, Farbwechsel alle 2 Beats.</t>
         </is>
       </c>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>progFullColors(16271, 15, 508)
+          <t>progFullColors(16271, 5, 508)
 Alter Effekt: alles in einer Farbe, pro Beat eine neue Zufallsfarbe.</t>
         </is>
       </c>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(1017, 30, 65, 255, 255, 255)
+          <t>progStrobo(1017, 8, 65, 255, 255, 255)
 Alter Effekt: weißer Strobo (65 ms) auf den Snare-Auftakt.</t>
         </is>
       </c>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(16272, 1017, 35, 20, 26, 5, true, 3)
+          <t>progSternNeu(16272, 1017, 9, 20, 26, 5, true, 3)
 Ausgabe: Blinder voll bei Takt 32,5 = 7119 ms, 407 ms lang, Blinder blendet in den 102 ms davor ein, 102 ms voll, 203 ms aus, Blinder voll bei Takt 32,75 = 7627 ms, 407 ms lang, Blinder blendet in den 102 ms davor ein, 102 ms voll, 203 ms aus, Blinder voll bei Takt 33 = 8136 ms, 407 ms lang, Blinder blendet in den 102 ms davor ein, 102 ms voll, 203 ms aus
 Alter Effekt: drehender, wandernder Stern, Farbwechsel alle 2 Beats. Ende des vierten Takts drei kurze Blinder auf drei Vierteln hintereinander.</t>
         </is>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="C212" s="6" t="inlineStr">
         <is>
-          <t>progBlack(1017, 55)
+          <t>progBlack(1017, 13)
 Ausgabe: Blinder bei 0 ms, 1017 ms lang, Blinder blendet 0 ms ein, 763 ms voll, 254 ms aus
 Starker Blinder statt Strobo: alle Geräte blenden 2 Beats lang voll warmweiß auf, bis der Chorus einsetzt.</t>
         </is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="C214" s="6" t="inlineStr">
         <is>
-          <t>progFastBlingBling(16271, 8, 60)
+          <t>progFastBlingBling(16271, 8, 14)
 Ausgabe: Blinder voll bei Takt 56,5 = 7119 ms, 407 ms lang, Blinder blendet in den 102 ms davor ein, 102 ms voll, 203 ms aus, Blinder voll bei Takt 56,75 = 7627 ms, 407 ms lang, Blinder blendet in den 102 ms davor ein, 102 ms voll, 203 ms aus, Blinder voll bei Takt 57 = 8136 ms, 407 ms lang, Blinder blendet in den 102 ms davor ein, 102 ms voll, 203 ms aus
 Alter Effekt: schnelle Einzelblitze. Ende des vierten Takts drei kurze Blinder auf drei Vierteln hintereinander.</t>
         </is>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="C278" s="6" t="inlineStr">
         <is>
-          <t>progWaterRipple(16272, 70, 50, true, false)
+          <t>progWaterRipple(16272, 16, 50, true, false)
 Alter Effekt: Wasserringe an zufälligen Stellen, mit Farbverlauf.</t>
         </is>
       </c>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="C312" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(1016, 80, 65, 255, 255, 255)
+          <t>progStrobo(1016, 18, 65, 255, 255, 255)
 Alter Effekt: weißer Strobo (65 ms) auf den Snare-Auftakt.</t>
         </is>
       </c>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="C378" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(1017, 95, 95, 255, 255, 255)
+          <t>progStrobo(1017, 21, 95, 255, 255, 255)
 Alter Effekt: weißer Strobo (95 ms).</t>
         </is>
       </c>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="C380" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(1017, 100, 65, 255, 255, 255)
+          <t>progStrobo(1017, 22, 65, 255, 255, 255)
 Alter Effekt: schnellerer weißer Strobo (65 ms).</t>
         </is>
       </c>

--- a/songs/TellItToMyHeart_v1/quelle/struktur.xlsx
+++ b/songs/TellItToMyHeart_v1/quelle/struktur.xlsx
@@ -37,7 +37,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -82,6 +88,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -448,16 +457,17 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G390"/>
+  <dimension ref="A1:H390"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="21.21875" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="21.21875" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +481,7 @@
           <t>Taylor Dayne</t>
         </is>
       </c>
-      <c r="G1" s="9" t="n"/>
+      <c r="H1" s="9" t="n"/>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
@@ -483,7 +493,8 @@
         <v>21</v>
       </c>
       <c r="D2" s="2" t="n"/>
-      <c r="G2" s="9" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="H2" s="9" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -495,7 +506,8 @@
         <v>118</v>
       </c>
       <c r="D3" s="2" t="n"/>
-      <c r="G3" s="9" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="H3" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n"/>
@@ -508,6 +520,7 @@
         <v>0.375</v>
       </c>
       <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -527,20 +540,25 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Alter Effekt (temporär)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Änderungswunsch</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -562,9 +580,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
+      <c r="E6" s="6" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" hidden="1" outlineLevel="2">
       <c r="A7" s="4" t="n">
@@ -573,9 +592,10 @@
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
+      <c r="E7" s="6" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" hidden="1" outlineLevel="2">
       <c r="A8" s="4" t="n">
@@ -584,9 +604,10 @@
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" hidden="1" outlineLevel="2">
       <c r="A9" s="4" t="n">
@@ -595,9 +616,10 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="6" t="n"/>
     </row>
     <row r="10" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A10" s="4" t="n">
@@ -606,9 +628,10 @@
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
+      <c r="E10" s="6" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" hidden="1" outlineLevel="2">
       <c r="A11" s="4" t="n">
@@ -617,9 +640,10 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
+      <c r="E11" s="6" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" hidden="1" outlineLevel="2">
       <c r="A12" s="4" t="n">
@@ -628,9 +652,10 @@
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
+      <c r="E12" s="6" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" hidden="1" outlineLevel="2">
       <c r="A13" s="4" t="n">
@@ -639,9 +664,10 @@
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
+      <c r="E13" s="6" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A14" s="4" t="n">
@@ -650,9 +676,10 @@
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
+      <c r="E14" s="6" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" hidden="1" outlineLevel="2">
       <c r="A15" s="4" t="n">
@@ -661,9 +688,10 @@
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
+      <c r="E15" s="6" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" hidden="1" outlineLevel="2">
       <c r="A16" s="4" t="n">
@@ -672,9 +700,10 @@
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
+      <c r="E16" s="6" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="6" t="n"/>
     </row>
     <row r="17" hidden="1" outlineLevel="2">
       <c r="A17" s="4" t="n">
@@ -683,9 +712,10 @@
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="E17" s="6" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="6" t="n"/>
     </row>
     <row r="18" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A18" s="4" t="n">
@@ -694,9 +724,10 @@
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="n"/>
+      <c r="E18" s="6" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" hidden="1" outlineLevel="2">
       <c r="A19" s="4" t="n">
@@ -705,9 +736,10 @@
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="n"/>
+      <c r="E19" s="6" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" hidden="1" outlineLevel="2">
       <c r="A20" s="4" t="n">
@@ -716,9 +748,10 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="5" t="n"/>
+      <c r="E20" s="6" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" hidden="1" outlineLevel="2">
       <c r="A21" s="4" t="n">
@@ -727,9 +760,10 @@
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="5" t="n"/>
+      <c r="E21" s="6" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" collapsed="1" ht="28.8" customHeight="1">
       <c r="A22" s="4" t="n">
@@ -747,9 +781,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="5" t="n"/>
+      <c r="E22" s="6" t="n"/>
       <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" hidden="1" outlineLevel="2">
       <c r="A23" s="4" t="n">
@@ -758,9 +793,10 @@
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="5" t="n"/>
+      <c r="E23" s="6" t="n"/>
       <c r="F23" s="5" t="n"/>
-      <c r="G23" s="6" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="6" t="n"/>
     </row>
     <row r="24" hidden="1" outlineLevel="2">
       <c r="A24" s="4" t="n">
@@ -769,9 +805,10 @@
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="5" t="n"/>
+      <c r="E24" s="6" t="n"/>
       <c r="F24" s="5" t="n"/>
-      <c r="G24" s="6" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="6" t="n"/>
     </row>
     <row r="25" hidden="1" outlineLevel="2">
       <c r="A25" s="4" t="n">
@@ -780,9 +817,10 @@
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="5" t="n"/>
+      <c r="E25" s="6" t="n"/>
       <c r="F25" s="5" t="n"/>
-      <c r="G25" s="6" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="6" t="n"/>
     </row>
     <row r="26" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A26" s="4" t="n">
@@ -791,9 +829,10 @@
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6" t="n"/>
       <c r="D26" s="6" t="n"/>
-      <c r="E26" s="5" t="n"/>
+      <c r="E26" s="6" t="n"/>
       <c r="F26" s="5" t="n"/>
-      <c r="G26" s="6" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="6" t="n"/>
     </row>
     <row r="27" hidden="1" outlineLevel="2">
       <c r="A27" s="4" t="n">
@@ -802,9 +841,10 @@
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="6" t="n"/>
-      <c r="E27" s="5" t="n"/>
+      <c r="E27" s="6" t="n"/>
       <c r="F27" s="5" t="n"/>
-      <c r="G27" s="6" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="6" t="n"/>
     </row>
     <row r="28" hidden="1" outlineLevel="2">
       <c r="A28" s="4" t="n">
@@ -813,9 +853,10 @@
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6" t="n"/>
       <c r="D28" s="6" t="n"/>
-      <c r="E28" s="5" t="n"/>
+      <c r="E28" s="6" t="n"/>
       <c r="F28" s="5" t="n"/>
-      <c r="G28" s="6" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="6" t="n"/>
     </row>
     <row r="29" hidden="1" outlineLevel="2">
       <c r="A29" s="4" t="n">
@@ -824,9 +865,10 @@
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6" t="n"/>
       <c r="D29" s="6" t="n"/>
-      <c r="E29" s="5" t="n"/>
+      <c r="E29" s="6" t="n"/>
       <c r="F29" s="5" t="n"/>
-      <c r="G29" s="6" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="6" t="n"/>
     </row>
     <row r="30" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A30" s="4" t="n">
@@ -835,9 +877,10 @@
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6" t="n"/>
       <c r="D30" s="6" t="n"/>
-      <c r="E30" s="5" t="n"/>
+      <c r="E30" s="6" t="n"/>
       <c r="F30" s="5" t="n"/>
-      <c r="G30" s="6" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="6" t="n"/>
     </row>
     <row r="31" hidden="1" outlineLevel="2">
       <c r="A31" s="4" t="n">
@@ -846,9 +889,10 @@
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6" t="n"/>
       <c r="D31" s="6" t="n"/>
-      <c r="E31" s="5" t="n"/>
+      <c r="E31" s="6" t="n"/>
       <c r="F31" s="5" t="n"/>
-      <c r="G31" s="6" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="6" t="n"/>
     </row>
     <row r="32" hidden="1" outlineLevel="2">
       <c r="A32" s="4" t="n">
@@ -857,9 +901,10 @@
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6" t="n"/>
       <c r="D32" s="6" t="n"/>
-      <c r="E32" s="5" t="n"/>
+      <c r="E32" s="6" t="n"/>
       <c r="F32" s="5" t="n"/>
-      <c r="G32" s="6" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="6" t="n"/>
     </row>
     <row r="33" hidden="1" outlineLevel="2">
       <c r="A33" s="4" t="n">
@@ -868,9 +913,10 @@
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6" t="n"/>
       <c r="D33" s="6" t="n"/>
-      <c r="E33" s="5" t="n"/>
+      <c r="E33" s="6" t="n"/>
       <c r="F33" s="5" t="n"/>
-      <c r="G33" s="6" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="6" t="n"/>
     </row>
     <row r="34" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A34" s="4" t="n">
@@ -879,9 +925,10 @@
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6" t="n"/>
       <c r="D34" s="6" t="n"/>
-      <c r="E34" s="5" t="n"/>
+      <c r="E34" s="6" t="n"/>
       <c r="F34" s="5" t="n"/>
-      <c r="G34" s="6" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="6" t="n"/>
     </row>
     <row r="35" hidden="1" outlineLevel="2">
       <c r="A35" s="4" t="n">
@@ -890,9 +937,10 @@
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6" t="n"/>
       <c r="D35" s="6" t="n"/>
-      <c r="E35" s="5" t="n"/>
+      <c r="E35" s="6" t="n"/>
       <c r="F35" s="5" t="n"/>
-      <c r="G35" s="6" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="6" t="n"/>
     </row>
     <row r="36" hidden="1" outlineLevel="2">
       <c r="A36" s="4" t="n">
@@ -901,9 +949,10 @@
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6" t="n"/>
       <c r="D36" s="6" t="n"/>
-      <c r="E36" s="5" t="n"/>
+      <c r="E36" s="6" t="n"/>
       <c r="F36" s="5" t="n"/>
-      <c r="G36" s="6" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="6" t="n"/>
     </row>
     <row r="37" hidden="1" outlineLevel="2">
       <c r="A37" s="4" t="n">
@@ -912,9 +961,10 @@
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6" t="n"/>
       <c r="D37" s="6" t="n"/>
-      <c r="E37" s="5" t="n"/>
+      <c r="E37" s="6" t="n"/>
       <c r="F37" s="5" t="n"/>
-      <c r="G37" s="6" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="6" t="n"/>
     </row>
     <row r="38" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A38" s="4" t="n">
@@ -923,9 +973,10 @@
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6" t="n"/>
       <c r="D38" s="6" t="n"/>
-      <c r="E38" s="5" t="n"/>
+      <c r="E38" s="6" t="n"/>
       <c r="F38" s="5" t="n"/>
-      <c r="G38" s="6" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="6" t="n"/>
     </row>
     <row r="39" hidden="1" outlineLevel="2">
       <c r="A39" s="4" t="n">
@@ -934,9 +985,10 @@
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6" t="n"/>
       <c r="D39" s="6" t="n"/>
-      <c r="E39" s="5" t="n"/>
+      <c r="E39" s="6" t="n"/>
       <c r="F39" s="5" t="n"/>
-      <c r="G39" s="6" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="6" t="n"/>
     </row>
     <row r="40" hidden="1" outlineLevel="2">
       <c r="A40" s="4" t="n">
@@ -945,9 +997,10 @@
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6" t="n"/>
       <c r="D40" s="6" t="n"/>
-      <c r="E40" s="5" t="n"/>
+      <c r="E40" s="6" t="n"/>
       <c r="F40" s="5" t="n"/>
-      <c r="G40" s="6" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="6" t="n"/>
     </row>
     <row r="41" hidden="1" outlineLevel="2">
       <c r="A41" s="4" t="n">
@@ -956,9 +1009,10 @@
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6" t="n"/>
       <c r="D41" s="6" t="n"/>
-      <c r="E41" s="5" t="n"/>
+      <c r="E41" s="6" t="n"/>
       <c r="F41" s="5" t="n"/>
-      <c r="G41" s="6" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="6" t="n"/>
     </row>
     <row r="42" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A42" s="4" t="n">
@@ -967,9 +1021,10 @@
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6" t="n"/>
       <c r="D42" s="6" t="n"/>
-      <c r="E42" s="5" t="n"/>
+      <c r="E42" s="6" t="n"/>
       <c r="F42" s="5" t="n"/>
-      <c r="G42" s="6" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="6" t="n"/>
     </row>
     <row r="43" hidden="1" outlineLevel="2">
       <c r="A43" s="4" t="n">
@@ -978,9 +1033,10 @@
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="6" t="n"/>
-      <c r="E43" s="5" t="n"/>
+      <c r="E43" s="6" t="n"/>
       <c r="F43" s="5" t="n"/>
-      <c r="G43" s="6" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="6" t="n"/>
     </row>
     <row r="44" hidden="1" outlineLevel="2">
       <c r="A44" s="4" t="n">
@@ -989,9 +1045,10 @@
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6" t="n"/>
       <c r="D44" s="6" t="n"/>
-      <c r="E44" s="5" t="n"/>
+      <c r="E44" s="6" t="n"/>
       <c r="F44" s="5" t="n"/>
-      <c r="G44" s="6" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="6" t="n"/>
     </row>
     <row r="45" hidden="1" outlineLevel="2">
       <c r="A45" s="4" t="n">
@@ -1000,9 +1057,10 @@
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="6" t="n"/>
       <c r="D45" s="6" t="n"/>
-      <c r="E45" s="5" t="n"/>
+      <c r="E45" s="6" t="n"/>
       <c r="F45" s="5" t="n"/>
-      <c r="G45" s="6" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="6" t="n"/>
     </row>
     <row r="46" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A46" s="4" t="n">
@@ -1011,9 +1069,10 @@
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="6" t="n"/>
       <c r="D46" s="6" t="n"/>
-      <c r="E46" s="5" t="n"/>
+      <c r="E46" s="6" t="n"/>
       <c r="F46" s="5" t="n"/>
-      <c r="G46" s="6" t="n"/>
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="6" t="n"/>
     </row>
     <row r="47" hidden="1" outlineLevel="2">
       <c r="A47" s="4" t="n">
@@ -1022,9 +1081,10 @@
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="6" t="n"/>
       <c r="D47" s="6" t="n"/>
-      <c r="E47" s="5" t="n"/>
+      <c r="E47" s="6" t="n"/>
       <c r="F47" s="5" t="n"/>
-      <c r="G47" s="6" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="6" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="2">
       <c r="A48" s="4" t="n">
@@ -1033,9 +1093,10 @@
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6" t="n"/>
       <c r="D48" s="6" t="n"/>
-      <c r="E48" s="5" t="n"/>
+      <c r="E48" s="6" t="n"/>
       <c r="F48" s="5" t="n"/>
-      <c r="G48" s="6" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="6" t="n"/>
     </row>
     <row r="49" hidden="1" outlineLevel="2">
       <c r="A49" s="4" t="n">
@@ -1044,9 +1105,10 @@
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="6" t="n"/>
       <c r="D49" s="6" t="n"/>
-      <c r="E49" s="5" t="n"/>
+      <c r="E49" s="6" t="n"/>
       <c r="F49" s="5" t="n"/>
-      <c r="G49" s="6" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="6" t="n"/>
     </row>
     <row r="50" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A50" s="4" t="n">
@@ -1055,9 +1117,10 @@
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="6" t="n"/>
       <c r="D50" s="6" t="n"/>
-      <c r="E50" s="5" t="n"/>
+      <c r="E50" s="6" t="n"/>
       <c r="F50" s="5" t="n"/>
-      <c r="G50" s="6" t="n"/>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="6" t="n"/>
     </row>
     <row r="51" hidden="1" outlineLevel="2">
       <c r="A51" s="4" t="n">
@@ -1066,9 +1129,10 @@
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="6" t="n"/>
       <c r="D51" s="6" t="n"/>
-      <c r="E51" s="5" t="n"/>
+      <c r="E51" s="6" t="n"/>
       <c r="F51" s="5" t="n"/>
-      <c r="G51" s="6" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="6" t="n"/>
     </row>
     <row r="52" hidden="1" outlineLevel="2">
       <c r="A52" s="4" t="n">
@@ -1077,9 +1141,10 @@
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="6" t="n"/>
       <c r="D52" s="6" t="n"/>
-      <c r="E52" s="5" t="n"/>
+      <c r="E52" s="6" t="n"/>
       <c r="F52" s="5" t="n"/>
-      <c r="G52" s="6" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="6" t="n"/>
     </row>
     <row r="53" hidden="1" outlineLevel="2">
       <c r="A53" s="4" t="n">
@@ -1088,9 +1153,10 @@
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="6" t="n"/>
       <c r="D53" s="6" t="n"/>
-      <c r="E53" s="5" t="n"/>
+      <c r="E53" s="6" t="n"/>
       <c r="F53" s="5" t="n"/>
-      <c r="G53" s="6" t="n"/>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="6" t="n"/>
     </row>
     <row r="54" collapsed="1" ht="28.8" customHeight="1">
       <c r="A54" s="4" t="n">
@@ -1101,16 +1167,22 @@
           <t>verse</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_HEART, Farben SCHEME_FIRE
+Strophe neu (18.10.2026, statt der alten Vollfarben): 'tell it to my heart' - alle Geräte schlagen auf jedem Beat wie ein Herz in Rot/Orange/Gelb, die Matrix zeigt eine Lissajous-Schleife</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>progFullColors(16271, 5, 508)
 Alter Effekt: alles in einer Farbe, pro Beat eine neue Zufallsfarbe.</t>
         </is>
       </c>
-      <c r="D54" s="6" t="n"/>
-      <c r="E54" s="5" t="n"/>
+      <c r="E54" s="6" t="n"/>
       <c r="F54" s="5" t="n"/>
-      <c r="G54" s="6" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="6" t="n"/>
     </row>
     <row r="55" hidden="1" outlineLevel="2">
       <c r="A55" s="4" t="n">
@@ -1119,9 +1191,10 @@
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="6" t="n"/>
       <c r="D55" s="6" t="n"/>
-      <c r="E55" s="5" t="n"/>
+      <c r="E55" s="6" t="n"/>
       <c r="F55" s="5" t="n"/>
-      <c r="G55" s="6" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="6" t="n"/>
     </row>
     <row r="56" hidden="1" outlineLevel="2">
       <c r="A56" s="4" t="n">
@@ -1130,9 +1203,10 @@
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="6" t="n"/>
       <c r="D56" s="6" t="n"/>
-      <c r="E56" s="5" t="n"/>
+      <c r="E56" s="6" t="n"/>
       <c r="F56" s="5" t="n"/>
-      <c r="G56" s="6" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="6" t="n"/>
     </row>
     <row r="57" hidden="1" outlineLevel="2">
       <c r="A57" s="4" t="n">
@@ -1141,9 +1215,10 @@
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="6" t="n"/>
       <c r="D57" s="6" t="n"/>
-      <c r="E57" s="5" t="n"/>
+      <c r="E57" s="6" t="n"/>
       <c r="F57" s="5" t="n"/>
-      <c r="G57" s="6" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="6" t="n"/>
     </row>
     <row r="58" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A58" s="4" t="n">
@@ -1152,9 +1227,10 @@
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="6" t="n"/>
       <c r="D58" s="6" t="n"/>
-      <c r="E58" s="5" t="n"/>
+      <c r="E58" s="6" t="n"/>
       <c r="F58" s="5" t="n"/>
-      <c r="G58" s="6" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="6" t="n"/>
     </row>
     <row r="59" hidden="1" outlineLevel="2">
       <c r="A59" s="4" t="n">
@@ -1163,9 +1239,10 @@
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="6" t="n"/>
       <c r="D59" s="6" t="n"/>
-      <c r="E59" s="5" t="n"/>
+      <c r="E59" s="6" t="n"/>
       <c r="F59" s="5" t="n"/>
-      <c r="G59" s="6" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="6" t="n"/>
     </row>
     <row r="60" hidden="1" outlineLevel="2">
       <c r="A60" s="4" t="n">
@@ -1174,9 +1251,10 @@
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="6" t="n"/>
       <c r="D60" s="6" t="n"/>
-      <c r="E60" s="5" t="n"/>
+      <c r="E60" s="6" t="n"/>
       <c r="F60" s="5" t="n"/>
-      <c r="G60" s="6" t="n"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="6" t="n"/>
     </row>
     <row r="61" hidden="1" outlineLevel="2">
       <c r="A61" s="4" t="n">
@@ -1185,9 +1263,10 @@
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="6" t="n"/>
       <c r="D61" s="6" t="n"/>
-      <c r="E61" s="5" t="n"/>
+      <c r="E61" s="6" t="n"/>
       <c r="F61" s="5" t="n"/>
-      <c r="G61" s="6" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="6" t="n"/>
     </row>
     <row r="62" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A62" s="4" t="n">
@@ -1196,9 +1275,10 @@
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="6" t="n"/>
       <c r="D62" s="6" t="n"/>
-      <c r="E62" s="5" t="n"/>
+      <c r="E62" s="6" t="n"/>
       <c r="F62" s="5" t="n"/>
-      <c r="G62" s="6" t="n"/>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="6" t="n"/>
     </row>
     <row r="63" hidden="1" outlineLevel="2">
       <c r="A63" s="4" t="n">
@@ -1207,9 +1287,10 @@
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="6" t="n"/>
       <c r="D63" s="6" t="n"/>
-      <c r="E63" s="5" t="n"/>
+      <c r="E63" s="6" t="n"/>
       <c r="F63" s="5" t="n"/>
-      <c r="G63" s="6" t="n"/>
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="6" t="n"/>
     </row>
     <row r="64" hidden="1" outlineLevel="2">
       <c r="A64" s="4" t="n">
@@ -1218,9 +1299,10 @@
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="6" t="n"/>
       <c r="D64" s="6" t="n"/>
-      <c r="E64" s="5" t="n"/>
+      <c r="E64" s="6" t="n"/>
       <c r="F64" s="5" t="n"/>
-      <c r="G64" s="6" t="n"/>
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="6" t="n"/>
     </row>
     <row r="65" hidden="1" outlineLevel="2">
       <c r="A65" s="4" t="n">
@@ -1229,9 +1311,10 @@
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="6" t="n"/>
       <c r="D65" s="6" t="n"/>
-      <c r="E65" s="5" t="n"/>
+      <c r="E65" s="6" t="n"/>
       <c r="F65" s="5" t="n"/>
-      <c r="G65" s="6" t="n"/>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="6" t="n"/>
     </row>
     <row r="66" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A66" s="4" t="n">
@@ -1240,9 +1323,10 @@
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="6" t="n"/>
       <c r="D66" s="6" t="n"/>
-      <c r="E66" s="5" t="n"/>
+      <c r="E66" s="6" t="n"/>
       <c r="F66" s="5" t="n"/>
-      <c r="G66" s="6" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="6" t="n"/>
     </row>
     <row r="67" hidden="1" outlineLevel="2">
       <c r="A67" s="4" t="n">
@@ -1251,9 +1335,10 @@
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="6" t="n"/>
       <c r="D67" s="6" t="n"/>
-      <c r="E67" s="5" t="n"/>
+      <c r="E67" s="6" t="n"/>
       <c r="F67" s="5" t="n"/>
-      <c r="G67" s="6" t="n"/>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="6" t="n"/>
     </row>
     <row r="68" hidden="1" outlineLevel="2">
       <c r="A68" s="4" t="n">
@@ -1262,9 +1347,10 @@
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="6" t="n"/>
       <c r="D68" s="6" t="n"/>
-      <c r="E68" s="5" t="n"/>
+      <c r="E68" s="6" t="n"/>
       <c r="F68" s="5" t="n"/>
-      <c r="G68" s="6" t="n"/>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="6" t="n"/>
     </row>
     <row r="69" hidden="1" outlineLevel="2">
       <c r="A69" s="4" t="n">
@@ -1273,9 +1359,10 @@
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="6" t="n"/>
       <c r="D69" s="6" t="n"/>
-      <c r="E69" s="5" t="n"/>
+      <c r="E69" s="6" t="n"/>
       <c r="F69" s="5" t="n"/>
-      <c r="G69" s="6" t="n"/>
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="6" t="n"/>
     </row>
     <row r="70" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A70" s="4" t="n">
@@ -1284,9 +1371,10 @@
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="6" t="n"/>
       <c r="D70" s="6" t="n"/>
-      <c r="E70" s="5" t="n"/>
+      <c r="E70" s="6" t="n"/>
       <c r="F70" s="5" t="n"/>
-      <c r="G70" s="6" t="n"/>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="6" t="n"/>
     </row>
     <row r="71" hidden="1" outlineLevel="2">
       <c r="A71" s="4" t="n">
@@ -1295,9 +1383,10 @@
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="6" t="n"/>
       <c r="D71" s="6" t="n"/>
-      <c r="E71" s="5" t="n"/>
+      <c r="E71" s="6" t="n"/>
       <c r="F71" s="5" t="n"/>
-      <c r="G71" s="6" t="n"/>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="6" t="n"/>
     </row>
     <row r="72" hidden="1" outlineLevel="2">
       <c r="A72" s="4" t="n">
@@ -1306,9 +1395,10 @@
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="6" t="n"/>
       <c r="D72" s="6" t="n"/>
-      <c r="E72" s="5" t="n"/>
+      <c r="E72" s="6" t="n"/>
       <c r="F72" s="5" t="n"/>
-      <c r="G72" s="6" t="n"/>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="6" t="n"/>
     </row>
     <row r="73" hidden="1" outlineLevel="2">
       <c r="A73" s="4" t="n">
@@ -1317,9 +1407,10 @@
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="6" t="n"/>
       <c r="D73" s="6" t="n"/>
-      <c r="E73" s="5" t="n"/>
+      <c r="E73" s="6" t="n"/>
       <c r="F73" s="5" t="n"/>
-      <c r="G73" s="6" t="n"/>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="6" t="n"/>
     </row>
     <row r="74" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A74" s="4" t="n">
@@ -1328,9 +1419,10 @@
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="6" t="n"/>
       <c r="D74" s="6" t="n"/>
-      <c r="E74" s="5" t="n"/>
+      <c r="E74" s="6" t="n"/>
       <c r="F74" s="5" t="n"/>
-      <c r="G74" s="6" t="n"/>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="6" t="n"/>
     </row>
     <row r="75" hidden="1" outlineLevel="2">
       <c r="A75" s="4" t="n">
@@ -1339,9 +1431,10 @@
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="6" t="n"/>
       <c r="D75" s="6" t="n"/>
-      <c r="E75" s="5" t="n"/>
+      <c r="E75" s="6" t="n"/>
       <c r="F75" s="5" t="n"/>
-      <c r="G75" s="6" t="n"/>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="6" t="n"/>
     </row>
     <row r="76" hidden="1" outlineLevel="2">
       <c r="A76" s="4" t="n">
@@ -1350,9 +1443,10 @@
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="6" t="n"/>
       <c r="D76" s="6" t="n"/>
-      <c r="E76" s="5" t="n"/>
+      <c r="E76" s="6" t="n"/>
       <c r="F76" s="5" t="n"/>
-      <c r="G76" s="6" t="n"/>
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="6" t="n"/>
     </row>
     <row r="77" hidden="1" outlineLevel="2">
       <c r="A77" s="4" t="n">
@@ -1361,9 +1455,10 @@
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="6" t="n"/>
       <c r="D77" s="6" t="n"/>
-      <c r="E77" s="5" t="n"/>
+      <c r="E77" s="6" t="n"/>
       <c r="F77" s="5" t="n"/>
-      <c r="G77" s="6" t="n"/>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="6" t="n"/>
     </row>
     <row r="78" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A78" s="4" t="n">
@@ -1372,9 +1467,10 @@
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="6" t="n"/>
       <c r="D78" s="6" t="n"/>
-      <c r="E78" s="5" t="n"/>
+      <c r="E78" s="6" t="n"/>
       <c r="F78" s="5" t="n"/>
-      <c r="G78" s="6" t="n"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="6" t="n"/>
     </row>
     <row r="79" hidden="1" outlineLevel="2">
       <c r="A79" s="4" t="n">
@@ -1383,9 +1479,10 @@
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="6" t="n"/>
       <c r="D79" s="6" t="n"/>
-      <c r="E79" s="5" t="n"/>
+      <c r="E79" s="6" t="n"/>
       <c r="F79" s="5" t="n"/>
-      <c r="G79" s="6" t="n"/>
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="6" t="n"/>
     </row>
     <row r="80" hidden="1" outlineLevel="2">
       <c r="A80" s="4" t="n">
@@ -1394,9 +1491,10 @@
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="6" t="n"/>
       <c r="D80" s="6" t="n"/>
-      <c r="E80" s="5" t="n"/>
+      <c r="E80" s="6" t="n"/>
       <c r="F80" s="5" t="n"/>
-      <c r="G80" s="6" t="n"/>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="6" t="n"/>
     </row>
     <row r="81" hidden="1" outlineLevel="2">
       <c r="A81" s="4" t="n">
@@ -1405,9 +1503,10 @@
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="6" t="n"/>
       <c r="D81" s="6" t="n"/>
-      <c r="E81" s="5" t="n"/>
+      <c r="E81" s="6" t="n"/>
       <c r="F81" s="5" t="n"/>
-      <c r="G81" s="6" t="n"/>
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="6" t="n"/>
     </row>
     <row r="82" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A82" s="4" t="n">
@@ -1416,9 +1515,10 @@
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="6" t="n"/>
       <c r="D82" s="6" t="n"/>
-      <c r="E82" s="5" t="n"/>
+      <c r="E82" s="6" t="n"/>
       <c r="F82" s="5" t="n"/>
-      <c r="G82" s="6" t="n"/>
+      <c r="G82" s="5" t="n"/>
+      <c r="H82" s="6" t="n"/>
     </row>
     <row r="83" hidden="1" outlineLevel="2">
       <c r="A83" s="4" t="n">
@@ -1427,9 +1527,10 @@
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="6" t="n"/>
       <c r="D83" s="6" t="n"/>
-      <c r="E83" s="5" t="n"/>
+      <c r="E83" s="6" t="n"/>
       <c r="F83" s="5" t="n"/>
-      <c r="G83" s="6" t="n"/>
+      <c r="G83" s="5" t="n"/>
+      <c r="H83" s="6" t="n"/>
     </row>
     <row r="84" hidden="1" outlineLevel="2">
       <c r="A84" s="4" t="n">
@@ -1438,9 +1539,10 @@
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="6" t="n"/>
       <c r="D84" s="6" t="n"/>
-      <c r="E84" s="5" t="n"/>
+      <c r="E84" s="6" t="n"/>
       <c r="F84" s="5" t="n"/>
-      <c r="G84" s="6" t="n"/>
+      <c r="G84" s="5" t="n"/>
+      <c r="H84" s="6" t="n"/>
     </row>
     <row r="85" hidden="1" outlineLevel="2">
       <c r="A85" s="4" t="n">
@@ -1449,9 +1551,10 @@
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="6" t="n"/>
       <c r="D85" s="6" t="n"/>
-      <c r="E85" s="5" t="n"/>
+      <c r="E85" s="6" t="n"/>
       <c r="F85" s="5" t="n"/>
-      <c r="G85" s="6" t="n"/>
+      <c r="G85" s="5" t="n"/>
+      <c r="H85" s="6" t="n"/>
     </row>
     <row r="86" collapsed="1" ht="28.8" customHeight="1">
       <c r="A86" s="4" t="n">
@@ -1469,9 +1572,10 @@
         </is>
       </c>
       <c r="D86" s="6" t="n"/>
-      <c r="E86" s="5" t="n"/>
+      <c r="E86" s="6" t="n"/>
       <c r="F86" s="5" t="n"/>
-      <c r="G86" s="6" t="n"/>
+      <c r="G86" s="5" t="n"/>
+      <c r="H86" s="6" t="n"/>
     </row>
     <row r="87" hidden="1" outlineLevel="2">
       <c r="A87" s="4" t="n">
@@ -1480,9 +1584,10 @@
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="6" t="n"/>
       <c r="D87" s="6" t="n"/>
-      <c r="E87" s="5" t="n"/>
+      <c r="E87" s="6" t="n"/>
       <c r="F87" s="5" t="n"/>
-      <c r="G87" s="6" t="n"/>
+      <c r="G87" s="5" t="n"/>
+      <c r="H87" s="6" t="n"/>
     </row>
     <row r="88" hidden="1" outlineLevel="2">
       <c r="A88" s="4" t="n">
@@ -1491,9 +1596,10 @@
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="6" t="n"/>
       <c r="D88" s="6" t="n"/>
-      <c r="E88" s="5" t="n"/>
+      <c r="E88" s="6" t="n"/>
       <c r="F88" s="5" t="n"/>
-      <c r="G88" s="6" t="n"/>
+      <c r="G88" s="5" t="n"/>
+      <c r="H88" s="6" t="n"/>
     </row>
     <row r="89" hidden="1" outlineLevel="2">
       <c r="A89" s="4" t="n">
@@ -1502,9 +1608,10 @@
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="6" t="n"/>
       <c r="D89" s="6" t="n"/>
-      <c r="E89" s="5" t="n"/>
+      <c r="E89" s="6" t="n"/>
       <c r="F89" s="5" t="n"/>
-      <c r="G89" s="6" t="n"/>
+      <c r="G89" s="5" t="n"/>
+      <c r="H89" s="6" t="n"/>
     </row>
     <row r="90" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A90" s="4" t="n">
@@ -1513,9 +1620,10 @@
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="6" t="n"/>
       <c r="D90" s="6" t="n"/>
-      <c r="E90" s="5" t="n"/>
+      <c r="E90" s="6" t="n"/>
       <c r="F90" s="5" t="n"/>
-      <c r="G90" s="6" t="n"/>
+      <c r="G90" s="5" t="n"/>
+      <c r="H90" s="6" t="n"/>
     </row>
     <row r="91" hidden="1" outlineLevel="2">
       <c r="A91" s="4" t="n">
@@ -1524,9 +1632,10 @@
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="6" t="n"/>
       <c r="D91" s="6" t="n"/>
-      <c r="E91" s="5" t="n"/>
+      <c r="E91" s="6" t="n"/>
       <c r="F91" s="5" t="n"/>
-      <c r="G91" s="6" t="n"/>
+      <c r="G91" s="5" t="n"/>
+      <c r="H91" s="6" t="n"/>
     </row>
     <row r="92" hidden="1" outlineLevel="2">
       <c r="A92" s="4" t="n">
@@ -1535,9 +1644,10 @@
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="6" t="n"/>
       <c r="D92" s="6" t="n"/>
-      <c r="E92" s="5" t="n"/>
+      <c r="E92" s="6" t="n"/>
       <c r="F92" s="5" t="n"/>
-      <c r="G92" s="6" t="n"/>
+      <c r="G92" s="5" t="n"/>
+      <c r="H92" s="6" t="n"/>
     </row>
     <row r="93" hidden="1" outlineLevel="2">
       <c r="A93" s="4" t="n">
@@ -1546,9 +1656,10 @@
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="6" t="n"/>
       <c r="D93" s="6" t="n"/>
-      <c r="E93" s="5" t="n"/>
+      <c r="E93" s="6" t="n"/>
       <c r="F93" s="5" t="n"/>
-      <c r="G93" s="6" t="n"/>
+      <c r="G93" s="5" t="n"/>
+      <c r="H93" s="6" t="n"/>
     </row>
     <row r="94" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A94" s="4" t="n">
@@ -1557,9 +1668,10 @@
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="6" t="n"/>
       <c r="D94" s="6" t="n"/>
-      <c r="E94" s="5" t="n"/>
+      <c r="E94" s="6" t="n"/>
       <c r="F94" s="5" t="n"/>
-      <c r="G94" s="6" t="n"/>
+      <c r="G94" s="5" t="n"/>
+      <c r="H94" s="6" t="n"/>
     </row>
     <row r="95" hidden="1" outlineLevel="2">
       <c r="A95" s="4" t="n">
@@ -1568,9 +1680,10 @@
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="6" t="n"/>
       <c r="D95" s="6" t="n"/>
-      <c r="E95" s="5" t="n"/>
+      <c r="E95" s="6" t="n"/>
       <c r="F95" s="5" t="n"/>
-      <c r="G95" s="6" t="n"/>
+      <c r="G95" s="5" t="n"/>
+      <c r="H95" s="6" t="n"/>
     </row>
     <row r="96" hidden="1" outlineLevel="2">
       <c r="A96" s="4" t="n">
@@ -1579,9 +1692,10 @@
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="6" t="n"/>
       <c r="D96" s="6" t="n"/>
-      <c r="E96" s="5" t="n"/>
+      <c r="E96" s="6" t="n"/>
       <c r="F96" s="5" t="n"/>
-      <c r="G96" s="6" t="n"/>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="6" t="n"/>
     </row>
     <row r="97" hidden="1" outlineLevel="2">
       <c r="A97" s="4" t="n">
@@ -1590,9 +1704,10 @@
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="6" t="n"/>
       <c r="D97" s="6" t="n"/>
-      <c r="E97" s="5" t="n"/>
+      <c r="E97" s="6" t="n"/>
       <c r="F97" s="5" t="n"/>
-      <c r="G97" s="6" t="n"/>
+      <c r="G97" s="5" t="n"/>
+      <c r="H97" s="6" t="n"/>
     </row>
     <row r="98" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A98" s="4" t="n">
@@ -1601,9 +1716,10 @@
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="6" t="n"/>
       <c r="D98" s="6" t="n"/>
-      <c r="E98" s="5" t="n"/>
+      <c r="E98" s="6" t="n"/>
       <c r="F98" s="5" t="n"/>
-      <c r="G98" s="6" t="n"/>
+      <c r="G98" s="5" t="n"/>
+      <c r="H98" s="6" t="n"/>
     </row>
     <row r="99" hidden="1" outlineLevel="2">
       <c r="A99" s="4" t="n">
@@ -1612,9 +1728,10 @@
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="6" t="n"/>
       <c r="D99" s="6" t="n"/>
-      <c r="E99" s="5" t="n"/>
+      <c r="E99" s="6" t="n"/>
       <c r="F99" s="5" t="n"/>
-      <c r="G99" s="6" t="n"/>
+      <c r="G99" s="5" t="n"/>
+      <c r="H99" s="6" t="n"/>
     </row>
     <row r="100" hidden="1" outlineLevel="2">
       <c r="A100" s="4" t="n">
@@ -1623,9 +1740,10 @@
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="6" t="n"/>
       <c r="D100" s="6" t="n"/>
-      <c r="E100" s="5" t="n"/>
+      <c r="E100" s="6" t="n"/>
       <c r="F100" s="5" t="n"/>
-      <c r="G100" s="6" t="n"/>
+      <c r="G100" s="5" t="n"/>
+      <c r="H100" s="6" t="n"/>
     </row>
     <row r="101" hidden="1" outlineLevel="2">
       <c r="A101" s="4" t="n">
@@ -1634,9 +1752,10 @@
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="6" t="n"/>
       <c r="D101" s="6" t="n"/>
-      <c r="E101" s="5" t="n"/>
+      <c r="E101" s="6" t="n"/>
       <c r="F101" s="5" t="n"/>
-      <c r="G101" s="6" t="n"/>
+      <c r="G101" s="5" t="n"/>
+      <c r="H101" s="6" t="n"/>
     </row>
     <row r="102" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A102" s="4" t="n">
@@ -1645,9 +1764,10 @@
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="6" t="n"/>
       <c r="D102" s="6" t="n"/>
-      <c r="E102" s="5" t="n"/>
+      <c r="E102" s="6" t="n"/>
       <c r="F102" s="5" t="n"/>
-      <c r="G102" s="6" t="n"/>
+      <c r="G102" s="5" t="n"/>
+      <c r="H102" s="6" t="n"/>
     </row>
     <row r="103" hidden="1" outlineLevel="2">
       <c r="A103" s="4" t="n">
@@ -1656,9 +1776,10 @@
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="6" t="n"/>
       <c r="D103" s="6" t="n"/>
-      <c r="E103" s="5" t="n"/>
+      <c r="E103" s="6" t="n"/>
       <c r="F103" s="5" t="n"/>
-      <c r="G103" s="6" t="n"/>
+      <c r="G103" s="5" t="n"/>
+      <c r="H103" s="6" t="n"/>
     </row>
     <row r="104" hidden="1" outlineLevel="2">
       <c r="A104" s="4" t="n">
@@ -1667,9 +1788,10 @@
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="6" t="n"/>
       <c r="D104" s="6" t="n"/>
-      <c r="E104" s="5" t="n"/>
+      <c r="E104" s="6" t="n"/>
       <c r="F104" s="5" t="n"/>
-      <c r="G104" s="6" t="n"/>
+      <c r="G104" s="5" t="n"/>
+      <c r="H104" s="6" t="n"/>
     </row>
     <row r="105" hidden="1" outlineLevel="2">
       <c r="A105" s="4" t="n">
@@ -1678,9 +1800,10 @@
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="6" t="n"/>
       <c r="D105" s="6" t="n"/>
-      <c r="E105" s="5" t="n"/>
+      <c r="E105" s="6" t="n"/>
       <c r="F105" s="5" t="n"/>
-      <c r="G105" s="6" t="n"/>
+      <c r="G105" s="5" t="n"/>
+      <c r="H105" s="6" t="n"/>
     </row>
     <row r="106" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A106" s="4" t="n">
@@ -1689,9 +1812,10 @@
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="6" t="n"/>
       <c r="D106" s="6" t="n"/>
-      <c r="E106" s="5" t="n"/>
+      <c r="E106" s="6" t="n"/>
       <c r="F106" s="5" t="n"/>
-      <c r="G106" s="6" t="n"/>
+      <c r="G106" s="5" t="n"/>
+      <c r="H106" s="6" t="n"/>
     </row>
     <row r="107" hidden="1" outlineLevel="2">
       <c r="A107" s="4" t="n">
@@ -1700,9 +1824,10 @@
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="6" t="n"/>
       <c r="D107" s="6" t="n"/>
-      <c r="E107" s="5" t="n"/>
+      <c r="E107" s="6" t="n"/>
       <c r="F107" s="5" t="n"/>
-      <c r="G107" s="6" t="n"/>
+      <c r="G107" s="5" t="n"/>
+      <c r="H107" s="6" t="n"/>
     </row>
     <row r="108" hidden="1" outlineLevel="2">
       <c r="A108" s="4" t="n">
@@ -1711,9 +1836,10 @@
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="6" t="n"/>
       <c r="D108" s="6" t="n"/>
-      <c r="E108" s="5" t="n"/>
+      <c r="E108" s="6" t="n"/>
       <c r="F108" s="5" t="n"/>
-      <c r="G108" s="6" t="n"/>
+      <c r="G108" s="5" t="n"/>
+      <c r="H108" s="6" t="n"/>
     </row>
     <row r="109" hidden="1" outlineLevel="2">
       <c r="A109" s="4" t="n">
@@ -1722,9 +1848,10 @@
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="6" t="n"/>
       <c r="D109" s="6" t="n"/>
-      <c r="E109" s="5" t="n"/>
+      <c r="E109" s="6" t="n"/>
       <c r="F109" s="5" t="n"/>
-      <c r="G109" s="6" t="n"/>
+      <c r="G109" s="5" t="n"/>
+      <c r="H109" s="6" t="n"/>
     </row>
     <row r="110" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A110" s="4" t="n">
@@ -1733,9 +1860,10 @@
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="6" t="n"/>
       <c r="D110" s="6" t="n"/>
-      <c r="E110" s="5" t="n"/>
+      <c r="E110" s="6" t="n"/>
       <c r="F110" s="5" t="n"/>
-      <c r="G110" s="6" t="n"/>
+      <c r="G110" s="5" t="n"/>
+      <c r="H110" s="6" t="n"/>
     </row>
     <row r="111" hidden="1" outlineLevel="2">
       <c r="A111" s="4" t="n">
@@ -1744,9 +1872,10 @@
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="6" t="n"/>
       <c r="D111" s="6" t="n"/>
-      <c r="E111" s="5" t="n"/>
+      <c r="E111" s="6" t="n"/>
       <c r="F111" s="5" t="n"/>
-      <c r="G111" s="6" t="n"/>
+      <c r="G111" s="5" t="n"/>
+      <c r="H111" s="6" t="n"/>
     </row>
     <row r="112" hidden="1" outlineLevel="2">
       <c r="A112" s="4" t="n">
@@ -1755,9 +1884,10 @@
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="6" t="n"/>
       <c r="D112" s="6" t="n"/>
-      <c r="E112" s="5" t="n"/>
+      <c r="E112" s="6" t="n"/>
       <c r="F112" s="5" t="n"/>
-      <c r="G112" s="6" t="n"/>
+      <c r="G112" s="5" t="n"/>
+      <c r="H112" s="6" t="n"/>
     </row>
     <row r="113" hidden="1" outlineLevel="2">
       <c r="A113" s="4" t="n">
@@ -1766,9 +1896,10 @@
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="6" t="n"/>
       <c r="D113" s="6" t="n"/>
-      <c r="E113" s="5" t="n"/>
+      <c r="E113" s="6" t="n"/>
       <c r="F113" s="5" t="n"/>
-      <c r="G113" s="6" t="n"/>
+      <c r="G113" s="5" t="n"/>
+      <c r="H113" s="6" t="n"/>
     </row>
     <row r="114" collapsed="1" ht="28.8" customHeight="1">
       <c r="A114" s="4" t="n">
@@ -1786,9 +1917,10 @@
         </is>
       </c>
       <c r="D114" s="6" t="n"/>
-      <c r="E114" s="5" t="n"/>
+      <c r="E114" s="6" t="n"/>
       <c r="F114" s="5" t="n"/>
-      <c r="G114" s="6" t="n"/>
+      <c r="G114" s="5" t="n"/>
+      <c r="H114" s="6" t="n"/>
     </row>
     <row r="115" hidden="1" outlineLevel="2">
       <c r="A115" s="4" t="n">
@@ -1797,9 +1929,10 @@
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="6" t="n"/>
       <c r="D115" s="6" t="n"/>
-      <c r="E115" s="5" t="n"/>
+      <c r="E115" s="6" t="n"/>
       <c r="F115" s="5" t="n"/>
-      <c r="G115" s="6" t="n"/>
+      <c r="G115" s="5" t="n"/>
+      <c r="H115" s="6" t="n"/>
     </row>
     <row r="116" collapsed="1" ht="28.8" customHeight="1">
       <c r="A116" s="4" t="n">
@@ -1817,9 +1950,10 @@
         </is>
       </c>
       <c r="D116" s="6" t="n"/>
-      <c r="E116" s="5" t="n"/>
+      <c r="E116" s="6" t="n"/>
       <c r="F116" s="5" t="n"/>
-      <c r="G116" s="6" t="n"/>
+      <c r="G116" s="5" t="n"/>
+      <c r="H116" s="6" t="n"/>
     </row>
     <row r="117" hidden="1" outlineLevel="2">
       <c r="A117" s="4" t="n">
@@ -1828,9 +1962,10 @@
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="6" t="n"/>
       <c r="D117" s="6" t="n"/>
-      <c r="E117" s="5" t="n"/>
+      <c r="E117" s="6" t="n"/>
       <c r="F117" s="5" t="n"/>
-      <c r="G117" s="6" t="n"/>
+      <c r="G117" s="5" t="n"/>
+      <c r="H117" s="6" t="n"/>
     </row>
     <row r="118" ht="28.8" customHeight="1">
       <c r="A118" s="4" t="n">
@@ -1849,9 +1984,10 @@
         </is>
       </c>
       <c r="D118" s="6" t="n"/>
-      <c r="E118" s="5" t="n"/>
+      <c r="E118" s="6" t="n"/>
       <c r="F118" s="5" t="n"/>
-      <c r="G118" s="6" t="n"/>
+      <c r="G118" s="5" t="n"/>
+      <c r="H118" s="6" t="n"/>
     </row>
     <row r="119" outlineLevel="2">
       <c r="A119" s="4" t="n">
@@ -1860,9 +1996,10 @@
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="6" t="n"/>
       <c r="D119" s="6" t="n"/>
-      <c r="E119" s="5" t="n"/>
+      <c r="E119" s="6" t="n"/>
       <c r="F119" s="5" t="n"/>
-      <c r="G119" s="6" t="n"/>
+      <c r="G119" s="5" t="n"/>
+      <c r="H119" s="6" t="n"/>
     </row>
     <row r="120" outlineLevel="2">
       <c r="A120" s="4" t="n">
@@ -1871,9 +2008,10 @@
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="6" t="n"/>
       <c r="D120" s="6" t="n"/>
-      <c r="E120" s="5" t="n"/>
+      <c r="E120" s="6" t="n"/>
       <c r="F120" s="5" t="n"/>
-      <c r="G120" s="6" t="n"/>
+      <c r="G120" s="5" t="n"/>
+      <c r="H120" s="6" t="n"/>
     </row>
     <row r="121" outlineLevel="2">
       <c r="A121" s="4" t="n">
@@ -1882,9 +2020,10 @@
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="6" t="n"/>
       <c r="D121" s="6" t="n"/>
-      <c r="E121" s="5" t="n"/>
+      <c r="E121" s="6" t="n"/>
       <c r="F121" s="5" t="n"/>
-      <c r="G121" s="6" t="n"/>
+      <c r="G121" s="5" t="n"/>
+      <c r="H121" s="6" t="n"/>
     </row>
     <row r="122" outlineLevel="1" collapsed="1">
       <c r="A122" s="4" t="n">
@@ -1893,9 +2032,10 @@
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="6" t="n"/>
       <c r="D122" s="6" t="n"/>
-      <c r="E122" s="5" t="n"/>
+      <c r="E122" s="6" t="n"/>
       <c r="F122" s="5" t="n"/>
-      <c r="G122" s="6" t="n"/>
+      <c r="G122" s="5" t="n"/>
+      <c r="H122" s="6" t="n"/>
     </row>
     <row r="123" hidden="1" outlineLevel="2">
       <c r="A123" s="4" t="n">
@@ -1904,9 +2044,10 @@
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="6" t="n"/>
       <c r="D123" s="6" t="n"/>
-      <c r="E123" s="5" t="n"/>
+      <c r="E123" s="6" t="n"/>
       <c r="F123" s="5" t="n"/>
-      <c r="G123" s="6" t="n"/>
+      <c r="G123" s="5" t="n"/>
+      <c r="H123" s="6" t="n"/>
     </row>
     <row r="124" hidden="1" outlineLevel="2">
       <c r="A124" s="4" t="n">
@@ -1915,9 +2056,10 @@
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="6" t="n"/>
       <c r="D124" s="6" t="n"/>
-      <c r="E124" s="5" t="n"/>
+      <c r="E124" s="6" t="n"/>
       <c r="F124" s="5" t="n"/>
-      <c r="G124" s="6" t="n"/>
+      <c r="G124" s="5" t="n"/>
+      <c r="H124" s="6" t="n"/>
     </row>
     <row r="125" hidden="1" outlineLevel="2">
       <c r="A125" s="4" t="n">
@@ -1926,9 +2068,10 @@
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6" t="n"/>
       <c r="D125" s="6" t="n"/>
-      <c r="E125" s="5" t="n"/>
+      <c r="E125" s="6" t="n"/>
       <c r="F125" s="5" t="n"/>
-      <c r="G125" s="6" t="n"/>
+      <c r="G125" s="5" t="n"/>
+      <c r="H125" s="6" t="n"/>
     </row>
     <row r="126" outlineLevel="1" collapsed="1">
       <c r="A126" s="4" t="n">
@@ -1937,9 +2080,10 @@
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="6" t="n"/>
       <c r="D126" s="6" t="n"/>
-      <c r="E126" s="5" t="n"/>
+      <c r="E126" s="6" t="n"/>
       <c r="F126" s="5" t="n"/>
-      <c r="G126" s="6" t="n"/>
+      <c r="G126" s="5" t="n"/>
+      <c r="H126" s="6" t="n"/>
     </row>
     <row r="127" hidden="1" outlineLevel="2">
       <c r="A127" s="4" t="n">
@@ -1948,9 +2092,10 @@
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="6" t="n"/>
       <c r="D127" s="6" t="n"/>
-      <c r="E127" s="5" t="n"/>
+      <c r="E127" s="6" t="n"/>
       <c r="F127" s="5" t="n"/>
-      <c r="G127" s="6" t="n"/>
+      <c r="G127" s="5" t="n"/>
+      <c r="H127" s="6" t="n"/>
     </row>
     <row r="128" hidden="1" outlineLevel="2" ht="28.8" customHeight="1">
       <c r="A128" s="4" t="n">
@@ -1959,9 +2104,10 @@
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="6" t="n"/>
       <c r="D128" s="6" t="n"/>
-      <c r="E128" s="5" t="n"/>
+      <c r="E128" s="6" t="n"/>
       <c r="F128" s="5" t="n"/>
-      <c r="G128" s="6" t="n"/>
+      <c r="G128" s="5" t="n"/>
+      <c r="H128" s="6" t="n"/>
     </row>
     <row r="129" hidden="1" outlineLevel="2" ht="28.8" customHeight="1">
       <c r="A129" s="4" t="n">
@@ -1970,9 +2116,10 @@
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="6" t="n"/>
       <c r="D129" s="6" t="n"/>
-      <c r="E129" s="5" t="n"/>
+      <c r="E129" s="6" t="n"/>
       <c r="F129" s="5" t="n"/>
-      <c r="G129" s="6" t="n"/>
+      <c r="G129" s="5" t="n"/>
+      <c r="H129" s="6" t="n"/>
     </row>
     <row r="130" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A130" s="4" t="n">
@@ -1981,9 +2128,10 @@
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="6" t="n"/>
       <c r="D130" s="6" t="n"/>
-      <c r="E130" s="5" t="n"/>
+      <c r="E130" s="6" t="n"/>
       <c r="F130" s="5" t="n"/>
-      <c r="G130" s="6" t="n"/>
+      <c r="G130" s="5" t="n"/>
+      <c r="H130" s="6" t="n"/>
     </row>
     <row r="131" outlineLevel="2">
       <c r="A131" s="4" t="n">
@@ -1992,9 +2140,10 @@
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="6" t="n"/>
       <c r="D131" s="6" t="n"/>
-      <c r="E131" s="5" t="n"/>
+      <c r="E131" s="6" t="n"/>
       <c r="F131" s="5" t="n"/>
-      <c r="G131" s="6" t="n"/>
+      <c r="G131" s="5" t="n"/>
+      <c r="H131" s="6" t="n"/>
     </row>
     <row r="132" outlineLevel="2" ht="43.2" customHeight="1">
       <c r="A132" s="4" t="n">
@@ -2007,9 +2156,10 @@
         </is>
       </c>
       <c r="D132" s="6" t="n"/>
-      <c r="E132" s="5" t="n"/>
+      <c r="E132" s="6" t="n"/>
       <c r="F132" s="5" t="n"/>
-      <c r="G132" s="6" t="n"/>
+      <c r="G132" s="5" t="n"/>
+      <c r="H132" s="6" t="n"/>
     </row>
     <row r="133" outlineLevel="2">
       <c r="A133" s="4" t="n">
@@ -2022,9 +2172,10 @@
         </is>
       </c>
       <c r="D133" s="6" t="n"/>
-      <c r="E133" s="5" t="n"/>
+      <c r="E133" s="6" t="n"/>
       <c r="F133" s="5" t="n"/>
-      <c r="G133" s="6" t="n"/>
+      <c r="G133" s="5" t="n"/>
+      <c r="H133" s="6" t="n"/>
     </row>
     <row r="134" outlineLevel="1" collapsed="1">
       <c r="A134" s="4" t="n">
@@ -2037,9 +2188,10 @@
         </is>
       </c>
       <c r="D134" s="6" t="n"/>
-      <c r="E134" s="5" t="n"/>
+      <c r="E134" s="6" t="n"/>
       <c r="F134" s="5" t="n"/>
-      <c r="G134" s="6" t="n"/>
+      <c r="G134" s="5" t="n"/>
+      <c r="H134" s="6" t="n"/>
     </row>
     <row r="135" hidden="1" outlineLevel="2">
       <c r="A135" s="4" t="n">
@@ -2048,9 +2200,10 @@
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="6" t="n"/>
       <c r="D135" s="6" t="n"/>
-      <c r="E135" s="5" t="n"/>
+      <c r="E135" s="6" t="n"/>
       <c r="F135" s="5" t="n"/>
-      <c r="G135" s="6" t="n"/>
+      <c r="G135" s="5" t="n"/>
+      <c r="H135" s="6" t="n"/>
     </row>
     <row r="136" hidden="1" outlineLevel="2" ht="43.2" customHeight="1">
       <c r="A136" s="4" t="n">
@@ -2059,9 +2212,10 @@
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="6" t="n"/>
       <c r="D136" s="6" t="n"/>
-      <c r="E136" s="5" t="n"/>
+      <c r="E136" s="6" t="n"/>
       <c r="F136" s="5" t="n"/>
-      <c r="G136" s="6" t="n"/>
+      <c r="G136" s="5" t="n"/>
+      <c r="H136" s="6" t="n"/>
     </row>
     <row r="137" hidden="1" outlineLevel="2" ht="43.2" customHeight="1">
       <c r="A137" s="4" t="n">
@@ -2070,9 +2224,10 @@
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="6" t="n"/>
       <c r="D137" s="6" t="n"/>
-      <c r="E137" s="5" t="n"/>
+      <c r="E137" s="6" t="n"/>
       <c r="F137" s="5" t="n"/>
-      <c r="G137" s="6" t="n"/>
+      <c r="G137" s="5" t="n"/>
+      <c r="H137" s="6" t="n"/>
     </row>
     <row r="138" outlineLevel="1" collapsed="1" ht="43.2" customHeight="1">
       <c r="A138" s="4" t="n">
@@ -2081,9 +2236,10 @@
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="6" t="n"/>
       <c r="D138" s="6" t="n"/>
-      <c r="E138" s="5" t="n"/>
+      <c r="E138" s="6" t="n"/>
       <c r="F138" s="5" t="n"/>
-      <c r="G138" s="6" t="n"/>
+      <c r="G138" s="5" t="n"/>
+      <c r="H138" s="6" t="n"/>
     </row>
     <row r="139" hidden="1" outlineLevel="2">
       <c r="A139" s="4" t="n">
@@ -2092,9 +2248,10 @@
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="6" t="n"/>
       <c r="D139" s="6" t="n"/>
-      <c r="E139" s="5" t="n"/>
+      <c r="E139" s="6" t="n"/>
       <c r="F139" s="5" t="n"/>
-      <c r="G139" s="6" t="n"/>
+      <c r="G139" s="5" t="n"/>
+      <c r="H139" s="6" t="n"/>
     </row>
     <row r="140" hidden="1" outlineLevel="2">
       <c r="A140" s="4" t="n">
@@ -2103,9 +2260,10 @@
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="6" t="n"/>
       <c r="D140" s="6" t="n"/>
-      <c r="E140" s="5" t="n"/>
+      <c r="E140" s="6" t="n"/>
       <c r="F140" s="5" t="n"/>
-      <c r="G140" s="6" t="n"/>
+      <c r="G140" s="5" t="n"/>
+      <c r="H140" s="6" t="n"/>
     </row>
     <row r="141" hidden="1" outlineLevel="2">
       <c r="A141" s="4" t="n">
@@ -2114,9 +2272,10 @@
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="6" t="n"/>
       <c r="D141" s="6" t="n"/>
-      <c r="E141" s="5" t="n"/>
+      <c r="E141" s="6" t="n"/>
       <c r="F141" s="5" t="n"/>
-      <c r="G141" s="6" t="n"/>
+      <c r="G141" s="5" t="n"/>
+      <c r="H141" s="6" t="n"/>
     </row>
     <row r="142" outlineLevel="1" collapsed="1">
       <c r="A142" s="4" t="n">
@@ -2125,9 +2284,10 @@
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6" t="n"/>
       <c r="D142" s="6" t="n"/>
-      <c r="E142" s="5" t="n"/>
+      <c r="E142" s="6" t="n"/>
       <c r="F142" s="5" t="n"/>
-      <c r="G142" s="6" t="n"/>
+      <c r="G142" s="5" t="n"/>
+      <c r="H142" s="6" t="n"/>
     </row>
     <row r="143" hidden="1" outlineLevel="2">
       <c r="A143" s="4" t="n">
@@ -2136,9 +2296,10 @@
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="6" t="n"/>
       <c r="D143" s="6" t="n"/>
-      <c r="E143" s="5" t="n"/>
+      <c r="E143" s="6" t="n"/>
       <c r="F143" s="5" t="n"/>
-      <c r="G143" s="6" t="n"/>
+      <c r="G143" s="5" t="n"/>
+      <c r="H143" s="6" t="n"/>
     </row>
     <row r="144" hidden="1" outlineLevel="2">
       <c r="A144" s="4" t="n">
@@ -2147,9 +2308,10 @@
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="6" t="n"/>
       <c r="D144" s="6" t="n"/>
-      <c r="E144" s="5" t="n"/>
+      <c r="E144" s="6" t="n"/>
       <c r="F144" s="5" t="n"/>
-      <c r="G144" s="6" t="n"/>
+      <c r="G144" s="5" t="n"/>
+      <c r="H144" s="6" t="n"/>
     </row>
     <row r="145" hidden="1" outlineLevel="2">
       <c r="A145" s="4" t="n">
@@ -2158,9 +2320,10 @@
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="6" t="n"/>
       <c r="D145" s="6" t="n"/>
-      <c r="E145" s="5" t="n"/>
+      <c r="E145" s="6" t="n"/>
       <c r="F145" s="5" t="n"/>
-      <c r="G145" s="6" t="n"/>
+      <c r="G145" s="5" t="n"/>
+      <c r="H145" s="6" t="n"/>
     </row>
     <row r="146" outlineLevel="1" collapsed="1">
       <c r="A146" s="4" t="n">
@@ -2169,9 +2332,10 @@
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="6" t="n"/>
       <c r="D146" s="6" t="n"/>
-      <c r="E146" s="5" t="n"/>
+      <c r="E146" s="6" t="n"/>
       <c r="F146" s="5" t="n"/>
-      <c r="G146" s="6" t="n"/>
+      <c r="G146" s="5" t="n"/>
+      <c r="H146" s="6" t="n"/>
     </row>
     <row r="147" hidden="1" outlineLevel="2">
       <c r="A147" s="4" t="n">
@@ -2180,9 +2344,10 @@
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="6" t="n"/>
       <c r="D147" s="6" t="n"/>
-      <c r="E147" s="5" t="n"/>
+      <c r="E147" s="6" t="n"/>
       <c r="F147" s="5" t="n"/>
-      <c r="G147" s="6" t="n"/>
+      <c r="G147" s="5" t="n"/>
+      <c r="H147" s="6" t="n"/>
     </row>
     <row r="148" hidden="1" outlineLevel="2">
       <c r="A148" s="4" t="n">
@@ -2191,9 +2356,10 @@
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="6" t="n"/>
       <c r="D148" s="6" t="n"/>
-      <c r="E148" s="5" t="n"/>
+      <c r="E148" s="6" t="n"/>
       <c r="F148" s="5" t="n"/>
-      <c r="G148" s="6" t="n"/>
+      <c r="G148" s="5" t="n"/>
+      <c r="H148" s="6" t="n"/>
     </row>
     <row r="149" hidden="1" outlineLevel="2">
       <c r="A149" s="4" t="n">
@@ -2202,9 +2368,10 @@
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="6" t="n"/>
       <c r="D149" s="6" t="n"/>
-      <c r="E149" s="5" t="n"/>
+      <c r="E149" s="6" t="n"/>
       <c r="F149" s="5" t="n"/>
-      <c r="G149" s="6" t="n"/>
+      <c r="G149" s="5" t="n"/>
+      <c r="H149" s="6" t="n"/>
     </row>
     <row r="150" collapsed="1" ht="28.8" customHeight="1">
       <c r="A150" s="4" t="n">
@@ -2222,9 +2389,10 @@
         </is>
       </c>
       <c r="D150" s="6" t="n"/>
-      <c r="E150" s="5" t="n"/>
+      <c r="E150" s="6" t="n"/>
       <c r="F150" s="5" t="n"/>
-      <c r="G150" s="6" t="n"/>
+      <c r="G150" s="5" t="n"/>
+      <c r="H150" s="6" t="n"/>
     </row>
     <row r="151" hidden="1" outlineLevel="2">
       <c r="A151" s="4" t="n">
@@ -2233,9 +2401,10 @@
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="6" t="n"/>
       <c r="D151" s="6" t="n"/>
-      <c r="E151" s="5" t="n"/>
+      <c r="E151" s="6" t="n"/>
       <c r="F151" s="5" t="n"/>
-      <c r="G151" s="6" t="n"/>
+      <c r="G151" s="5" t="n"/>
+      <c r="H151" s="6" t="n"/>
     </row>
     <row r="152" hidden="1" outlineLevel="2">
       <c r="A152" s="4" t="n">
@@ -2244,9 +2413,10 @@
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="6" t="n"/>
       <c r="D152" s="6" t="n"/>
-      <c r="E152" s="5" t="n"/>
+      <c r="E152" s="6" t="n"/>
       <c r="F152" s="5" t="n"/>
-      <c r="G152" s="6" t="n"/>
+      <c r="G152" s="5" t="n"/>
+      <c r="H152" s="6" t="n"/>
     </row>
     <row r="153" hidden="1" outlineLevel="2">
       <c r="A153" s="4" t="n">
@@ -2255,9 +2425,10 @@
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="6" t="n"/>
       <c r="D153" s="6" t="n"/>
-      <c r="E153" s="5" t="n"/>
+      <c r="E153" s="6" t="n"/>
       <c r="F153" s="5" t="n"/>
-      <c r="G153" s="6" t="n"/>
+      <c r="G153" s="5" t="n"/>
+      <c r="H153" s="6" t="n"/>
     </row>
     <row r="154" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A154" s="4" t="n">
@@ -2266,9 +2437,10 @@
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="6" t="n"/>
       <c r="D154" s="6" t="n"/>
-      <c r="E154" s="5" t="n"/>
+      <c r="E154" s="6" t="n"/>
       <c r="F154" s="5" t="n"/>
-      <c r="G154" s="6" t="n"/>
+      <c r="G154" s="5" t="n"/>
+      <c r="H154" s="6" t="n"/>
     </row>
     <row r="155" hidden="1" outlineLevel="2">
       <c r="A155" s="4" t="n">
@@ -2277,9 +2449,10 @@
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="6" t="n"/>
       <c r="D155" s="6" t="n"/>
-      <c r="E155" s="5" t="n"/>
+      <c r="E155" s="6" t="n"/>
       <c r="F155" s="5" t="n"/>
-      <c r="G155" s="6" t="n"/>
+      <c r="G155" s="5" t="n"/>
+      <c r="H155" s="6" t="n"/>
     </row>
     <row r="156" hidden="1" outlineLevel="2">
       <c r="A156" s="4" t="n">
@@ -2288,9 +2461,10 @@
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="6" t="n"/>
       <c r="D156" s="6" t="n"/>
-      <c r="E156" s="5" t="n"/>
+      <c r="E156" s="6" t="n"/>
       <c r="F156" s="5" t="n"/>
-      <c r="G156" s="6" t="n"/>
+      <c r="G156" s="5" t="n"/>
+      <c r="H156" s="6" t="n"/>
     </row>
     <row r="157" hidden="1" outlineLevel="2">
       <c r="A157" s="4" t="n">
@@ -2299,9 +2473,10 @@
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="6" t="n"/>
       <c r="D157" s="6" t="n"/>
-      <c r="E157" s="5" t="n"/>
+      <c r="E157" s="6" t="n"/>
       <c r="F157" s="5" t="n"/>
-      <c r="G157" s="6" t="n"/>
+      <c r="G157" s="5" t="n"/>
+      <c r="H157" s="6" t="n"/>
     </row>
     <row r="158" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A158" s="4" t="n">
@@ -2310,9 +2485,10 @@
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="6" t="n"/>
       <c r="D158" s="6" t="n"/>
-      <c r="E158" s="5" t="n"/>
+      <c r="E158" s="6" t="n"/>
       <c r="F158" s="5" t="n"/>
-      <c r="G158" s="6" t="n"/>
+      <c r="G158" s="5" t="n"/>
+      <c r="H158" s="6" t="n"/>
     </row>
     <row r="159" hidden="1" outlineLevel="2">
       <c r="A159" s="4" t="n">
@@ -2321,9 +2497,10 @@
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="6" t="n"/>
       <c r="D159" s="6" t="n"/>
-      <c r="E159" s="5" t="n"/>
+      <c r="E159" s="6" t="n"/>
       <c r="F159" s="5" t="n"/>
-      <c r="G159" s="6" t="n"/>
+      <c r="G159" s="5" t="n"/>
+      <c r="H159" s="6" t="n"/>
     </row>
     <row r="160" hidden="1" outlineLevel="2">
       <c r="A160" s="4" t="n">
@@ -2332,9 +2509,10 @@
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="6" t="n"/>
       <c r="D160" s="6" t="n"/>
-      <c r="E160" s="5" t="n"/>
+      <c r="E160" s="6" t="n"/>
       <c r="F160" s="5" t="n"/>
-      <c r="G160" s="6" t="n"/>
+      <c r="G160" s="5" t="n"/>
+      <c r="H160" s="6" t="n"/>
     </row>
     <row r="161" hidden="1" outlineLevel="2">
       <c r="A161" s="4" t="n">
@@ -2343,9 +2521,10 @@
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="6" t="n"/>
       <c r="D161" s="6" t="n"/>
-      <c r="E161" s="5" t="n"/>
+      <c r="E161" s="6" t="n"/>
       <c r="F161" s="5" t="n"/>
-      <c r="G161" s="6" t="n"/>
+      <c r="G161" s="5" t="n"/>
+      <c r="H161" s="6" t="n"/>
     </row>
     <row r="162" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A162" s="4" t="n">
@@ -2354,9 +2533,10 @@
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="6" t="n"/>
       <c r="D162" s="6" t="n"/>
-      <c r="E162" s="5" t="n"/>
+      <c r="E162" s="6" t="n"/>
       <c r="F162" s="5" t="n"/>
-      <c r="G162" s="6" t="n"/>
+      <c r="G162" s="5" t="n"/>
+      <c r="H162" s="6" t="n"/>
     </row>
     <row r="163" hidden="1" outlineLevel="2">
       <c r="A163" s="4" t="n">
@@ -2365,9 +2545,10 @@
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="6" t="n"/>
       <c r="D163" s="6" t="n"/>
-      <c r="E163" s="5" t="n"/>
+      <c r="E163" s="6" t="n"/>
       <c r="F163" s="5" t="n"/>
-      <c r="G163" s="6" t="n"/>
+      <c r="G163" s="5" t="n"/>
+      <c r="H163" s="6" t="n"/>
     </row>
     <row r="164" hidden="1" outlineLevel="2">
       <c r="A164" s="4" t="n">
@@ -2376,9 +2557,10 @@
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="6" t="n"/>
       <c r="D164" s="6" t="n"/>
-      <c r="E164" s="5" t="n"/>
+      <c r="E164" s="6" t="n"/>
       <c r="F164" s="5" t="n"/>
-      <c r="G164" s="6" t="n"/>
+      <c r="G164" s="5" t="n"/>
+      <c r="H164" s="6" t="n"/>
     </row>
     <row r="165" hidden="1" outlineLevel="2">
       <c r="A165" s="4" t="n">
@@ -2387,9 +2569,10 @@
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="6" t="n"/>
       <c r="D165" s="6" t="n"/>
-      <c r="E165" s="5" t="n"/>
+      <c r="E165" s="6" t="n"/>
       <c r="F165" s="5" t="n"/>
-      <c r="G165" s="6" t="n"/>
+      <c r="G165" s="5" t="n"/>
+      <c r="H165" s="6" t="n"/>
     </row>
     <row r="166" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A166" s="4" t="n">
@@ -2398,9 +2581,10 @@
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="6" t="n"/>
       <c r="D166" s="6" t="n"/>
-      <c r="E166" s="5" t="n"/>
+      <c r="E166" s="6" t="n"/>
       <c r="F166" s="5" t="n"/>
-      <c r="G166" s="6" t="n"/>
+      <c r="G166" s="5" t="n"/>
+      <c r="H166" s="6" t="n"/>
     </row>
     <row r="167" hidden="1" outlineLevel="2">
       <c r="A167" s="4" t="n">
@@ -2409,9 +2593,10 @@
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="6" t="n"/>
       <c r="D167" s="6" t="n"/>
-      <c r="E167" s="5" t="n"/>
+      <c r="E167" s="6" t="n"/>
       <c r="F167" s="5" t="n"/>
-      <c r="G167" s="6" t="n"/>
+      <c r="G167" s="5" t="n"/>
+      <c r="H167" s="6" t="n"/>
     </row>
     <row r="168" hidden="1" outlineLevel="2">
       <c r="A168" s="4" t="n">
@@ -2420,9 +2605,10 @@
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="6" t="n"/>
       <c r="D168" s="6" t="n"/>
-      <c r="E168" s="5" t="n"/>
+      <c r="E168" s="6" t="n"/>
       <c r="F168" s="5" t="n"/>
-      <c r="G168" s="6" t="n"/>
+      <c r="G168" s="5" t="n"/>
+      <c r="H168" s="6" t="n"/>
     </row>
     <row r="169" hidden="1" outlineLevel="2">
       <c r="A169" s="4" t="n">
@@ -2431,9 +2617,10 @@
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="6" t="n"/>
       <c r="D169" s="6" t="n"/>
-      <c r="E169" s="5" t="n"/>
+      <c r="E169" s="6" t="n"/>
       <c r="F169" s="5" t="n"/>
-      <c r="G169" s="6" t="n"/>
+      <c r="G169" s="5" t="n"/>
+      <c r="H169" s="6" t="n"/>
     </row>
     <row r="170" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A170" s="4" t="n">
@@ -2442,9 +2629,10 @@
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="6" t="n"/>
       <c r="D170" s="6" t="n"/>
-      <c r="E170" s="5" t="n"/>
+      <c r="E170" s="6" t="n"/>
       <c r="F170" s="5" t="n"/>
-      <c r="G170" s="6" t="n"/>
+      <c r="G170" s="5" t="n"/>
+      <c r="H170" s="6" t="n"/>
     </row>
     <row r="171" hidden="1" outlineLevel="2">
       <c r="A171" s="4" t="n">
@@ -2453,9 +2641,10 @@
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="6" t="n"/>
       <c r="D171" s="6" t="n"/>
-      <c r="E171" s="5" t="n"/>
+      <c r="E171" s="6" t="n"/>
       <c r="F171" s="5" t="n"/>
-      <c r="G171" s="6" t="n"/>
+      <c r="G171" s="5" t="n"/>
+      <c r="H171" s="6" t="n"/>
     </row>
     <row r="172" hidden="1" outlineLevel="2">
       <c r="A172" s="4" t="n">
@@ -2464,9 +2653,10 @@
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="6" t="n"/>
       <c r="D172" s="6" t="n"/>
-      <c r="E172" s="5" t="n"/>
+      <c r="E172" s="6" t="n"/>
       <c r="F172" s="5" t="n"/>
-      <c r="G172" s="6" t="n"/>
+      <c r="G172" s="5" t="n"/>
+      <c r="H172" s="6" t="n"/>
     </row>
     <row r="173" hidden="1" outlineLevel="2">
       <c r="A173" s="4" t="n">
@@ -2475,9 +2665,10 @@
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="6" t="n"/>
       <c r="D173" s="6" t="n"/>
-      <c r="E173" s="5" t="n"/>
+      <c r="E173" s="6" t="n"/>
       <c r="F173" s="5" t="n"/>
-      <c r="G173" s="6" t="n"/>
+      <c r="G173" s="5" t="n"/>
+      <c r="H173" s="6" t="n"/>
     </row>
     <row r="174" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A174" s="4" t="n">
@@ -2486,9 +2677,10 @@
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="6" t="n"/>
       <c r="D174" s="6" t="n"/>
-      <c r="E174" s="5" t="n"/>
+      <c r="E174" s="6" t="n"/>
       <c r="F174" s="5" t="n"/>
-      <c r="G174" s="6" t="n"/>
+      <c r="G174" s="5" t="n"/>
+      <c r="H174" s="6" t="n"/>
     </row>
     <row r="175" hidden="1" outlineLevel="2">
       <c r="A175" s="4" t="n">
@@ -2497,9 +2689,10 @@
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="6" t="n"/>
       <c r="D175" s="6" t="n"/>
-      <c r="E175" s="5" t="n"/>
+      <c r="E175" s="6" t="n"/>
       <c r="F175" s="5" t="n"/>
-      <c r="G175" s="6" t="n"/>
+      <c r="G175" s="5" t="n"/>
+      <c r="H175" s="6" t="n"/>
     </row>
     <row r="176" hidden="1" outlineLevel="2">
       <c r="A176" s="4" t="n">
@@ -2508,9 +2701,10 @@
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="6" t="n"/>
       <c r="D176" s="6" t="n"/>
-      <c r="E176" s="5" t="n"/>
+      <c r="E176" s="6" t="n"/>
       <c r="F176" s="5" t="n"/>
-      <c r="G176" s="6" t="n"/>
+      <c r="G176" s="5" t="n"/>
+      <c r="H176" s="6" t="n"/>
     </row>
     <row r="177" hidden="1" outlineLevel="2">
       <c r="A177" s="4" t="n">
@@ -2519,9 +2713,10 @@
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="6" t="n"/>
       <c r="D177" s="6" t="n"/>
-      <c r="E177" s="5" t="n"/>
+      <c r="E177" s="6" t="n"/>
       <c r="F177" s="5" t="n"/>
-      <c r="G177" s="6" t="n"/>
+      <c r="G177" s="5" t="n"/>
+      <c r="H177" s="6" t="n"/>
     </row>
     <row r="178" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A178" s="4" t="n">
@@ -2530,9 +2725,10 @@
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="6" t="n"/>
       <c r="D178" s="6" t="n"/>
-      <c r="E178" s="5" t="n"/>
+      <c r="E178" s="6" t="n"/>
       <c r="F178" s="5" t="n"/>
-      <c r="G178" s="6" t="n"/>
+      <c r="G178" s="5" t="n"/>
+      <c r="H178" s="6" t="n"/>
     </row>
     <row r="179" hidden="1" outlineLevel="2">
       <c r="A179" s="4" t="n">
@@ -2541,9 +2737,10 @@
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="6" t="n"/>
       <c r="D179" s="6" t="n"/>
-      <c r="E179" s="5" t="n"/>
+      <c r="E179" s="6" t="n"/>
       <c r="F179" s="5" t="n"/>
-      <c r="G179" s="6" t="n"/>
+      <c r="G179" s="5" t="n"/>
+      <c r="H179" s="6" t="n"/>
     </row>
     <row r="180" hidden="1" outlineLevel="2">
       <c r="A180" s="4" t="n">
@@ -2552,9 +2749,10 @@
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="6" t="n"/>
       <c r="D180" s="6" t="n"/>
-      <c r="E180" s="5" t="n"/>
+      <c r="E180" s="6" t="n"/>
       <c r="F180" s="5" t="n"/>
-      <c r="G180" s="6" t="n"/>
+      <c r="G180" s="5" t="n"/>
+      <c r="H180" s="6" t="n"/>
     </row>
     <row r="181" hidden="1" outlineLevel="2">
       <c r="A181" s="4" t="n">
@@ -2563,9 +2761,10 @@
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="6" t="n"/>
       <c r="D181" s="6" t="n"/>
-      <c r="E181" s="5" t="n"/>
+      <c r="E181" s="6" t="n"/>
       <c r="F181" s="5" t="n"/>
-      <c r="G181" s="6" t="n"/>
+      <c r="G181" s="5" t="n"/>
+      <c r="H181" s="6" t="n"/>
     </row>
     <row r="182" collapsed="1" ht="28.8" customHeight="1">
       <c r="A182" s="4" t="n">
@@ -2583,9 +2782,10 @@
         </is>
       </c>
       <c r="D182" s="6" t="n"/>
-      <c r="E182" s="5" t="n"/>
+      <c r="E182" s="6" t="n"/>
       <c r="F182" s="5" t="n"/>
-      <c r="G182" s="6" t="n"/>
+      <c r="G182" s="5" t="n"/>
+      <c r="H182" s="6" t="n"/>
     </row>
     <row r="183" hidden="1" outlineLevel="2">
       <c r="A183" s="4" t="n">
@@ -2594,9 +2794,10 @@
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="6" t="n"/>
       <c r="D183" s="6" t="n"/>
-      <c r="E183" s="5" t="n"/>
+      <c r="E183" s="6" t="n"/>
       <c r="F183" s="5" t="n"/>
-      <c r="G183" s="6" t="n"/>
+      <c r="G183" s="5" t="n"/>
+      <c r="H183" s="6" t="n"/>
     </row>
     <row r="184" hidden="1" outlineLevel="2">
       <c r="A184" s="4" t="n">
@@ -2605,9 +2806,10 @@
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="6" t="n"/>
       <c r="D184" s="6" t="n"/>
-      <c r="E184" s="5" t="n"/>
+      <c r="E184" s="6" t="n"/>
       <c r="F184" s="5" t="n"/>
-      <c r="G184" s="6" t="n"/>
+      <c r="G184" s="5" t="n"/>
+      <c r="H184" s="6" t="n"/>
     </row>
     <row r="185" hidden="1" outlineLevel="2">
       <c r="A185" s="4" t="n">
@@ -2616,9 +2818,10 @@
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="6" t="n"/>
       <c r="D185" s="6" t="n"/>
-      <c r="E185" s="5" t="n"/>
+      <c r="E185" s="6" t="n"/>
       <c r="F185" s="5" t="n"/>
-      <c r="G185" s="6" t="n"/>
+      <c r="G185" s="5" t="n"/>
+      <c r="H185" s="6" t="n"/>
     </row>
     <row r="186" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A186" s="4" t="n">
@@ -2627,9 +2830,10 @@
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="6" t="n"/>
       <c r="D186" s="6" t="n"/>
-      <c r="E186" s="5" t="n"/>
+      <c r="E186" s="6" t="n"/>
       <c r="F186" s="5" t="n"/>
-      <c r="G186" s="6" t="n"/>
+      <c r="G186" s="5" t="n"/>
+      <c r="H186" s="6" t="n"/>
     </row>
     <row r="187" hidden="1" outlineLevel="2">
       <c r="A187" s="4" t="n">
@@ -2638,9 +2842,10 @@
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="6" t="n"/>
       <c r="D187" s="6" t="n"/>
-      <c r="E187" s="5" t="n"/>
+      <c r="E187" s="6" t="n"/>
       <c r="F187" s="5" t="n"/>
-      <c r="G187" s="6" t="n"/>
+      <c r="G187" s="5" t="n"/>
+      <c r="H187" s="6" t="n"/>
     </row>
     <row r="188" hidden="1" outlineLevel="2">
       <c r="A188" s="4" t="n">
@@ -2649,9 +2854,10 @@
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="6" t="n"/>
       <c r="D188" s="6" t="n"/>
-      <c r="E188" s="5" t="n"/>
+      <c r="E188" s="6" t="n"/>
       <c r="F188" s="5" t="n"/>
-      <c r="G188" s="6" t="n"/>
+      <c r="G188" s="5" t="n"/>
+      <c r="H188" s="6" t="n"/>
     </row>
     <row r="189" hidden="1" outlineLevel="2">
       <c r="A189" s="4" t="n">
@@ -2660,9 +2866,10 @@
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="6" t="n"/>
       <c r="D189" s="6" t="n"/>
-      <c r="E189" s="5" t="n"/>
+      <c r="E189" s="6" t="n"/>
       <c r="F189" s="5" t="n"/>
-      <c r="G189" s="6" t="n"/>
+      <c r="G189" s="5" t="n"/>
+      <c r="H189" s="6" t="n"/>
     </row>
     <row r="190" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A190" s="4" t="n">
@@ -2671,9 +2878,10 @@
       <c r="B190" s="5" t="n"/>
       <c r="C190" s="6" t="n"/>
       <c r="D190" s="6" t="n"/>
-      <c r="E190" s="5" t="n"/>
+      <c r="E190" s="6" t="n"/>
       <c r="F190" s="5" t="n"/>
-      <c r="G190" s="6" t="n"/>
+      <c r="G190" s="5" t="n"/>
+      <c r="H190" s="6" t="n"/>
     </row>
     <row r="191" hidden="1" outlineLevel="2">
       <c r="A191" s="4" t="n">
@@ -2682,9 +2890,10 @@
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="6" t="n"/>
       <c r="D191" s="6" t="n"/>
-      <c r="E191" s="5" t="n"/>
+      <c r="E191" s="6" t="n"/>
       <c r="F191" s="5" t="n"/>
-      <c r="G191" s="6" t="n"/>
+      <c r="G191" s="5" t="n"/>
+      <c r="H191" s="6" t="n"/>
     </row>
     <row r="192" hidden="1" outlineLevel="2">
       <c r="A192" s="4" t="n">
@@ -2693,9 +2902,10 @@
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="6" t="n"/>
       <c r="D192" s="6" t="n"/>
-      <c r="E192" s="5" t="n"/>
+      <c r="E192" s="6" t="n"/>
       <c r="F192" s="5" t="n"/>
-      <c r="G192" s="6" t="n"/>
+      <c r="G192" s="5" t="n"/>
+      <c r="H192" s="6" t="n"/>
     </row>
     <row r="193" hidden="1" outlineLevel="2">
       <c r="A193" s="4" t="n">
@@ -2704,9 +2914,10 @@
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="6" t="n"/>
       <c r="D193" s="6" t="n"/>
-      <c r="E193" s="5" t="n"/>
+      <c r="E193" s="6" t="n"/>
       <c r="F193" s="5" t="n"/>
-      <c r="G193" s="6" t="n"/>
+      <c r="G193" s="5" t="n"/>
+      <c r="H193" s="6" t="n"/>
     </row>
     <row r="194" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A194" s="4" t="n">
@@ -2715,9 +2926,10 @@
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="6" t="n"/>
       <c r="D194" s="6" t="n"/>
-      <c r="E194" s="5" t="n"/>
+      <c r="E194" s="6" t="n"/>
       <c r="F194" s="5" t="n"/>
-      <c r="G194" s="6" t="n"/>
+      <c r="G194" s="5" t="n"/>
+      <c r="H194" s="6" t="n"/>
     </row>
     <row r="195" hidden="1" outlineLevel="2">
       <c r="A195" s="4" t="n">
@@ -2726,9 +2938,10 @@
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="6" t="n"/>
       <c r="D195" s="6" t="n"/>
-      <c r="E195" s="5" t="n"/>
+      <c r="E195" s="6" t="n"/>
       <c r="F195" s="5" t="n"/>
-      <c r="G195" s="6" t="n"/>
+      <c r="G195" s="5" t="n"/>
+      <c r="H195" s="6" t="n"/>
     </row>
     <row r="196" hidden="1" outlineLevel="2">
       <c r="A196" s="4" t="n">
@@ -2737,9 +2950,10 @@
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="6" t="n"/>
       <c r="D196" s="6" t="n"/>
-      <c r="E196" s="5" t="n"/>
+      <c r="E196" s="6" t="n"/>
       <c r="F196" s="5" t="n"/>
-      <c r="G196" s="6" t="n"/>
+      <c r="G196" s="5" t="n"/>
+      <c r="H196" s="6" t="n"/>
     </row>
     <row r="197" hidden="1" outlineLevel="2">
       <c r="A197" s="4" t="n">
@@ -2748,9 +2962,10 @@
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="6" t="n"/>
       <c r="D197" s="6" t="n"/>
-      <c r="E197" s="5" t="n"/>
+      <c r="E197" s="6" t="n"/>
       <c r="F197" s="5" t="n"/>
-      <c r="G197" s="6" t="n"/>
+      <c r="G197" s="5" t="n"/>
+      <c r="H197" s="6" t="n"/>
     </row>
     <row r="198" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A198" s="4" t="n">
@@ -2759,9 +2974,10 @@
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="6" t="n"/>
       <c r="D198" s="6" t="n"/>
-      <c r="E198" s="5" t="n"/>
+      <c r="E198" s="6" t="n"/>
       <c r="F198" s="5" t="n"/>
-      <c r="G198" s="6" t="n"/>
+      <c r="G198" s="5" t="n"/>
+      <c r="H198" s="6" t="n"/>
     </row>
     <row r="199" hidden="1" outlineLevel="2">
       <c r="A199" s="4" t="n">
@@ -2770,9 +2986,10 @@
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="6" t="n"/>
       <c r="D199" s="6" t="n"/>
-      <c r="E199" s="5" t="n"/>
+      <c r="E199" s="6" t="n"/>
       <c r="F199" s="5" t="n"/>
-      <c r="G199" s="6" t="n"/>
+      <c r="G199" s="5" t="n"/>
+      <c r="H199" s="6" t="n"/>
     </row>
     <row r="200" hidden="1" outlineLevel="2">
       <c r="A200" s="4" t="n">
@@ -2781,9 +2998,10 @@
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="6" t="n"/>
       <c r="D200" s="6" t="n"/>
-      <c r="E200" s="5" t="n"/>
+      <c r="E200" s="6" t="n"/>
       <c r="F200" s="5" t="n"/>
-      <c r="G200" s="6" t="n"/>
+      <c r="G200" s="5" t="n"/>
+      <c r="H200" s="6" t="n"/>
     </row>
     <row r="201" hidden="1" outlineLevel="2">
       <c r="A201" s="4" t="n">
@@ -2792,9 +3010,10 @@
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="6" t="n"/>
       <c r="D201" s="6" t="n"/>
-      <c r="E201" s="5" t="n"/>
+      <c r="E201" s="6" t="n"/>
       <c r="F201" s="5" t="n"/>
-      <c r="G201" s="6" t="n"/>
+      <c r="G201" s="5" t="n"/>
+      <c r="H201" s="6" t="n"/>
     </row>
     <row r="202" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A202" s="4" t="n">
@@ -2803,9 +3022,10 @@
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="6" t="n"/>
       <c r="D202" s="6" t="n"/>
-      <c r="E202" s="5" t="n"/>
+      <c r="E202" s="6" t="n"/>
       <c r="F202" s="5" t="n"/>
-      <c r="G202" s="6" t="n"/>
+      <c r="G202" s="5" t="n"/>
+      <c r="H202" s="6" t="n"/>
     </row>
     <row r="203" hidden="1" outlineLevel="2">
       <c r="A203" s="4" t="n">
@@ -2814,9 +3034,10 @@
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="6" t="n"/>
       <c r="D203" s="6" t="n"/>
-      <c r="E203" s="5" t="n"/>
+      <c r="E203" s="6" t="n"/>
       <c r="F203" s="5" t="n"/>
-      <c r="G203" s="6" t="n"/>
+      <c r="G203" s="5" t="n"/>
+      <c r="H203" s="6" t="n"/>
     </row>
     <row r="204" hidden="1" outlineLevel="2">
       <c r="A204" s="4" t="n">
@@ -2825,9 +3046,10 @@
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="6" t="n"/>
       <c r="D204" s="6" t="n"/>
-      <c r="E204" s="5" t="n"/>
+      <c r="E204" s="6" t="n"/>
       <c r="F204" s="5" t="n"/>
-      <c r="G204" s="6" t="n"/>
+      <c r="G204" s="5" t="n"/>
+      <c r="H204" s="6" t="n"/>
     </row>
     <row r="205" hidden="1" outlineLevel="2">
       <c r="A205" s="4" t="n">
@@ -2836,9 +3058,10 @@
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="6" t="n"/>
       <c r="D205" s="6" t="n"/>
-      <c r="E205" s="5" t="n"/>
+      <c r="E205" s="6" t="n"/>
       <c r="F205" s="5" t="n"/>
-      <c r="G205" s="6" t="n"/>
+      <c r="G205" s="5" t="n"/>
+      <c r="H205" s="6" t="n"/>
     </row>
     <row r="206" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A206" s="4" t="n">
@@ -2847,9 +3070,10 @@
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="6" t="n"/>
       <c r="D206" s="6" t="n"/>
-      <c r="E206" s="5" t="n"/>
+      <c r="E206" s="6" t="n"/>
       <c r="F206" s="5" t="n"/>
-      <c r="G206" s="6" t="n"/>
+      <c r="G206" s="5" t="n"/>
+      <c r="H206" s="6" t="n"/>
     </row>
     <row r="207" hidden="1" outlineLevel="2">
       <c r="A207" s="4" t="n">
@@ -2858,9 +3082,10 @@
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="6" t="n"/>
       <c r="D207" s="6" t="n"/>
-      <c r="E207" s="5" t="n"/>
+      <c r="E207" s="6" t="n"/>
       <c r="F207" s="5" t="n"/>
-      <c r="G207" s="6" t="n"/>
+      <c r="G207" s="5" t="n"/>
+      <c r="H207" s="6" t="n"/>
     </row>
     <row r="208" hidden="1" outlineLevel="2">
       <c r="A208" s="4" t="n">
@@ -2869,9 +3094,10 @@
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="6" t="n"/>
       <c r="D208" s="6" t="n"/>
-      <c r="E208" s="5" t="n"/>
+      <c r="E208" s="6" t="n"/>
       <c r="F208" s="5" t="n"/>
-      <c r="G208" s="6" t="n"/>
+      <c r="G208" s="5" t="n"/>
+      <c r="H208" s="6" t="n"/>
     </row>
     <row r="209" hidden="1" outlineLevel="2">
       <c r="A209" s="4" t="n">
@@ -2880,9 +3106,10 @@
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="6" t="n"/>
       <c r="D209" s="6" t="n"/>
-      <c r="E209" s="5" t="n"/>
+      <c r="E209" s="6" t="n"/>
       <c r="F209" s="5" t="n"/>
-      <c r="G209" s="6" t="n"/>
+      <c r="G209" s="5" t="n"/>
+      <c r="H209" s="6" t="n"/>
     </row>
     <row r="210" collapsed="1" ht="28.8" customHeight="1">
       <c r="A210" s="4" t="n">
@@ -2900,9 +3127,10 @@
         </is>
       </c>
       <c r="D210" s="6" t="n"/>
-      <c r="E210" s="5" t="n"/>
+      <c r="E210" s="6" t="n"/>
       <c r="F210" s="5" t="n"/>
-      <c r="G210" s="6" t="n"/>
+      <c r="G210" s="5" t="n"/>
+      <c r="H210" s="6" t="n"/>
     </row>
     <row r="211" hidden="1" outlineLevel="2">
       <c r="A211" s="4" t="n">
@@ -2911,9 +3139,10 @@
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="6" t="n"/>
       <c r="D211" s="6" t="n"/>
-      <c r="E211" s="5" t="n"/>
+      <c r="E211" s="6" t="n"/>
       <c r="F211" s="5" t="n"/>
-      <c r="G211" s="6" t="n"/>
+      <c r="G211" s="5" t="n"/>
+      <c r="H211" s="6" t="n"/>
     </row>
     <row r="212" collapsed="1" ht="28.8" customHeight="1">
       <c r="A212" s="4" t="n">
@@ -2932,9 +3161,10 @@
         </is>
       </c>
       <c r="D212" s="6" t="n"/>
-      <c r="E212" s="5" t="n"/>
+      <c r="E212" s="6" t="n"/>
       <c r="F212" s="5" t="n"/>
-      <c r="G212" s="6" t="n"/>
+      <c r="G212" s="5" t="n"/>
+      <c r="H212" s="6" t="n"/>
     </row>
     <row r="213" hidden="1" outlineLevel="2">
       <c r="A213" s="4" t="n">
@@ -2943,9 +3173,10 @@
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="6" t="n"/>
       <c r="D213" s="6" t="n"/>
-      <c r="E213" s="5" t="n"/>
+      <c r="E213" s="6" t="n"/>
       <c r="F213" s="5" t="n"/>
-      <c r="G213" s="6" t="n"/>
+      <c r="G213" s="5" t="n"/>
+      <c r="H213" s="6" t="n"/>
     </row>
     <row r="214" ht="28.8" customHeight="1">
       <c r="A214" s="4" t="n">
@@ -2964,9 +3195,10 @@
         </is>
       </c>
       <c r="D214" s="6" t="n"/>
-      <c r="E214" s="5" t="n"/>
+      <c r="E214" s="6" t="n"/>
       <c r="F214" s="5" t="n"/>
-      <c r="G214" s="6" t="n"/>
+      <c r="G214" s="5" t="n"/>
+      <c r="H214" s="6" t="n"/>
     </row>
     <row r="215" outlineLevel="2">
       <c r="A215" s="4" t="n">
@@ -2975,9 +3207,10 @@
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="6" t="n"/>
       <c r="D215" s="6" t="n"/>
-      <c r="E215" s="5" t="n"/>
+      <c r="E215" s="6" t="n"/>
       <c r="F215" s="5" t="n"/>
-      <c r="G215" s="6" t="n"/>
+      <c r="G215" s="5" t="n"/>
+      <c r="H215" s="6" t="n"/>
     </row>
     <row r="216" outlineLevel="2">
       <c r="A216" s="4" t="n">
@@ -2986,9 +3219,10 @@
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="6" t="n"/>
       <c r="D216" s="6" t="n"/>
-      <c r="E216" s="5" t="n"/>
+      <c r="E216" s="6" t="n"/>
       <c r="F216" s="5" t="n"/>
-      <c r="G216" s="6" t="n"/>
+      <c r="G216" s="5" t="n"/>
+      <c r="H216" s="6" t="n"/>
     </row>
     <row r="217" outlineLevel="2">
       <c r="A217" s="4" t="n">
@@ -2997,9 +3231,10 @@
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="6" t="n"/>
       <c r="D217" s="6" t="n"/>
-      <c r="E217" s="5" t="n"/>
+      <c r="E217" s="6" t="n"/>
       <c r="F217" s="5" t="n"/>
-      <c r="G217" s="6" t="n"/>
+      <c r="G217" s="5" t="n"/>
+      <c r="H217" s="6" t="n"/>
     </row>
     <row r="218" outlineLevel="1" collapsed="1">
       <c r="A218" s="4" t="n">
@@ -3008,9 +3243,10 @@
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="6" t="n"/>
       <c r="D218" s="6" t="n"/>
-      <c r="E218" s="5" t="n"/>
+      <c r="E218" s="6" t="n"/>
       <c r="F218" s="5" t="n"/>
-      <c r="G218" s="6" t="n"/>
+      <c r="G218" s="5" t="n"/>
+      <c r="H218" s="6" t="n"/>
     </row>
     <row r="219" hidden="1" outlineLevel="2">
       <c r="A219" s="4" t="n">
@@ -3019,9 +3255,10 @@
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="6" t="n"/>
       <c r="D219" s="6" t="n"/>
-      <c r="E219" s="5" t="n"/>
+      <c r="E219" s="6" t="n"/>
       <c r="F219" s="5" t="n"/>
-      <c r="G219" s="6" t="n"/>
+      <c r="G219" s="5" t="n"/>
+      <c r="H219" s="6" t="n"/>
     </row>
     <row r="220" hidden="1" outlineLevel="2">
       <c r="A220" s="4" t="n">
@@ -3030,9 +3267,10 @@
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="6" t="n"/>
       <c r="D220" s="6" t="n"/>
-      <c r="E220" s="5" t="n"/>
+      <c r="E220" s="6" t="n"/>
       <c r="F220" s="5" t="n"/>
-      <c r="G220" s="6" t="n"/>
+      <c r="G220" s="5" t="n"/>
+      <c r="H220" s="6" t="n"/>
     </row>
     <row r="221" hidden="1" outlineLevel="2">
       <c r="A221" s="4" t="n">
@@ -3041,9 +3279,10 @@
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="6" t="n"/>
       <c r="D221" s="6" t="n"/>
-      <c r="E221" s="5" t="n"/>
+      <c r="E221" s="6" t="n"/>
       <c r="F221" s="5" t="n"/>
-      <c r="G221" s="6" t="n"/>
+      <c r="G221" s="5" t="n"/>
+      <c r="H221" s="6" t="n"/>
     </row>
     <row r="222" outlineLevel="1" collapsed="1">
       <c r="A222" s="4" t="n">
@@ -3052,9 +3291,10 @@
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="6" t="n"/>
       <c r="D222" s="6" t="n"/>
-      <c r="E222" s="5" t="n"/>
+      <c r="E222" s="6" t="n"/>
       <c r="F222" s="5" t="n"/>
-      <c r="G222" s="6" t="n"/>
+      <c r="G222" s="5" t="n"/>
+      <c r="H222" s="6" t="n"/>
     </row>
     <row r="223" hidden="1" outlineLevel="2">
       <c r="A223" s="4" t="n">
@@ -3063,9 +3303,10 @@
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="6" t="n"/>
       <c r="D223" s="6" t="n"/>
-      <c r="E223" s="5" t="n"/>
+      <c r="E223" s="6" t="n"/>
       <c r="F223" s="5" t="n"/>
-      <c r="G223" s="6" t="n"/>
+      <c r="G223" s="5" t="n"/>
+      <c r="H223" s="6" t="n"/>
     </row>
     <row r="224" hidden="1" outlineLevel="2">
       <c r="A224" s="4" t="n">
@@ -3074,9 +3315,10 @@
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="6" t="n"/>
       <c r="D224" s="6" t="n"/>
-      <c r="E224" s="5" t="n"/>
+      <c r="E224" s="6" t="n"/>
       <c r="F224" s="5" t="n"/>
-      <c r="G224" s="6" t="n"/>
+      <c r="G224" s="5" t="n"/>
+      <c r="H224" s="6" t="n"/>
     </row>
     <row r="225" hidden="1" outlineLevel="2">
       <c r="A225" s="4" t="n">
@@ -3085,9 +3327,10 @@
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="6" t="n"/>
       <c r="D225" s="6" t="n"/>
-      <c r="E225" s="5" t="n"/>
+      <c r="E225" s="6" t="n"/>
       <c r="F225" s="5" t="n"/>
-      <c r="G225" s="6" t="n"/>
+      <c r="G225" s="5" t="n"/>
+      <c r="H225" s="6" t="n"/>
     </row>
     <row r="226" outlineLevel="1">
       <c r="A226" s="4" t="n">
@@ -3096,9 +3339,10 @@
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="6" t="n"/>
       <c r="D226" s="6" t="n"/>
-      <c r="E226" s="5" t="n"/>
+      <c r="E226" s="6" t="n"/>
       <c r="F226" s="5" t="n"/>
-      <c r="G226" s="6" t="n"/>
+      <c r="G226" s="5" t="n"/>
+      <c r="H226" s="6" t="n"/>
     </row>
     <row r="227" outlineLevel="2">
       <c r="A227" s="4" t="n">
@@ -3107,9 +3351,10 @@
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="6" t="n"/>
       <c r="D227" s="6" t="n"/>
-      <c r="E227" s="5" t="n"/>
+      <c r="E227" s="6" t="n"/>
       <c r="F227" s="5" t="n"/>
-      <c r="G227" s="6" t="n"/>
+      <c r="G227" s="5" t="n"/>
+      <c r="H227" s="6" t="n"/>
     </row>
     <row r="228" outlineLevel="2" ht="43.2" customHeight="1">
       <c r="A228" s="4" t="n">
@@ -3122,9 +3367,10 @@
         </is>
       </c>
       <c r="D228" s="6" t="n"/>
-      <c r="E228" s="5" t="n"/>
+      <c r="E228" s="6" t="n"/>
       <c r="F228" s="5" t="n"/>
-      <c r="G228" s="6" t="n"/>
+      <c r="G228" s="5" t="n"/>
+      <c r="H228" s="6" t="n"/>
     </row>
     <row r="229" outlineLevel="2">
       <c r="A229" s="4" t="n">
@@ -3137,9 +3383,10 @@
         </is>
       </c>
       <c r="D229" s="6" t="n"/>
-      <c r="E229" s="5" t="n"/>
+      <c r="E229" s="6" t="n"/>
       <c r="F229" s="5" t="n"/>
-      <c r="G229" s="6" t="n"/>
+      <c r="G229" s="5" t="n"/>
+      <c r="H229" s="6" t="n"/>
     </row>
     <row r="230" outlineLevel="1" collapsed="1">
       <c r="A230" s="4" t="n">
@@ -3152,9 +3399,10 @@
         </is>
       </c>
       <c r="D230" s="6" t="n"/>
-      <c r="E230" s="5" t="n"/>
+      <c r="E230" s="6" t="n"/>
       <c r="F230" s="5" t="n"/>
-      <c r="G230" s="6" t="n"/>
+      <c r="G230" s="5" t="n"/>
+      <c r="H230" s="6" t="n"/>
     </row>
     <row r="231" hidden="1" outlineLevel="2">
       <c r="A231" s="4" t="n">
@@ -3163,9 +3411,10 @@
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="6" t="n"/>
       <c r="D231" s="6" t="n"/>
-      <c r="E231" s="5" t="n"/>
+      <c r="E231" s="6" t="n"/>
       <c r="F231" s="5" t="n"/>
-      <c r="G231" s="6" t="n"/>
+      <c r="G231" s="5" t="n"/>
+      <c r="H231" s="6" t="n"/>
     </row>
     <row r="232" hidden="1" outlineLevel="2">
       <c r="A232" s="4" t="n">
@@ -3174,9 +3423,10 @@
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="6" t="n"/>
       <c r="D232" s="6" t="n"/>
-      <c r="E232" s="5" t="n"/>
+      <c r="E232" s="6" t="n"/>
       <c r="F232" s="5" t="n"/>
-      <c r="G232" s="6" t="n"/>
+      <c r="G232" s="5" t="n"/>
+      <c r="H232" s="6" t="n"/>
     </row>
     <row r="233" hidden="1" outlineLevel="2">
       <c r="A233" s="4" t="n">
@@ -3185,9 +3435,10 @@
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="6" t="n"/>
       <c r="D233" s="6" t="n"/>
-      <c r="E233" s="5" t="n"/>
+      <c r="E233" s="6" t="n"/>
       <c r="F233" s="5" t="n"/>
-      <c r="G233" s="6" t="n"/>
+      <c r="G233" s="5" t="n"/>
+      <c r="H233" s="6" t="n"/>
     </row>
     <row r="234" outlineLevel="1" collapsed="1">
       <c r="A234" s="4" t="n">
@@ -3196,9 +3447,10 @@
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="6" t="n"/>
       <c r="D234" s="6" t="n"/>
-      <c r="E234" s="5" t="n"/>
+      <c r="E234" s="6" t="n"/>
       <c r="F234" s="5" t="n"/>
-      <c r="G234" s="6" t="n"/>
+      <c r="G234" s="5" t="n"/>
+      <c r="H234" s="6" t="n"/>
     </row>
     <row r="235" hidden="1" outlineLevel="2">
       <c r="A235" s="4" t="n">
@@ -3207,9 +3459,10 @@
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="6" t="n"/>
       <c r="D235" s="6" t="n"/>
-      <c r="E235" s="5" t="n"/>
+      <c r="E235" s="6" t="n"/>
       <c r="F235" s="5" t="n"/>
-      <c r="G235" s="6" t="n"/>
+      <c r="G235" s="5" t="n"/>
+      <c r="H235" s="6" t="n"/>
     </row>
     <row r="236" hidden="1" outlineLevel="2">
       <c r="A236" s="4" t="n">
@@ -3218,9 +3471,10 @@
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="6" t="n"/>
       <c r="D236" s="6" t="n"/>
-      <c r="E236" s="5" t="n"/>
+      <c r="E236" s="6" t="n"/>
       <c r="F236" s="5" t="n"/>
-      <c r="G236" s="6" t="n"/>
+      <c r="G236" s="5" t="n"/>
+      <c r="H236" s="6" t="n"/>
     </row>
     <row r="237" hidden="1" outlineLevel="2">
       <c r="A237" s="4" t="n">
@@ -3229,9 +3483,10 @@
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="6" t="n"/>
       <c r="D237" s="6" t="n"/>
-      <c r="E237" s="5" t="n"/>
+      <c r="E237" s="6" t="n"/>
       <c r="F237" s="5" t="n"/>
-      <c r="G237" s="6" t="n"/>
+      <c r="G237" s="5" t="n"/>
+      <c r="H237" s="6" t="n"/>
     </row>
     <row r="238" outlineLevel="1" collapsed="1">
       <c r="A238" s="4" t="n">
@@ -3240,9 +3495,10 @@
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="6" t="n"/>
       <c r="D238" s="6" t="n"/>
-      <c r="E238" s="5" t="n"/>
+      <c r="E238" s="6" t="n"/>
       <c r="F238" s="5" t="n"/>
-      <c r="G238" s="6" t="n"/>
+      <c r="G238" s="5" t="n"/>
+      <c r="H238" s="6" t="n"/>
     </row>
     <row r="239" hidden="1" outlineLevel="2">
       <c r="A239" s="4" t="n">
@@ -3251,9 +3507,10 @@
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="6" t="n"/>
       <c r="D239" s="6" t="n"/>
-      <c r="E239" s="5" t="n"/>
+      <c r="E239" s="6" t="n"/>
       <c r="F239" s="5" t="n"/>
-      <c r="G239" s="6" t="n"/>
+      <c r="G239" s="5" t="n"/>
+      <c r="H239" s="6" t="n"/>
     </row>
     <row r="240" hidden="1" outlineLevel="2">
       <c r="A240" s="4" t="n">
@@ -3262,9 +3519,10 @@
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="6" t="n"/>
       <c r="D240" s="6" t="n"/>
-      <c r="E240" s="5" t="n"/>
+      <c r="E240" s="6" t="n"/>
       <c r="F240" s="5" t="n"/>
-      <c r="G240" s="6" t="n"/>
+      <c r="G240" s="5" t="n"/>
+      <c r="H240" s="6" t="n"/>
     </row>
     <row r="241" hidden="1" outlineLevel="2">
       <c r="A241" s="4" t="n">
@@ -3273,9 +3531,10 @@
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="6" t="n"/>
       <c r="D241" s="6" t="n"/>
-      <c r="E241" s="5" t="n"/>
+      <c r="E241" s="6" t="n"/>
       <c r="F241" s="5" t="n"/>
-      <c r="G241" s="6" t="n"/>
+      <c r="G241" s="5" t="n"/>
+      <c r="H241" s="6" t="n"/>
     </row>
     <row r="242" outlineLevel="1" collapsed="1">
       <c r="A242" s="4" t="n">
@@ -3284,9 +3543,10 @@
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="6" t="n"/>
       <c r="D242" s="6" t="n"/>
-      <c r="E242" s="5" t="n"/>
+      <c r="E242" s="6" t="n"/>
       <c r="F242" s="5" t="n"/>
-      <c r="G242" s="6" t="n"/>
+      <c r="G242" s="5" t="n"/>
+      <c r="H242" s="6" t="n"/>
     </row>
     <row r="243" hidden="1" outlineLevel="2">
       <c r="A243" s="4" t="n">
@@ -3295,9 +3555,10 @@
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="6" t="n"/>
       <c r="D243" s="6" t="n"/>
-      <c r="E243" s="5" t="n"/>
+      <c r="E243" s="6" t="n"/>
       <c r="F243" s="5" t="n"/>
-      <c r="G243" s="6" t="n"/>
+      <c r="G243" s="5" t="n"/>
+      <c r="H243" s="6" t="n"/>
     </row>
     <row r="244" hidden="1" outlineLevel="2">
       <c r="A244" s="4" t="n">
@@ -3306,9 +3567,10 @@
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="6" t="n"/>
       <c r="D244" s="6" t="n"/>
-      <c r="E244" s="5" t="n"/>
+      <c r="E244" s="6" t="n"/>
       <c r="F244" s="5" t="n"/>
-      <c r="G244" s="6" t="n"/>
+      <c r="G244" s="5" t="n"/>
+      <c r="H244" s="6" t="n"/>
     </row>
     <row r="245" hidden="1" outlineLevel="2">
       <c r="A245" s="4" t="n">
@@ -3317,9 +3579,10 @@
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="6" t="n"/>
       <c r="D245" s="6" t="n"/>
-      <c r="E245" s="5" t="n"/>
+      <c r="E245" s="6" t="n"/>
       <c r="F245" s="5" t="n"/>
-      <c r="G245" s="6" t="n"/>
+      <c r="G245" s="5" t="n"/>
+      <c r="H245" s="6" t="n"/>
     </row>
     <row r="246" collapsed="1" ht="28.8" customHeight="1">
       <c r="A246" s="4" t="n">
@@ -3337,9 +3600,10 @@
         </is>
       </c>
       <c r="D246" s="6" t="n"/>
-      <c r="E246" s="5" t="n"/>
+      <c r="E246" s="6" t="n"/>
       <c r="F246" s="5" t="n"/>
-      <c r="G246" s="6" t="n"/>
+      <c r="G246" s="5" t="n"/>
+      <c r="H246" s="6" t="n"/>
     </row>
     <row r="247" hidden="1" outlineLevel="2">
       <c r="A247" s="4" t="n">
@@ -3348,9 +3612,10 @@
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="6" t="n"/>
       <c r="D247" s="6" t="n"/>
-      <c r="E247" s="5" t="n"/>
+      <c r="E247" s="6" t="n"/>
       <c r="F247" s="5" t="n"/>
-      <c r="G247" s="6" t="n"/>
+      <c r="G247" s="5" t="n"/>
+      <c r="H247" s="6" t="n"/>
     </row>
     <row r="248" hidden="1" outlineLevel="2">
       <c r="A248" s="4" t="n">
@@ -3359,9 +3624,10 @@
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="6" t="n"/>
       <c r="D248" s="6" t="n"/>
-      <c r="E248" s="5" t="n"/>
+      <c r="E248" s="6" t="n"/>
       <c r="F248" s="5" t="n"/>
-      <c r="G248" s="6" t="n"/>
+      <c r="G248" s="5" t="n"/>
+      <c r="H248" s="6" t="n"/>
     </row>
     <row r="249" hidden="1" outlineLevel="2">
       <c r="A249" s="4" t="n">
@@ -3370,9 +3636,10 @@
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="6" t="n"/>
       <c r="D249" s="6" t="n"/>
-      <c r="E249" s="5" t="n"/>
+      <c r="E249" s="6" t="n"/>
       <c r="F249" s="5" t="n"/>
-      <c r="G249" s="6" t="n"/>
+      <c r="G249" s="5" t="n"/>
+      <c r="H249" s="6" t="n"/>
     </row>
     <row r="250" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A250" s="4" t="n">
@@ -3381,9 +3648,10 @@
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="6" t="n"/>
       <c r="D250" s="6" t="n"/>
-      <c r="E250" s="5" t="n"/>
+      <c r="E250" s="6" t="n"/>
       <c r="F250" s="5" t="n"/>
-      <c r="G250" s="6" t="n"/>
+      <c r="G250" s="5" t="n"/>
+      <c r="H250" s="6" t="n"/>
     </row>
     <row r="251" hidden="1" outlineLevel="2">
       <c r="A251" s="4" t="n">
@@ -3392,9 +3660,10 @@
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="6" t="n"/>
       <c r="D251" s="6" t="n"/>
-      <c r="E251" s="5" t="n"/>
+      <c r="E251" s="6" t="n"/>
       <c r="F251" s="5" t="n"/>
-      <c r="G251" s="6" t="n"/>
+      <c r="G251" s="5" t="n"/>
+      <c r="H251" s="6" t="n"/>
     </row>
     <row r="252" hidden="1" outlineLevel="2">
       <c r="A252" s="4" t="n">
@@ -3403,9 +3672,10 @@
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="6" t="n"/>
       <c r="D252" s="6" t="n"/>
-      <c r="E252" s="5" t="n"/>
+      <c r="E252" s="6" t="n"/>
       <c r="F252" s="5" t="n"/>
-      <c r="G252" s="6" t="n"/>
+      <c r="G252" s="5" t="n"/>
+      <c r="H252" s="6" t="n"/>
     </row>
     <row r="253" hidden="1" outlineLevel="2">
       <c r="A253" s="4" t="n">
@@ -3414,9 +3684,10 @@
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="6" t="n"/>
       <c r="D253" s="6" t="n"/>
-      <c r="E253" s="5" t="n"/>
+      <c r="E253" s="6" t="n"/>
       <c r="F253" s="5" t="n"/>
-      <c r="G253" s="6" t="n"/>
+      <c r="G253" s="5" t="n"/>
+      <c r="H253" s="6" t="n"/>
     </row>
     <row r="254" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A254" s="4" t="n">
@@ -3425,9 +3696,10 @@
       <c r="B254" s="5" t="n"/>
       <c r="C254" s="6" t="n"/>
       <c r="D254" s="6" t="n"/>
-      <c r="E254" s="5" t="n"/>
+      <c r="E254" s="6" t="n"/>
       <c r="F254" s="5" t="n"/>
-      <c r="G254" s="6" t="n"/>
+      <c r="G254" s="5" t="n"/>
+      <c r="H254" s="6" t="n"/>
     </row>
     <row r="255" hidden="1" outlineLevel="2">
       <c r="A255" s="4" t="n">
@@ -3436,9 +3708,10 @@
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="6" t="n"/>
       <c r="D255" s="6" t="n"/>
-      <c r="E255" s="5" t="n"/>
+      <c r="E255" s="6" t="n"/>
       <c r="F255" s="5" t="n"/>
-      <c r="G255" s="6" t="n"/>
+      <c r="G255" s="5" t="n"/>
+      <c r="H255" s="6" t="n"/>
     </row>
     <row r="256" hidden="1" outlineLevel="2">
       <c r="A256" s="4" t="n">
@@ -3447,9 +3720,10 @@
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6" t="n"/>
       <c r="D256" s="6" t="n"/>
-      <c r="E256" s="5" t="n"/>
+      <c r="E256" s="6" t="n"/>
       <c r="F256" s="5" t="n"/>
-      <c r="G256" s="6" t="n"/>
+      <c r="G256" s="5" t="n"/>
+      <c r="H256" s="6" t="n"/>
     </row>
     <row r="257" hidden="1" outlineLevel="2">
       <c r="A257" s="4" t="n">
@@ -3458,9 +3732,10 @@
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="6" t="n"/>
       <c r="D257" s="6" t="n"/>
-      <c r="E257" s="5" t="n"/>
+      <c r="E257" s="6" t="n"/>
       <c r="F257" s="5" t="n"/>
-      <c r="G257" s="6" t="n"/>
+      <c r="G257" s="5" t="n"/>
+      <c r="H257" s="6" t="n"/>
     </row>
     <row r="258" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A258" s="4" t="n">
@@ -3469,9 +3744,10 @@
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="6" t="n"/>
       <c r="D258" s="6" t="n"/>
-      <c r="E258" s="5" t="n"/>
+      <c r="E258" s="6" t="n"/>
       <c r="F258" s="5" t="n"/>
-      <c r="G258" s="6" t="n"/>
+      <c r="G258" s="5" t="n"/>
+      <c r="H258" s="6" t="n"/>
     </row>
     <row r="259" hidden="1" outlineLevel="2">
       <c r="A259" s="4" t="n">
@@ -3480,9 +3756,10 @@
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="6" t="n"/>
       <c r="D259" s="6" t="n"/>
-      <c r="E259" s="5" t="n"/>
+      <c r="E259" s="6" t="n"/>
       <c r="F259" s="5" t="n"/>
-      <c r="G259" s="6" t="n"/>
+      <c r="G259" s="5" t="n"/>
+      <c r="H259" s="6" t="n"/>
     </row>
     <row r="260" hidden="1" outlineLevel="2">
       <c r="A260" s="4" t="n">
@@ -3491,9 +3768,10 @@
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="6" t="n"/>
       <c r="D260" s="6" t="n"/>
-      <c r="E260" s="5" t="n"/>
+      <c r="E260" s="6" t="n"/>
       <c r="F260" s="5" t="n"/>
-      <c r="G260" s="6" t="n"/>
+      <c r="G260" s="5" t="n"/>
+      <c r="H260" s="6" t="n"/>
     </row>
     <row r="261" hidden="1" outlineLevel="2">
       <c r="A261" s="4" t="n">
@@ -3502,9 +3780,10 @@
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="6" t="n"/>
       <c r="D261" s="6" t="n"/>
-      <c r="E261" s="5" t="n"/>
+      <c r="E261" s="6" t="n"/>
       <c r="F261" s="5" t="n"/>
-      <c r="G261" s="6" t="n"/>
+      <c r="G261" s="5" t="n"/>
+      <c r="H261" s="6" t="n"/>
     </row>
     <row r="262" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A262" s="4" t="n">
@@ -3513,9 +3792,10 @@
       <c r="B262" s="5" t="n"/>
       <c r="C262" s="6" t="n"/>
       <c r="D262" s="6" t="n"/>
-      <c r="E262" s="5" t="n"/>
+      <c r="E262" s="6" t="n"/>
       <c r="F262" s="5" t="n"/>
-      <c r="G262" s="6" t="n"/>
+      <c r="G262" s="5" t="n"/>
+      <c r="H262" s="6" t="n"/>
     </row>
     <row r="263" hidden="1" outlineLevel="2">
       <c r="A263" s="4" t="n">
@@ -3524,9 +3804,10 @@
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="6" t="n"/>
       <c r="D263" s="6" t="n"/>
-      <c r="E263" s="5" t="n"/>
+      <c r="E263" s="6" t="n"/>
       <c r="F263" s="5" t="n"/>
-      <c r="G263" s="6" t="n"/>
+      <c r="G263" s="5" t="n"/>
+      <c r="H263" s="6" t="n"/>
     </row>
     <row r="264" hidden="1" outlineLevel="2">
       <c r="A264" s="4" t="n">
@@ -3535,9 +3816,10 @@
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="6" t="n"/>
       <c r="D264" s="6" t="n"/>
-      <c r="E264" s="5" t="n"/>
+      <c r="E264" s="6" t="n"/>
       <c r="F264" s="5" t="n"/>
-      <c r="G264" s="6" t="n"/>
+      <c r="G264" s="5" t="n"/>
+      <c r="H264" s="6" t="n"/>
     </row>
     <row r="265" hidden="1" outlineLevel="2">
       <c r="A265" s="4" t="n">
@@ -3546,9 +3828,10 @@
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="6" t="n"/>
       <c r="D265" s="6" t="n"/>
-      <c r="E265" s="5" t="n"/>
+      <c r="E265" s="6" t="n"/>
       <c r="F265" s="5" t="n"/>
-      <c r="G265" s="6" t="n"/>
+      <c r="G265" s="5" t="n"/>
+      <c r="H265" s="6" t="n"/>
     </row>
     <row r="266" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A266" s="4" t="n">
@@ -3557,9 +3840,10 @@
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="6" t="n"/>
       <c r="D266" s="6" t="n"/>
-      <c r="E266" s="5" t="n"/>
+      <c r="E266" s="6" t="n"/>
       <c r="F266" s="5" t="n"/>
-      <c r="G266" s="6" t="n"/>
+      <c r="G266" s="5" t="n"/>
+      <c r="H266" s="6" t="n"/>
     </row>
     <row r="267" hidden="1" outlineLevel="2">
       <c r="A267" s="4" t="n">
@@ -3568,9 +3852,10 @@
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="6" t="n"/>
       <c r="D267" s="6" t="n"/>
-      <c r="E267" s="5" t="n"/>
+      <c r="E267" s="6" t="n"/>
       <c r="F267" s="5" t="n"/>
-      <c r="G267" s="6" t="n"/>
+      <c r="G267" s="5" t="n"/>
+      <c r="H267" s="6" t="n"/>
     </row>
     <row r="268" hidden="1" outlineLevel="2">
       <c r="A268" s="4" t="n">
@@ -3579,9 +3864,10 @@
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="6" t="n"/>
       <c r="D268" s="6" t="n"/>
-      <c r="E268" s="5" t="n"/>
+      <c r="E268" s="6" t="n"/>
       <c r="F268" s="5" t="n"/>
-      <c r="G268" s="6" t="n"/>
+      <c r="G268" s="5" t="n"/>
+      <c r="H268" s="6" t="n"/>
     </row>
     <row r="269" hidden="1" outlineLevel="2">
       <c r="A269" s="4" t="n">
@@ -3590,9 +3876,10 @@
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="6" t="n"/>
       <c r="D269" s="6" t="n"/>
-      <c r="E269" s="5" t="n"/>
+      <c r="E269" s="6" t="n"/>
       <c r="F269" s="5" t="n"/>
-      <c r="G269" s="6" t="n"/>
+      <c r="G269" s="5" t="n"/>
+      <c r="H269" s="6" t="n"/>
     </row>
     <row r="270" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A270" s="4" t="n">
@@ -3601,9 +3888,10 @@
       <c r="B270" s="5" t="n"/>
       <c r="C270" s="6" t="n"/>
       <c r="D270" s="6" t="n"/>
-      <c r="E270" s="5" t="n"/>
+      <c r="E270" s="6" t="n"/>
       <c r="F270" s="5" t="n"/>
-      <c r="G270" s="6" t="n"/>
+      <c r="G270" s="5" t="n"/>
+      <c r="H270" s="6" t="n"/>
     </row>
     <row r="271" hidden="1" outlineLevel="2">
       <c r="A271" s="4" t="n">
@@ -3612,9 +3900,10 @@
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="6" t="n"/>
       <c r="D271" s="6" t="n"/>
-      <c r="E271" s="5" t="n"/>
+      <c r="E271" s="6" t="n"/>
       <c r="F271" s="5" t="n"/>
-      <c r="G271" s="6" t="n"/>
+      <c r="G271" s="5" t="n"/>
+      <c r="H271" s="6" t="n"/>
     </row>
     <row r="272" hidden="1" outlineLevel="2">
       <c r="A272" s="4" t="n">
@@ -3623,9 +3912,10 @@
       <c r="B272" s="5" t="n"/>
       <c r="C272" s="6" t="n"/>
       <c r="D272" s="6" t="n"/>
-      <c r="E272" s="5" t="n"/>
+      <c r="E272" s="6" t="n"/>
       <c r="F272" s="5" t="n"/>
-      <c r="G272" s="6" t="n"/>
+      <c r="G272" s="5" t="n"/>
+      <c r="H272" s="6" t="n"/>
     </row>
     <row r="273" hidden="1" outlineLevel="2">
       <c r="A273" s="4" t="n">
@@ -3634,9 +3924,10 @@
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="6" t="n"/>
       <c r="D273" s="6" t="n"/>
-      <c r="E273" s="5" t="n"/>
+      <c r="E273" s="6" t="n"/>
       <c r="F273" s="5" t="n"/>
-      <c r="G273" s="6" t="n"/>
+      <c r="G273" s="5" t="n"/>
+      <c r="H273" s="6" t="n"/>
     </row>
     <row r="274" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A274" s="4" t="n">
@@ -3645,9 +3936,10 @@
       <c r="B274" s="5" t="n"/>
       <c r="C274" s="6" t="n"/>
       <c r="D274" s="6" t="n"/>
-      <c r="E274" s="5" t="n"/>
+      <c r="E274" s="6" t="n"/>
       <c r="F274" s="5" t="n"/>
-      <c r="G274" s="6" t="n"/>
+      <c r="G274" s="5" t="n"/>
+      <c r="H274" s="6" t="n"/>
     </row>
     <row r="275" hidden="1" outlineLevel="2">
       <c r="A275" s="4" t="n">
@@ -3656,9 +3948,10 @@
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="6" t="n"/>
       <c r="D275" s="6" t="n"/>
-      <c r="E275" s="5" t="n"/>
+      <c r="E275" s="6" t="n"/>
       <c r="F275" s="5" t="n"/>
-      <c r="G275" s="6" t="n"/>
+      <c r="G275" s="5" t="n"/>
+      <c r="H275" s="6" t="n"/>
     </row>
     <row r="276" hidden="1" outlineLevel="2">
       <c r="A276" s="4" t="n">
@@ -3667,9 +3960,10 @@
       <c r="B276" s="5" t="n"/>
       <c r="C276" s="6" t="n"/>
       <c r="D276" s="6" t="n"/>
-      <c r="E276" s="5" t="n"/>
+      <c r="E276" s="6" t="n"/>
       <c r="F276" s="5" t="n"/>
-      <c r="G276" s="6" t="n"/>
+      <c r="G276" s="5" t="n"/>
+      <c r="H276" s="6" t="n"/>
     </row>
     <row r="277" hidden="1" outlineLevel="2">
       <c r="A277" s="4" t="n">
@@ -3678,9 +3972,10 @@
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="6" t="n"/>
       <c r="D277" s="6" t="n"/>
-      <c r="E277" s="5" t="n"/>
+      <c r="E277" s="6" t="n"/>
       <c r="F277" s="5" t="n"/>
-      <c r="G277" s="6" t="n"/>
+      <c r="G277" s="5" t="n"/>
+      <c r="H277" s="6" t="n"/>
     </row>
     <row r="278" collapsed="1" ht="28.8" customHeight="1">
       <c r="A278" s="4" t="n">
@@ -3698,9 +3993,10 @@
         </is>
       </c>
       <c r="D278" s="6" t="n"/>
-      <c r="E278" s="5" t="n"/>
+      <c r="E278" s="6" t="n"/>
       <c r="F278" s="5" t="n"/>
-      <c r="G278" s="6" t="n"/>
+      <c r="G278" s="5" t="n"/>
+      <c r="H278" s="6" t="n"/>
     </row>
     <row r="279" hidden="1" outlineLevel="2">
       <c r="A279" s="4" t="n">
@@ -3709,9 +4005,10 @@
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="6" t="n"/>
       <c r="D279" s="6" t="n"/>
-      <c r="E279" s="5" t="n"/>
+      <c r="E279" s="6" t="n"/>
       <c r="F279" s="5" t="n"/>
-      <c r="G279" s="6" t="n"/>
+      <c r="G279" s="5" t="n"/>
+      <c r="H279" s="6" t="n"/>
     </row>
     <row r="280" hidden="1" outlineLevel="2">
       <c r="A280" s="4" t="n">
@@ -3720,9 +4017,10 @@
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="6" t="n"/>
       <c r="D280" s="6" t="n"/>
-      <c r="E280" s="5" t="n"/>
+      <c r="E280" s="6" t="n"/>
       <c r="F280" s="5" t="n"/>
-      <c r="G280" s="6" t="n"/>
+      <c r="G280" s="5" t="n"/>
+      <c r="H280" s="6" t="n"/>
     </row>
     <row r="281" hidden="1" outlineLevel="2">
       <c r="A281" s="4" t="n">
@@ -3731,9 +4029,10 @@
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="6" t="n"/>
       <c r="D281" s="6" t="n"/>
-      <c r="E281" s="5" t="n"/>
+      <c r="E281" s="6" t="n"/>
       <c r="F281" s="5" t="n"/>
-      <c r="G281" s="6" t="n"/>
+      <c r="G281" s="5" t="n"/>
+      <c r="H281" s="6" t="n"/>
     </row>
     <row r="282" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A282" s="4" t="n">
@@ -3742,9 +4041,10 @@
       <c r="B282" s="5" t="n"/>
       <c r="C282" s="6" t="n"/>
       <c r="D282" s="6" t="n"/>
-      <c r="E282" s="5" t="n"/>
+      <c r="E282" s="6" t="n"/>
       <c r="F282" s="5" t="n"/>
-      <c r="G282" s="6" t="n"/>
+      <c r="G282" s="5" t="n"/>
+      <c r="H282" s="6" t="n"/>
     </row>
     <row r="283" hidden="1" outlineLevel="2">
       <c r="A283" s="4" t="n">
@@ -3753,9 +4053,10 @@
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="6" t="n"/>
       <c r="D283" s="6" t="n"/>
-      <c r="E283" s="5" t="n"/>
+      <c r="E283" s="6" t="n"/>
       <c r="F283" s="5" t="n"/>
-      <c r="G283" s="6" t="n"/>
+      <c r="G283" s="5" t="n"/>
+      <c r="H283" s="6" t="n"/>
     </row>
     <row r="284" hidden="1" outlineLevel="2">
       <c r="A284" s="4" t="n">
@@ -3764,9 +4065,10 @@
       <c r="B284" s="5" t="n"/>
       <c r="C284" s="6" t="n"/>
       <c r="D284" s="6" t="n"/>
-      <c r="E284" s="5" t="n"/>
+      <c r="E284" s="6" t="n"/>
       <c r="F284" s="5" t="n"/>
-      <c r="G284" s="6" t="n"/>
+      <c r="G284" s="5" t="n"/>
+      <c r="H284" s="6" t="n"/>
     </row>
     <row r="285" hidden="1" outlineLevel="2">
       <c r="A285" s="4" t="n">
@@ -3775,9 +4077,10 @@
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="6" t="n"/>
       <c r="D285" s="6" t="n"/>
-      <c r="E285" s="5" t="n"/>
+      <c r="E285" s="6" t="n"/>
       <c r="F285" s="5" t="n"/>
-      <c r="G285" s="6" t="n"/>
+      <c r="G285" s="5" t="n"/>
+      <c r="H285" s="6" t="n"/>
     </row>
     <row r="286" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A286" s="4" t="n">
@@ -3786,9 +4089,10 @@
       <c r="B286" s="5" t="n"/>
       <c r="C286" s="6" t="n"/>
       <c r="D286" s="6" t="n"/>
-      <c r="E286" s="5" t="n"/>
+      <c r="E286" s="6" t="n"/>
       <c r="F286" s="5" t="n"/>
-      <c r="G286" s="6" t="n"/>
+      <c r="G286" s="5" t="n"/>
+      <c r="H286" s="6" t="n"/>
     </row>
     <row r="287" hidden="1" outlineLevel="2">
       <c r="A287" s="4" t="n">
@@ -3797,9 +4101,10 @@
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="6" t="n"/>
       <c r="D287" s="6" t="n"/>
-      <c r="E287" s="5" t="n"/>
+      <c r="E287" s="6" t="n"/>
       <c r="F287" s="5" t="n"/>
-      <c r="G287" s="6" t="n"/>
+      <c r="G287" s="5" t="n"/>
+      <c r="H287" s="6" t="n"/>
     </row>
     <row r="288" hidden="1" outlineLevel="2">
       <c r="A288" s="4" t="n">
@@ -3808,9 +4113,10 @@
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="6" t="n"/>
       <c r="D288" s="6" t="n"/>
-      <c r="E288" s="5" t="n"/>
+      <c r="E288" s="6" t="n"/>
       <c r="F288" s="5" t="n"/>
-      <c r="G288" s="6" t="n"/>
+      <c r="G288" s="5" t="n"/>
+      <c r="H288" s="6" t="n"/>
     </row>
     <row r="289" hidden="1" outlineLevel="2">
       <c r="A289" s="4" t="n">
@@ -3819,9 +4125,10 @@
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="6" t="n"/>
       <c r="D289" s="6" t="n"/>
-      <c r="E289" s="5" t="n"/>
+      <c r="E289" s="6" t="n"/>
       <c r="F289" s="5" t="n"/>
-      <c r="G289" s="6" t="n"/>
+      <c r="G289" s="5" t="n"/>
+      <c r="H289" s="6" t="n"/>
     </row>
     <row r="290" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A290" s="4" t="n">
@@ -3830,9 +4137,10 @@
       <c r="B290" s="5" t="n"/>
       <c r="C290" s="6" t="n"/>
       <c r="D290" s="6" t="n"/>
-      <c r="E290" s="5" t="n"/>
+      <c r="E290" s="6" t="n"/>
       <c r="F290" s="5" t="n"/>
-      <c r="G290" s="6" t="n"/>
+      <c r="G290" s="5" t="n"/>
+      <c r="H290" s="6" t="n"/>
     </row>
     <row r="291" hidden="1" outlineLevel="2">
       <c r="A291" s="4" t="n">
@@ -3841,9 +4149,10 @@
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="6" t="n"/>
       <c r="D291" s="6" t="n"/>
-      <c r="E291" s="5" t="n"/>
+      <c r="E291" s="6" t="n"/>
       <c r="F291" s="5" t="n"/>
-      <c r="G291" s="6" t="n"/>
+      <c r="G291" s="5" t="n"/>
+      <c r="H291" s="6" t="n"/>
     </row>
     <row r="292" hidden="1" outlineLevel="2">
       <c r="A292" s="4" t="n">
@@ -3852,9 +4161,10 @@
       <c r="B292" s="5" t="n"/>
       <c r="C292" s="6" t="n"/>
       <c r="D292" s="6" t="n"/>
-      <c r="E292" s="5" t="n"/>
+      <c r="E292" s="6" t="n"/>
       <c r="F292" s="5" t="n"/>
-      <c r="G292" s="6" t="n"/>
+      <c r="G292" s="5" t="n"/>
+      <c r="H292" s="6" t="n"/>
     </row>
     <row r="293" hidden="1" outlineLevel="2">
       <c r="A293" s="4" t="n">
@@ -3863,9 +4173,10 @@
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="6" t="n"/>
       <c r="D293" s="6" t="n"/>
-      <c r="E293" s="5" t="n"/>
+      <c r="E293" s="6" t="n"/>
       <c r="F293" s="5" t="n"/>
-      <c r="G293" s="6" t="n"/>
+      <c r="G293" s="5" t="n"/>
+      <c r="H293" s="6" t="n"/>
     </row>
     <row r="294" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A294" s="4" t="n">
@@ -3874,9 +4185,10 @@
       <c r="B294" s="5" t="n"/>
       <c r="C294" s="6" t="n"/>
       <c r="D294" s="6" t="n"/>
-      <c r="E294" s="5" t="n"/>
+      <c r="E294" s="6" t="n"/>
       <c r="F294" s="5" t="n"/>
-      <c r="G294" s="6" t="n"/>
+      <c r="G294" s="5" t="n"/>
+      <c r="H294" s="6" t="n"/>
     </row>
     <row r="295" hidden="1" outlineLevel="2">
       <c r="A295" s="4" t="n">
@@ -3885,9 +4197,10 @@
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="6" t="n"/>
       <c r="D295" s="6" t="n"/>
-      <c r="E295" s="5" t="n"/>
+      <c r="E295" s="6" t="n"/>
       <c r="F295" s="5" t="n"/>
-      <c r="G295" s="6" t="n"/>
+      <c r="G295" s="5" t="n"/>
+      <c r="H295" s="6" t="n"/>
     </row>
     <row r="296" hidden="1" outlineLevel="2">
       <c r="A296" s="4" t="n">
@@ -3896,9 +4209,10 @@
       <c r="B296" s="5" t="n"/>
       <c r="C296" s="6" t="n"/>
       <c r="D296" s="6" t="n"/>
-      <c r="E296" s="5" t="n"/>
+      <c r="E296" s="6" t="n"/>
       <c r="F296" s="5" t="n"/>
-      <c r="G296" s="6" t="n"/>
+      <c r="G296" s="5" t="n"/>
+      <c r="H296" s="6" t="n"/>
     </row>
     <row r="297" hidden="1" outlineLevel="2">
       <c r="A297" s="4" t="n">
@@ -3907,9 +4221,10 @@
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="6" t="n"/>
       <c r="D297" s="6" t="n"/>
-      <c r="E297" s="5" t="n"/>
+      <c r="E297" s="6" t="n"/>
       <c r="F297" s="5" t="n"/>
-      <c r="G297" s="6" t="n"/>
+      <c r="G297" s="5" t="n"/>
+      <c r="H297" s="6" t="n"/>
     </row>
     <row r="298" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A298" s="4" t="n">
@@ -3918,9 +4233,10 @@
       <c r="B298" s="5" t="n"/>
       <c r="C298" s="6" t="n"/>
       <c r="D298" s="6" t="n"/>
-      <c r="E298" s="5" t="n"/>
+      <c r="E298" s="6" t="n"/>
       <c r="F298" s="5" t="n"/>
-      <c r="G298" s="6" t="n"/>
+      <c r="G298" s="5" t="n"/>
+      <c r="H298" s="6" t="n"/>
     </row>
     <row r="299" hidden="1" outlineLevel="2">
       <c r="A299" s="4" t="n">
@@ -3929,9 +4245,10 @@
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="6" t="n"/>
       <c r="D299" s="6" t="n"/>
-      <c r="E299" s="5" t="n"/>
+      <c r="E299" s="6" t="n"/>
       <c r="F299" s="5" t="n"/>
-      <c r="G299" s="6" t="n"/>
+      <c r="G299" s="5" t="n"/>
+      <c r="H299" s="6" t="n"/>
     </row>
     <row r="300" hidden="1" outlineLevel="2">
       <c r="A300" s="4" t="n">
@@ -3940,9 +4257,10 @@
       <c r="B300" s="5" t="n"/>
       <c r="C300" s="6" t="n"/>
       <c r="D300" s="6" t="n"/>
-      <c r="E300" s="5" t="n"/>
+      <c r="E300" s="6" t="n"/>
       <c r="F300" s="5" t="n"/>
-      <c r="G300" s="6" t="n"/>
+      <c r="G300" s="5" t="n"/>
+      <c r="H300" s="6" t="n"/>
     </row>
     <row r="301" hidden="1" outlineLevel="2">
       <c r="A301" s="4" t="n">
@@ -3951,9 +4269,10 @@
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="6" t="n"/>
       <c r="D301" s="6" t="n"/>
-      <c r="E301" s="5" t="n"/>
+      <c r="E301" s="6" t="n"/>
       <c r="F301" s="5" t="n"/>
-      <c r="G301" s="6" t="n"/>
+      <c r="G301" s="5" t="n"/>
+      <c r="H301" s="6" t="n"/>
     </row>
     <row r="302" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A302" s="4" t="n">
@@ -3962,9 +4281,10 @@
       <c r="B302" s="5" t="n"/>
       <c r="C302" s="6" t="n"/>
       <c r="D302" s="6" t="n"/>
-      <c r="E302" s="5" t="n"/>
+      <c r="E302" s="6" t="n"/>
       <c r="F302" s="5" t="n"/>
-      <c r="G302" s="6" t="n"/>
+      <c r="G302" s="5" t="n"/>
+      <c r="H302" s="6" t="n"/>
     </row>
     <row r="303" hidden="1" outlineLevel="2">
       <c r="A303" s="4" t="n">
@@ -3973,9 +4293,10 @@
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="6" t="n"/>
       <c r="D303" s="6" t="n"/>
-      <c r="E303" s="5" t="n"/>
+      <c r="E303" s="6" t="n"/>
       <c r="F303" s="5" t="n"/>
-      <c r="G303" s="6" t="n"/>
+      <c r="G303" s="5" t="n"/>
+      <c r="H303" s="6" t="n"/>
     </row>
     <row r="304" hidden="1" outlineLevel="2">
       <c r="A304" s="4" t="n">
@@ -3984,9 +4305,10 @@
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="6" t="n"/>
       <c r="D304" s="6" t="n"/>
-      <c r="E304" s="5" t="n"/>
+      <c r="E304" s="6" t="n"/>
       <c r="F304" s="5" t="n"/>
-      <c r="G304" s="6" t="n"/>
+      <c r="G304" s="5" t="n"/>
+      <c r="H304" s="6" t="n"/>
     </row>
     <row r="305" hidden="1" outlineLevel="2">
       <c r="A305" s="4" t="n">
@@ -3995,9 +4317,10 @@
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="6" t="n"/>
       <c r="D305" s="6" t="n"/>
-      <c r="E305" s="5" t="n"/>
+      <c r="E305" s="6" t="n"/>
       <c r="F305" s="5" t="n"/>
-      <c r="G305" s="6" t="n"/>
+      <c r="G305" s="5" t="n"/>
+      <c r="H305" s="6" t="n"/>
     </row>
     <row r="306" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A306" s="4" t="n">
@@ -4006,9 +4329,10 @@
       <c r="B306" s="5" t="n"/>
       <c r="C306" s="6" t="n"/>
       <c r="D306" s="6" t="n"/>
-      <c r="E306" s="5" t="n"/>
+      <c r="E306" s="6" t="n"/>
       <c r="F306" s="5" t="n"/>
-      <c r="G306" s="6" t="n"/>
+      <c r="G306" s="5" t="n"/>
+      <c r="H306" s="6" t="n"/>
     </row>
     <row r="307" hidden="1" outlineLevel="2">
       <c r="A307" s="4" t="n">
@@ -4017,9 +4341,10 @@
       <c r="B307" s="5" t="n"/>
       <c r="C307" s="6" t="n"/>
       <c r="D307" s="6" t="n"/>
-      <c r="E307" s="5" t="n"/>
+      <c r="E307" s="6" t="n"/>
       <c r="F307" s="5" t="n"/>
-      <c r="G307" s="6" t="n"/>
+      <c r="G307" s="5" t="n"/>
+      <c r="H307" s="6" t="n"/>
     </row>
     <row r="308" hidden="1" outlineLevel="2">
       <c r="A308" s="4" t="n">
@@ -4028,9 +4353,10 @@
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="6" t="n"/>
       <c r="D308" s="6" t="n"/>
-      <c r="E308" s="5" t="n"/>
+      <c r="E308" s="6" t="n"/>
       <c r="F308" s="5" t="n"/>
-      <c r="G308" s="6" t="n"/>
+      <c r="G308" s="5" t="n"/>
+      <c r="H308" s="6" t="n"/>
     </row>
     <row r="309" hidden="1" outlineLevel="2">
       <c r="A309" s="4" t="n">
@@ -4039,9 +4365,10 @@
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="6" t="n"/>
       <c r="D309" s="6" t="n"/>
-      <c r="E309" s="5" t="n"/>
+      <c r="E309" s="6" t="n"/>
       <c r="F309" s="5" t="n"/>
-      <c r="G309" s="6" t="n"/>
+      <c r="G309" s="5" t="n"/>
+      <c r="H309" s="6" t="n"/>
     </row>
     <row r="310" collapsed="1" ht="28.8" customHeight="1">
       <c r="A310" s="4" t="n">
@@ -4059,9 +4386,10 @@
         </is>
       </c>
       <c r="D310" s="6" t="n"/>
-      <c r="E310" s="5" t="n"/>
+      <c r="E310" s="6" t="n"/>
       <c r="F310" s="5" t="n"/>
-      <c r="G310" s="6" t="n"/>
+      <c r="G310" s="5" t="n"/>
+      <c r="H310" s="6" t="n"/>
     </row>
     <row r="311" hidden="1" outlineLevel="2">
       <c r="A311" s="4" t="n">
@@ -4070,9 +4398,10 @@
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="6" t="n"/>
       <c r="D311" s="6" t="n"/>
-      <c r="E311" s="5" t="n"/>
+      <c r="E311" s="6" t="n"/>
       <c r="F311" s="5" t="n"/>
-      <c r="G311" s="6" t="n"/>
+      <c r="G311" s="5" t="n"/>
+      <c r="H311" s="6" t="n"/>
     </row>
     <row r="312" collapsed="1" ht="28.8" customHeight="1">
       <c r="A312" s="4" t="n">
@@ -4090,9 +4419,10 @@
         </is>
       </c>
       <c r="D312" s="6" t="n"/>
-      <c r="E312" s="5" t="n"/>
+      <c r="E312" s="6" t="n"/>
       <c r="F312" s="5" t="n"/>
-      <c r="G312" s="6" t="n"/>
+      <c r="G312" s="5" t="n"/>
+      <c r="H312" s="6" t="n"/>
     </row>
     <row r="313" hidden="1" outlineLevel="2">
       <c r="A313" s="4" t="n">
@@ -4101,9 +4431,10 @@
       <c r="B313" s="5" t="n"/>
       <c r="C313" s="6" t="n"/>
       <c r="D313" s="6" t="n"/>
-      <c r="E313" s="5" t="n"/>
+      <c r="E313" s="6" t="n"/>
       <c r="F313" s="5" t="n"/>
-      <c r="G313" s="6" t="n"/>
+      <c r="G313" s="5" t="n"/>
+      <c r="H313" s="6" t="n"/>
     </row>
     <row r="314" ht="28.8" customHeight="1">
       <c r="A314" s="4" t="n">
@@ -4122,9 +4453,10 @@
         </is>
       </c>
       <c r="D314" s="6" t="n"/>
-      <c r="E314" s="5" t="n"/>
+      <c r="E314" s="6" t="n"/>
       <c r="F314" s="5" t="n"/>
-      <c r="G314" s="6" t="n"/>
+      <c r="G314" s="5" t="n"/>
+      <c r="H314" s="6" t="n"/>
     </row>
     <row r="315" outlineLevel="2">
       <c r="A315" s="4" t="n">
@@ -4133,9 +4465,10 @@
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="6" t="n"/>
       <c r="D315" s="6" t="n"/>
-      <c r="E315" s="5" t="n"/>
+      <c r="E315" s="6" t="n"/>
       <c r="F315" s="5" t="n"/>
-      <c r="G315" s="6" t="n"/>
+      <c r="G315" s="5" t="n"/>
+      <c r="H315" s="6" t="n"/>
     </row>
     <row r="316" outlineLevel="2">
       <c r="A316" s="4" t="n">
@@ -4144,9 +4477,10 @@
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="6" t="n"/>
       <c r="D316" s="6" t="n"/>
-      <c r="E316" s="5" t="n"/>
+      <c r="E316" s="6" t="n"/>
       <c r="F316" s="5" t="n"/>
-      <c r="G316" s="6" t="n"/>
+      <c r="G316" s="5" t="n"/>
+      <c r="H316" s="6" t="n"/>
     </row>
     <row r="317" outlineLevel="2">
       <c r="A317" s="4" t="n">
@@ -4155,9 +4489,10 @@
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="6" t="n"/>
       <c r="D317" s="6" t="n"/>
-      <c r="E317" s="5" t="n"/>
+      <c r="E317" s="6" t="n"/>
       <c r="F317" s="5" t="n"/>
-      <c r="G317" s="6" t="n"/>
+      <c r="G317" s="5" t="n"/>
+      <c r="H317" s="6" t="n"/>
     </row>
     <row r="318" outlineLevel="1" collapsed="1">
       <c r="A318" s="4" t="n">
@@ -4166,9 +4501,10 @@
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="6" t="n"/>
       <c r="D318" s="6" t="n"/>
-      <c r="E318" s="5" t="n"/>
+      <c r="E318" s="6" t="n"/>
       <c r="F318" s="5" t="n"/>
-      <c r="G318" s="6" t="n"/>
+      <c r="G318" s="5" t="n"/>
+      <c r="H318" s="6" t="n"/>
     </row>
     <row r="319" hidden="1" outlineLevel="2">
       <c r="A319" s="4" t="n">
@@ -4177,9 +4513,10 @@
       <c r="B319" s="5" t="n"/>
       <c r="C319" s="6" t="n"/>
       <c r="D319" s="6" t="n"/>
-      <c r="E319" s="5" t="n"/>
+      <c r="E319" s="6" t="n"/>
       <c r="F319" s="5" t="n"/>
-      <c r="G319" s="6" t="n"/>
+      <c r="G319" s="5" t="n"/>
+      <c r="H319" s="6" t="n"/>
     </row>
     <row r="320" hidden="1" outlineLevel="2">
       <c r="A320" s="4" t="n">
@@ -4188,9 +4525,10 @@
       <c r="B320" s="5" t="n"/>
       <c r="C320" s="6" t="n"/>
       <c r="D320" s="6" t="n"/>
-      <c r="E320" s="5" t="n"/>
+      <c r="E320" s="6" t="n"/>
       <c r="F320" s="5" t="n"/>
-      <c r="G320" s="6" t="n"/>
+      <c r="G320" s="5" t="n"/>
+      <c r="H320" s="6" t="n"/>
     </row>
     <row r="321" hidden="1" outlineLevel="2">
       <c r="A321" s="4" t="n">
@@ -4199,9 +4537,10 @@
       <c r="B321" s="5" t="n"/>
       <c r="C321" s="6" t="n"/>
       <c r="D321" s="6" t="n"/>
-      <c r="E321" s="5" t="n"/>
+      <c r="E321" s="6" t="n"/>
       <c r="F321" s="5" t="n"/>
-      <c r="G321" s="6" t="n"/>
+      <c r="G321" s="5" t="n"/>
+      <c r="H321" s="6" t="n"/>
     </row>
     <row r="322" outlineLevel="1" collapsed="1">
       <c r="A322" s="4" t="n">
@@ -4210,9 +4549,10 @@
       <c r="B322" s="5" t="n"/>
       <c r="C322" s="6" t="n"/>
       <c r="D322" s="6" t="n"/>
-      <c r="E322" s="5" t="n"/>
+      <c r="E322" s="6" t="n"/>
       <c r="F322" s="5" t="n"/>
-      <c r="G322" s="6" t="n"/>
+      <c r="G322" s="5" t="n"/>
+      <c r="H322" s="6" t="n"/>
     </row>
     <row r="323" hidden="1" outlineLevel="2">
       <c r="A323" s="4" t="n">
@@ -4221,9 +4561,10 @@
       <c r="B323" s="5" t="n"/>
       <c r="C323" s="6" t="n"/>
       <c r="D323" s="6" t="n"/>
-      <c r="E323" s="5" t="n"/>
+      <c r="E323" s="6" t="n"/>
       <c r="F323" s="5" t="n"/>
-      <c r="G323" s="6" t="n"/>
+      <c r="G323" s="5" t="n"/>
+      <c r="H323" s="6" t="n"/>
     </row>
     <row r="324" hidden="1" outlineLevel="2">
       <c r="A324" s="4" t="n">
@@ -4232,9 +4573,10 @@
       <c r="B324" s="5" t="n"/>
       <c r="C324" s="6" t="n"/>
       <c r="D324" s="6" t="n"/>
-      <c r="E324" s="5" t="n"/>
+      <c r="E324" s="6" t="n"/>
       <c r="F324" s="5" t="n"/>
-      <c r="G324" s="6" t="n"/>
+      <c r="G324" s="5" t="n"/>
+      <c r="H324" s="6" t="n"/>
     </row>
     <row r="325" hidden="1" outlineLevel="2">
       <c r="A325" s="4" t="n">
@@ -4243,9 +4585,10 @@
       <c r="B325" s="5" t="n"/>
       <c r="C325" s="6" t="n"/>
       <c r="D325" s="6" t="n"/>
-      <c r="E325" s="5" t="n"/>
+      <c r="E325" s="6" t="n"/>
       <c r="F325" s="5" t="n"/>
-      <c r="G325" s="6" t="n"/>
+      <c r="G325" s="5" t="n"/>
+      <c r="H325" s="6" t="n"/>
     </row>
     <row r="326" outlineLevel="1">
       <c r="A326" s="4" t="n">
@@ -4254,9 +4597,10 @@
       <c r="B326" s="5" t="n"/>
       <c r="C326" s="6" t="n"/>
       <c r="D326" s="6" t="n"/>
-      <c r="E326" s="5" t="n"/>
+      <c r="E326" s="6" t="n"/>
       <c r="F326" s="5" t="n"/>
-      <c r="G326" s="6" t="n"/>
+      <c r="G326" s="5" t="n"/>
+      <c r="H326" s="6" t="n"/>
     </row>
     <row r="327" outlineLevel="2">
       <c r="A327" s="4" t="n">
@@ -4265,9 +4609,10 @@
       <c r="B327" s="5" t="n"/>
       <c r="C327" s="6" t="n"/>
       <c r="D327" s="6" t="n"/>
-      <c r="E327" s="5" t="n"/>
+      <c r="E327" s="6" t="n"/>
       <c r="F327" s="5" t="n"/>
-      <c r="G327" s="6" t="n"/>
+      <c r="G327" s="5" t="n"/>
+      <c r="H327" s="6" t="n"/>
     </row>
     <row r="328" outlineLevel="2" ht="43.2" customHeight="1">
       <c r="A328" s="4" t="n">
@@ -4280,9 +4625,10 @@
         </is>
       </c>
       <c r="D328" s="6" t="n"/>
-      <c r="E328" s="5" t="n"/>
+      <c r="E328" s="6" t="n"/>
       <c r="F328" s="5" t="n"/>
-      <c r="G328" s="6" t="n"/>
+      <c r="G328" s="5" t="n"/>
+      <c r="H328" s="6" t="n"/>
     </row>
     <row r="329" outlineLevel="2">
       <c r="A329" s="4" t="n">
@@ -4295,9 +4641,10 @@
         </is>
       </c>
       <c r="D329" s="6" t="n"/>
-      <c r="E329" s="5" t="n"/>
+      <c r="E329" s="6" t="n"/>
       <c r="F329" s="5" t="n"/>
-      <c r="G329" s="6" t="n"/>
+      <c r="G329" s="5" t="n"/>
+      <c r="H329" s="6" t="n"/>
     </row>
     <row r="330" outlineLevel="1" collapsed="1">
       <c r="A330" s="4" t="n">
@@ -4310,9 +4657,10 @@
         </is>
       </c>
       <c r="D330" s="6" t="n"/>
-      <c r="E330" s="5" t="n"/>
+      <c r="E330" s="6" t="n"/>
       <c r="F330" s="5" t="n"/>
-      <c r="G330" s="6" t="n"/>
+      <c r="G330" s="5" t="n"/>
+      <c r="H330" s="6" t="n"/>
     </row>
     <row r="331" hidden="1" outlineLevel="2">
       <c r="A331" s="4" t="n">
@@ -4321,9 +4669,10 @@
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="6" t="n"/>
       <c r="D331" s="6" t="n"/>
-      <c r="E331" s="5" t="n"/>
+      <c r="E331" s="6" t="n"/>
       <c r="F331" s="5" t="n"/>
-      <c r="G331" s="6" t="n"/>
+      <c r="G331" s="5" t="n"/>
+      <c r="H331" s="6" t="n"/>
     </row>
     <row r="332" hidden="1" outlineLevel="2">
       <c r="A332" s="4" t="n">
@@ -4332,9 +4681,10 @@
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="6" t="n"/>
       <c r="D332" s="6" t="n"/>
-      <c r="E332" s="5" t="n"/>
+      <c r="E332" s="6" t="n"/>
       <c r="F332" s="5" t="n"/>
-      <c r="G332" s="6" t="n"/>
+      <c r="G332" s="5" t="n"/>
+      <c r="H332" s="6" t="n"/>
     </row>
     <row r="333" hidden="1" outlineLevel="2">
       <c r="A333" s="4" t="n">
@@ -4343,9 +4693,10 @@
       <c r="B333" s="5" t="n"/>
       <c r="C333" s="6" t="n"/>
       <c r="D333" s="6" t="n"/>
-      <c r="E333" s="5" t="n"/>
+      <c r="E333" s="6" t="n"/>
       <c r="F333" s="5" t="n"/>
-      <c r="G333" s="6" t="n"/>
+      <c r="G333" s="5" t="n"/>
+      <c r="H333" s="6" t="n"/>
     </row>
     <row r="334" outlineLevel="1" collapsed="1">
       <c r="A334" s="4" t="n">
@@ -4354,9 +4705,10 @@
       <c r="B334" s="5" t="n"/>
       <c r="C334" s="6" t="n"/>
       <c r="D334" s="6" t="n"/>
-      <c r="E334" s="5" t="n"/>
+      <c r="E334" s="6" t="n"/>
       <c r="F334" s="5" t="n"/>
-      <c r="G334" s="6" t="n"/>
+      <c r="G334" s="5" t="n"/>
+      <c r="H334" s="6" t="n"/>
     </row>
     <row r="335" hidden="1" outlineLevel="2">
       <c r="A335" s="4" t="n">
@@ -4365,9 +4717,10 @@
       <c r="B335" s="5" t="n"/>
       <c r="C335" s="6" t="n"/>
       <c r="D335" s="6" t="n"/>
-      <c r="E335" s="5" t="n"/>
+      <c r="E335" s="6" t="n"/>
       <c r="F335" s="5" t="n"/>
-      <c r="G335" s="6" t="n"/>
+      <c r="G335" s="5" t="n"/>
+      <c r="H335" s="6" t="n"/>
     </row>
     <row r="336" hidden="1" outlineLevel="2">
       <c r="A336" s="4" t="n">
@@ -4376,9 +4729,10 @@
       <c r="B336" s="5" t="n"/>
       <c r="C336" s="6" t="n"/>
       <c r="D336" s="6" t="n"/>
-      <c r="E336" s="5" t="n"/>
+      <c r="E336" s="6" t="n"/>
       <c r="F336" s="5" t="n"/>
-      <c r="G336" s="6" t="n"/>
+      <c r="G336" s="5" t="n"/>
+      <c r="H336" s="6" t="n"/>
     </row>
     <row r="337" hidden="1" outlineLevel="2">
       <c r="A337" s="4" t="n">
@@ -4387,9 +4741,10 @@
       <c r="B337" s="5" t="n"/>
       <c r="C337" s="6" t="n"/>
       <c r="D337" s="6" t="n"/>
-      <c r="E337" s="5" t="n"/>
+      <c r="E337" s="6" t="n"/>
       <c r="F337" s="5" t="n"/>
-      <c r="G337" s="6" t="n"/>
+      <c r="G337" s="5" t="n"/>
+      <c r="H337" s="6" t="n"/>
     </row>
     <row r="338" outlineLevel="1" collapsed="1">
       <c r="A338" s="4" t="n">
@@ -4398,9 +4753,10 @@
       <c r="B338" s="5" t="n"/>
       <c r="C338" s="6" t="n"/>
       <c r="D338" s="6" t="n"/>
-      <c r="E338" s="5" t="n"/>
+      <c r="E338" s="6" t="n"/>
       <c r="F338" s="5" t="n"/>
-      <c r="G338" s="6" t="n"/>
+      <c r="G338" s="5" t="n"/>
+      <c r="H338" s="6" t="n"/>
     </row>
     <row r="339" hidden="1" outlineLevel="2">
       <c r="A339" s="4" t="n">
@@ -4409,9 +4765,10 @@
       <c r="B339" s="5" t="n"/>
       <c r="C339" s="6" t="n"/>
       <c r="D339" s="6" t="n"/>
-      <c r="E339" s="5" t="n"/>
+      <c r="E339" s="6" t="n"/>
       <c r="F339" s="5" t="n"/>
-      <c r="G339" s="6" t="n"/>
+      <c r="G339" s="5" t="n"/>
+      <c r="H339" s="6" t="n"/>
     </row>
     <row r="340" hidden="1" outlineLevel="2">
       <c r="A340" s="4" t="n">
@@ -4420,9 +4777,10 @@
       <c r="B340" s="5" t="n"/>
       <c r="C340" s="6" t="n"/>
       <c r="D340" s="6" t="n"/>
-      <c r="E340" s="5" t="n"/>
+      <c r="E340" s="6" t="n"/>
       <c r="F340" s="5" t="n"/>
-      <c r="G340" s="6" t="n"/>
+      <c r="G340" s="5" t="n"/>
+      <c r="H340" s="6" t="n"/>
     </row>
     <row r="341" hidden="1" outlineLevel="2">
       <c r="A341" s="4" t="n">
@@ -4431,9 +4789,10 @@
       <c r="B341" s="5" t="n"/>
       <c r="C341" s="6" t="n"/>
       <c r="D341" s="6" t="n"/>
-      <c r="E341" s="5" t="n"/>
+      <c r="E341" s="6" t="n"/>
       <c r="F341" s="5" t="n"/>
-      <c r="G341" s="6" t="n"/>
+      <c r="G341" s="5" t="n"/>
+      <c r="H341" s="6" t="n"/>
     </row>
     <row r="342" outlineLevel="1">
       <c r="A342" s="4" t="n">
@@ -4442,9 +4801,10 @@
       <c r="B342" s="5" t="n"/>
       <c r="C342" s="6" t="n"/>
       <c r="D342" s="6" t="n"/>
-      <c r="E342" s="5" t="n"/>
+      <c r="E342" s="6" t="n"/>
       <c r="F342" s="5" t="n"/>
-      <c r="G342" s="6" t="n"/>
+      <c r="G342" s="5" t="n"/>
+      <c r="H342" s="6" t="n"/>
     </row>
     <row r="343" outlineLevel="2">
       <c r="A343" s="4" t="n">
@@ -4453,9 +4813,10 @@
       <c r="B343" s="5" t="n"/>
       <c r="C343" s="6" t="n"/>
       <c r="D343" s="6" t="n"/>
-      <c r="E343" s="5" t="n"/>
+      <c r="E343" s="6" t="n"/>
       <c r="F343" s="5" t="n"/>
-      <c r="G343" s="6" t="n"/>
+      <c r="G343" s="5" t="n"/>
+      <c r="H343" s="6" t="n"/>
     </row>
     <row r="344" outlineLevel="2" ht="43.2" customHeight="1">
       <c r="A344" s="4" t="n">
@@ -4468,9 +4829,10 @@
         </is>
       </c>
       <c r="D344" s="6" t="n"/>
-      <c r="E344" s="5" t="n"/>
+      <c r="E344" s="6" t="n"/>
       <c r="F344" s="5" t="n"/>
-      <c r="G344" s="6" t="n"/>
+      <c r="G344" s="5" t="n"/>
+      <c r="H344" s="6" t="n"/>
     </row>
     <row r="345" outlineLevel="2">
       <c r="A345" s="4" t="n">
@@ -4483,9 +4845,10 @@
         </is>
       </c>
       <c r="D345" s="6" t="n"/>
-      <c r="E345" s="5" t="n"/>
+      <c r="E345" s="6" t="n"/>
       <c r="F345" s="5" t="n"/>
-      <c r="G345" s="6" t="n"/>
+      <c r="G345" s="5" t="n"/>
+      <c r="H345" s="6" t="n"/>
     </row>
     <row r="346" ht="28.8" customHeight="1">
       <c r="A346" s="4" t="n">
@@ -4504,9 +4867,10 @@
         </is>
       </c>
       <c r="D346" s="6" t="n"/>
-      <c r="E346" s="5" t="n"/>
+      <c r="E346" s="6" t="n"/>
       <c r="F346" s="5" t="n"/>
-      <c r="G346" s="6" t="n"/>
+      <c r="G346" s="5" t="n"/>
+      <c r="H346" s="6" t="n"/>
     </row>
     <row r="347" outlineLevel="2">
       <c r="A347" s="4" t="n">
@@ -4515,9 +4879,10 @@
       <c r="B347" s="5" t="n"/>
       <c r="C347" s="6" t="n"/>
       <c r="D347" s="6" t="n"/>
-      <c r="E347" s="5" t="n"/>
+      <c r="E347" s="6" t="n"/>
       <c r="F347" s="5" t="n"/>
-      <c r="G347" s="6" t="n"/>
+      <c r="G347" s="5" t="n"/>
+      <c r="H347" s="6" t="n"/>
     </row>
     <row r="348" outlineLevel="2">
       <c r="A348" s="4" t="n">
@@ -4526,9 +4891,10 @@
       <c r="B348" s="5" t="n"/>
       <c r="C348" s="6" t="n"/>
       <c r="D348" s="6" t="n"/>
-      <c r="E348" s="5" t="n"/>
+      <c r="E348" s="6" t="n"/>
       <c r="F348" s="5" t="n"/>
-      <c r="G348" s="6" t="n"/>
+      <c r="G348" s="5" t="n"/>
+      <c r="H348" s="6" t="n"/>
     </row>
     <row r="349" outlineLevel="2">
       <c r="A349" s="4" t="n">
@@ -4537,9 +4903,10 @@
       <c r="B349" s="5" t="n"/>
       <c r="C349" s="6" t="n"/>
       <c r="D349" s="6" t="n"/>
-      <c r="E349" s="5" t="n"/>
+      <c r="E349" s="6" t="n"/>
       <c r="F349" s="5" t="n"/>
-      <c r="G349" s="6" t="n"/>
+      <c r="G349" s="5" t="n"/>
+      <c r="H349" s="6" t="n"/>
     </row>
     <row r="350" outlineLevel="1" collapsed="1">
       <c r="A350" s="4" t="n">
@@ -4548,9 +4915,10 @@
       <c r="B350" s="5" t="n"/>
       <c r="C350" s="6" t="n"/>
       <c r="D350" s="6" t="n"/>
-      <c r="E350" s="5" t="n"/>
+      <c r="E350" s="6" t="n"/>
       <c r="F350" s="5" t="n"/>
-      <c r="G350" s="6" t="n"/>
+      <c r="G350" s="5" t="n"/>
+      <c r="H350" s="6" t="n"/>
     </row>
     <row r="351" hidden="1" outlineLevel="2">
       <c r="A351" s="4" t="n">
@@ -4559,9 +4927,10 @@
       <c r="B351" s="5" t="n"/>
       <c r="C351" s="6" t="n"/>
       <c r="D351" s="6" t="n"/>
-      <c r="E351" s="5" t="n"/>
+      <c r="E351" s="6" t="n"/>
       <c r="F351" s="5" t="n"/>
-      <c r="G351" s="6" t="n"/>
+      <c r="G351" s="5" t="n"/>
+      <c r="H351" s="6" t="n"/>
     </row>
     <row r="352" hidden="1" outlineLevel="2">
       <c r="A352" s="4" t="n">
@@ -4570,9 +4939,10 @@
       <c r="B352" s="5" t="n"/>
       <c r="C352" s="6" t="n"/>
       <c r="D352" s="6" t="n"/>
-      <c r="E352" s="5" t="n"/>
+      <c r="E352" s="6" t="n"/>
       <c r="F352" s="5" t="n"/>
-      <c r="G352" s="6" t="n"/>
+      <c r="G352" s="5" t="n"/>
+      <c r="H352" s="6" t="n"/>
     </row>
     <row r="353" hidden="1" outlineLevel="2">
       <c r="A353" s="4" t="n">
@@ -4581,9 +4951,10 @@
       <c r="B353" s="5" t="n"/>
       <c r="C353" s="6" t="n"/>
       <c r="D353" s="6" t="n"/>
-      <c r="E353" s="5" t="n"/>
+      <c r="E353" s="6" t="n"/>
       <c r="F353" s="5" t="n"/>
-      <c r="G353" s="6" t="n"/>
+      <c r="G353" s="5" t="n"/>
+      <c r="H353" s="6" t="n"/>
     </row>
     <row r="354" outlineLevel="1" collapsed="1">
       <c r="A354" s="4" t="n">
@@ -4592,9 +4963,10 @@
       <c r="B354" s="5" t="n"/>
       <c r="C354" s="6" t="n"/>
       <c r="D354" s="6" t="n"/>
-      <c r="E354" s="5" t="n"/>
+      <c r="E354" s="6" t="n"/>
       <c r="F354" s="5" t="n"/>
-      <c r="G354" s="6" t="n"/>
+      <c r="G354" s="5" t="n"/>
+      <c r="H354" s="6" t="n"/>
     </row>
     <row r="355" hidden="1" outlineLevel="2">
       <c r="A355" s="4" t="n">
@@ -4603,9 +4975,10 @@
       <c r="B355" s="5" t="n"/>
       <c r="C355" s="6" t="n"/>
       <c r="D355" s="6" t="n"/>
-      <c r="E355" s="5" t="n"/>
+      <c r="E355" s="6" t="n"/>
       <c r="F355" s="5" t="n"/>
-      <c r="G355" s="6" t="n"/>
+      <c r="G355" s="5" t="n"/>
+      <c r="H355" s="6" t="n"/>
     </row>
     <row r="356" hidden="1" outlineLevel="2">
       <c r="A356" s="4" t="n">
@@ -4614,9 +4987,10 @@
       <c r="B356" s="5" t="n"/>
       <c r="C356" s="6" t="n"/>
       <c r="D356" s="6" t="n"/>
-      <c r="E356" s="5" t="n"/>
+      <c r="E356" s="6" t="n"/>
       <c r="F356" s="5" t="n"/>
-      <c r="G356" s="6" t="n"/>
+      <c r="G356" s="5" t="n"/>
+      <c r="H356" s="6" t="n"/>
     </row>
     <row r="357" hidden="1" outlineLevel="2">
       <c r="A357" s="4" t="n">
@@ -4625,9 +4999,10 @@
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="6" t="n"/>
       <c r="D357" s="6" t="n"/>
-      <c r="E357" s="5" t="n"/>
+      <c r="E357" s="6" t="n"/>
       <c r="F357" s="5" t="n"/>
-      <c r="G357" s="6" t="n"/>
+      <c r="G357" s="5" t="n"/>
+      <c r="H357" s="6" t="n"/>
     </row>
     <row r="358" outlineLevel="1">
       <c r="A358" s="4" t="n">
@@ -4636,9 +5011,10 @@
       <c r="B358" s="5" t="n"/>
       <c r="C358" s="6" t="n"/>
       <c r="D358" s="6" t="n"/>
-      <c r="E358" s="5" t="n"/>
+      <c r="E358" s="6" t="n"/>
       <c r="F358" s="5" t="n"/>
-      <c r="G358" s="6" t="n"/>
+      <c r="G358" s="5" t="n"/>
+      <c r="H358" s="6" t="n"/>
     </row>
     <row r="359" outlineLevel="2">
       <c r="A359" s="4" t="n">
@@ -4647,9 +5023,10 @@
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="6" t="n"/>
       <c r="D359" s="6" t="n"/>
-      <c r="E359" s="5" t="n"/>
+      <c r="E359" s="6" t="n"/>
       <c r="F359" s="5" t="n"/>
-      <c r="G359" s="6" t="n"/>
+      <c r="G359" s="5" t="n"/>
+      <c r="H359" s="6" t="n"/>
     </row>
     <row r="360" outlineLevel="2" ht="43.2" customHeight="1">
       <c r="A360" s="4" t="n">
@@ -4662,9 +5039,10 @@
         </is>
       </c>
       <c r="D360" s="6" t="n"/>
-      <c r="E360" s="5" t="n"/>
+      <c r="E360" s="6" t="n"/>
       <c r="F360" s="5" t="n"/>
-      <c r="G360" s="6" t="n"/>
+      <c r="G360" s="5" t="n"/>
+      <c r="H360" s="6" t="n"/>
     </row>
     <row r="361" outlineLevel="2">
       <c r="A361" s="4" t="n">
@@ -4677,9 +5055,10 @@
         </is>
       </c>
       <c r="D361" s="6" t="n"/>
-      <c r="E361" s="5" t="n"/>
+      <c r="E361" s="6" t="n"/>
       <c r="F361" s="5" t="n"/>
-      <c r="G361" s="6" t="n"/>
+      <c r="G361" s="5" t="n"/>
+      <c r="H361" s="6" t="n"/>
     </row>
     <row r="362" outlineLevel="1" collapsed="1">
       <c r="A362" s="4" t="n">
@@ -4692,9 +5071,10 @@
         </is>
       </c>
       <c r="D362" s="6" t="n"/>
-      <c r="E362" s="5" t="n"/>
+      <c r="E362" s="6" t="n"/>
       <c r="F362" s="5" t="n"/>
-      <c r="G362" s="6" t="n"/>
+      <c r="G362" s="5" t="n"/>
+      <c r="H362" s="6" t="n"/>
     </row>
     <row r="363" hidden="1" outlineLevel="2">
       <c r="A363" s="4" t="n">
@@ -4703,9 +5083,10 @@
       <c r="B363" s="5" t="n"/>
       <c r="C363" s="6" t="n"/>
       <c r="D363" s="6" t="n"/>
-      <c r="E363" s="5" t="n"/>
+      <c r="E363" s="6" t="n"/>
       <c r="F363" s="5" t="n"/>
-      <c r="G363" s="6" t="n"/>
+      <c r="G363" s="5" t="n"/>
+      <c r="H363" s="6" t="n"/>
     </row>
     <row r="364" hidden="1" outlineLevel="2">
       <c r="A364" s="4" t="n">
@@ -4714,9 +5095,10 @@
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="6" t="n"/>
       <c r="D364" s="6" t="n"/>
-      <c r="E364" s="5" t="n"/>
+      <c r="E364" s="6" t="n"/>
       <c r="F364" s="5" t="n"/>
-      <c r="G364" s="6" t="n"/>
+      <c r="G364" s="5" t="n"/>
+      <c r="H364" s="6" t="n"/>
     </row>
     <row r="365" hidden="1" outlineLevel="2">
       <c r="A365" s="4" t="n">
@@ -4725,9 +5107,10 @@
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="6" t="n"/>
       <c r="D365" s="6" t="n"/>
-      <c r="E365" s="5" t="n"/>
+      <c r="E365" s="6" t="n"/>
       <c r="F365" s="5" t="n"/>
-      <c r="G365" s="6" t="n"/>
+      <c r="G365" s="5" t="n"/>
+      <c r="H365" s="6" t="n"/>
     </row>
     <row r="366" outlineLevel="1" collapsed="1">
       <c r="A366" s="4" t="n">
@@ -4736,9 +5119,10 @@
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="6" t="n"/>
       <c r="D366" s="6" t="n"/>
-      <c r="E366" s="5" t="n"/>
+      <c r="E366" s="6" t="n"/>
       <c r="F366" s="5" t="n"/>
-      <c r="G366" s="6" t="n"/>
+      <c r="G366" s="5" t="n"/>
+      <c r="H366" s="6" t="n"/>
     </row>
     <row r="367" hidden="1" outlineLevel="2">
       <c r="A367" s="4" t="n">
@@ -4747,9 +5131,10 @@
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="6" t="n"/>
       <c r="D367" s="6" t="n"/>
-      <c r="E367" s="5" t="n"/>
+      <c r="E367" s="6" t="n"/>
       <c r="F367" s="5" t="n"/>
-      <c r="G367" s="6" t="n"/>
+      <c r="G367" s="5" t="n"/>
+      <c r="H367" s="6" t="n"/>
     </row>
     <row r="368" hidden="1" outlineLevel="2">
       <c r="A368" s="4" t="n">
@@ -4758,9 +5143,10 @@
       <c r="B368" s="5" t="n"/>
       <c r="C368" s="6" t="n"/>
       <c r="D368" s="6" t="n"/>
-      <c r="E368" s="5" t="n"/>
+      <c r="E368" s="6" t="n"/>
       <c r="F368" s="5" t="n"/>
-      <c r="G368" s="6" t="n"/>
+      <c r="G368" s="5" t="n"/>
+      <c r="H368" s="6" t="n"/>
     </row>
     <row r="369" hidden="1" outlineLevel="2">
       <c r="A369" s="4" t="n">
@@ -4769,9 +5155,10 @@
       <c r="B369" s="5" t="n"/>
       <c r="C369" s="6" t="n"/>
       <c r="D369" s="6" t="n"/>
-      <c r="E369" s="5" t="n"/>
+      <c r="E369" s="6" t="n"/>
       <c r="F369" s="5" t="n"/>
-      <c r="G369" s="6" t="n"/>
+      <c r="G369" s="5" t="n"/>
+      <c r="H369" s="6" t="n"/>
     </row>
     <row r="370" outlineLevel="1" collapsed="1">
       <c r="A370" s="4" t="n">
@@ -4780,9 +5167,10 @@
       <c r="B370" s="5" t="n"/>
       <c r="C370" s="6" t="n"/>
       <c r="D370" s="6" t="n"/>
-      <c r="E370" s="5" t="n"/>
+      <c r="E370" s="6" t="n"/>
       <c r="F370" s="5" t="n"/>
-      <c r="G370" s="6" t="n"/>
+      <c r="G370" s="5" t="n"/>
+      <c r="H370" s="6" t="n"/>
     </row>
     <row r="371" hidden="1" outlineLevel="2">
       <c r="A371" s="4" t="n">
@@ -4791,9 +5179,10 @@
       <c r="B371" s="5" t="n"/>
       <c r="C371" s="6" t="n"/>
       <c r="D371" s="6" t="n"/>
-      <c r="E371" s="5" t="n"/>
+      <c r="E371" s="6" t="n"/>
       <c r="F371" s="5" t="n"/>
-      <c r="G371" s="6" t="n"/>
+      <c r="G371" s="5" t="n"/>
+      <c r="H371" s="6" t="n"/>
     </row>
     <row r="372" hidden="1" outlineLevel="2">
       <c r="A372" s="4" t="n">
@@ -4802,9 +5191,10 @@
       <c r="B372" s="5" t="n"/>
       <c r="C372" s="6" t="n"/>
       <c r="D372" s="6" t="n"/>
-      <c r="E372" s="5" t="n"/>
+      <c r="E372" s="6" t="n"/>
       <c r="F372" s="5" t="n"/>
-      <c r="G372" s="6" t="n"/>
+      <c r="G372" s="5" t="n"/>
+      <c r="H372" s="6" t="n"/>
     </row>
     <row r="373" hidden="1" outlineLevel="2">
       <c r="A373" s="4" t="n">
@@ -4813,9 +5203,10 @@
       <c r="B373" s="5" t="n"/>
       <c r="C373" s="6" t="n"/>
       <c r="D373" s="6" t="n"/>
-      <c r="E373" s="5" t="n"/>
+      <c r="E373" s="6" t="n"/>
       <c r="F373" s="5" t="n"/>
-      <c r="G373" s="6" t="n"/>
+      <c r="G373" s="5" t="n"/>
+      <c r="H373" s="6" t="n"/>
     </row>
     <row r="374" outlineLevel="1" collapsed="1">
       <c r="A374" s="4" t="n">
@@ -4824,9 +5215,10 @@
       <c r="B374" s="5" t="n"/>
       <c r="C374" s="6" t="n"/>
       <c r="D374" s="6" t="n"/>
-      <c r="E374" s="5" t="n"/>
+      <c r="E374" s="6" t="n"/>
       <c r="F374" s="5" t="n"/>
-      <c r="G374" s="6" t="n"/>
+      <c r="G374" s="5" t="n"/>
+      <c r="H374" s="6" t="n"/>
     </row>
     <row r="375" hidden="1" outlineLevel="2">
       <c r="A375" s="4" t="n">
@@ -4835,9 +5227,10 @@
       <c r="B375" s="5" t="n"/>
       <c r="C375" s="6" t="n"/>
       <c r="D375" s="6" t="n"/>
-      <c r="E375" s="5" t="n"/>
+      <c r="E375" s="6" t="n"/>
       <c r="F375" s="5" t="n"/>
-      <c r="G375" s="6" t="n"/>
+      <c r="G375" s="5" t="n"/>
+      <c r="H375" s="6" t="n"/>
     </row>
     <row r="376" hidden="1" outlineLevel="2">
       <c r="A376" s="4" t="n">
@@ -4846,9 +5239,10 @@
       <c r="B376" s="5" t="n"/>
       <c r="C376" s="6" t="n"/>
       <c r="D376" s="6" t="n"/>
-      <c r="E376" s="5" t="n"/>
+      <c r="E376" s="6" t="n"/>
       <c r="F376" s="5" t="n"/>
-      <c r="G376" s="6" t="n"/>
+      <c r="G376" s="5" t="n"/>
+      <c r="H376" s="6" t="n"/>
     </row>
     <row r="377" hidden="1" outlineLevel="2">
       <c r="A377" s="4" t="n">
@@ -4857,9 +5251,10 @@
       <c r="B377" s="5" t="n"/>
       <c r="C377" s="6" t="n"/>
       <c r="D377" s="6" t="n"/>
-      <c r="E377" s="5" t="n"/>
+      <c r="E377" s="6" t="n"/>
       <c r="F377" s="5" t="n"/>
-      <c r="G377" s="6" t="n"/>
+      <c r="G377" s="5" t="n"/>
+      <c r="H377" s="6" t="n"/>
     </row>
     <row r="378" collapsed="1" ht="28.8" customHeight="1">
       <c r="A378" s="4" t="n">
@@ -4877,9 +5272,10 @@
         </is>
       </c>
       <c r="D378" s="6" t="n"/>
-      <c r="E378" s="5" t="n"/>
+      <c r="E378" s="6" t="n"/>
       <c r="F378" s="5" t="n"/>
-      <c r="G378" s="6" t="n"/>
+      <c r="G378" s="5" t="n"/>
+      <c r="H378" s="6" t="n"/>
     </row>
     <row r="379" hidden="1" outlineLevel="2">
       <c r="A379" s="4" t="n">
@@ -4888,9 +5284,10 @@
       <c r="B379" s="5" t="n"/>
       <c r="C379" s="6" t="n"/>
       <c r="D379" s="6" t="n"/>
-      <c r="E379" s="5" t="n"/>
+      <c r="E379" s="6" t="n"/>
       <c r="F379" s="5" t="n"/>
-      <c r="G379" s="6" t="n"/>
+      <c r="G379" s="5" t="n"/>
+      <c r="H379" s="6" t="n"/>
     </row>
     <row r="380" collapsed="1" ht="28.8" customHeight="1">
       <c r="A380" s="4" t="n">
@@ -4908,9 +5305,10 @@
         </is>
       </c>
       <c r="D380" s="6" t="n"/>
-      <c r="E380" s="5" t="n"/>
+      <c r="E380" s="6" t="n"/>
       <c r="F380" s="5" t="n"/>
-      <c r="G380" s="6" t="n"/>
+      <c r="G380" s="5" t="n"/>
+      <c r="H380" s="6" t="n"/>
     </row>
     <row r="381" hidden="1" outlineLevel="2">
       <c r="A381" s="4" t="n">
@@ -4919,9 +5317,10 @@
       <c r="B381" s="5" t="n"/>
       <c r="C381" s="6" t="n"/>
       <c r="D381" s="6" t="n"/>
-      <c r="E381" s="5" t="n"/>
+      <c r="E381" s="6" t="n"/>
       <c r="F381" s="5" t="n"/>
-      <c r="G381" s="6" t="n"/>
+      <c r="G381" s="5" t="n"/>
+      <c r="H381" s="6" t="n"/>
     </row>
     <row r="382" collapsed="1" ht="28.8" customHeight="1">
       <c r="A382" s="4" t="n">
@@ -4939,9 +5338,10 @@
         </is>
       </c>
       <c r="D382" s="6" t="n"/>
-      <c r="E382" s="5" t="n"/>
+      <c r="E382" s="6" t="n"/>
       <c r="F382" s="5" t="n"/>
-      <c r="G382" s="6" t="n"/>
+      <c r="G382" s="5" t="n"/>
+      <c r="H382" s="6" t="n"/>
     </row>
     <row r="383" hidden="1" outlineLevel="2">
       <c r="A383" s="4" t="n">
@@ -4950,9 +5350,10 @@
       <c r="B383" s="5" t="n"/>
       <c r="C383" s="6" t="n"/>
       <c r="D383" s="6" t="n"/>
-      <c r="E383" s="5" t="n"/>
+      <c r="E383" s="6" t="n"/>
       <c r="F383" s="5" t="n"/>
-      <c r="G383" s="6" t="n"/>
+      <c r="G383" s="5" t="n"/>
+      <c r="H383" s="6" t="n"/>
     </row>
     <row r="384" hidden="1" outlineLevel="2">
       <c r="A384" s="4" t="n">
@@ -4961,9 +5362,10 @@
       <c r="B384" s="5" t="n"/>
       <c r="C384" s="6" t="n"/>
       <c r="D384" s="6" t="n"/>
-      <c r="E384" s="5" t="n"/>
+      <c r="E384" s="6" t="n"/>
       <c r="F384" s="5" t="n"/>
-      <c r="G384" s="6" t="n"/>
+      <c r="G384" s="5" t="n"/>
+      <c r="H384" s="6" t="n"/>
     </row>
     <row r="385" hidden="1" outlineLevel="2">
       <c r="A385" s="4" t="n">
@@ -4972,9 +5374,10 @@
       <c r="B385" s="5" t="n"/>
       <c r="C385" s="6" t="n"/>
       <c r="D385" s="6" t="n"/>
-      <c r="E385" s="5" t="n"/>
+      <c r="E385" s="6" t="n"/>
       <c r="F385" s="5" t="n"/>
-      <c r="G385" s="6" t="n"/>
+      <c r="G385" s="5" t="n"/>
+      <c r="H385" s="6" t="n"/>
     </row>
     <row r="386" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A386" s="4" t="n">
@@ -4983,9 +5386,10 @@
       <c r="B386" s="5" t="n"/>
       <c r="C386" s="6" t="n"/>
       <c r="D386" s="6" t="n"/>
-      <c r="E386" s="5" t="n"/>
+      <c r="E386" s="6" t="n"/>
       <c r="F386" s="5" t="n"/>
-      <c r="G386" s="6" t="n"/>
+      <c r="G386" s="5" t="n"/>
+      <c r="H386" s="6" t="n"/>
     </row>
     <row r="387" hidden="1" outlineLevel="2">
       <c r="A387" s="4" t="n">
@@ -4994,9 +5398,10 @@
       <c r="B387" s="5" t="n"/>
       <c r="C387" s="6" t="n"/>
       <c r="D387" s="6" t="n"/>
-      <c r="E387" s="5" t="n"/>
+      <c r="E387" s="6" t="n"/>
       <c r="F387" s="5" t="n"/>
-      <c r="G387" s="6" t="n"/>
+      <c r="G387" s="5" t="n"/>
+      <c r="H387" s="6" t="n"/>
     </row>
     <row r="388" hidden="1" outlineLevel="2">
       <c r="A388" s="4" t="n">
@@ -5005,9 +5410,10 @@
       <c r="B388" s="5" t="n"/>
       <c r="C388" s="6" t="n"/>
       <c r="D388" s="6" t="n"/>
-      <c r="E388" s="5" t="n"/>
+      <c r="E388" s="6" t="n"/>
       <c r="F388" s="5" t="n"/>
-      <c r="G388" s="6" t="n"/>
+      <c r="G388" s="5" t="n"/>
+      <c r="H388" s="6" t="n"/>
     </row>
     <row r="389" hidden="1" outlineLevel="2">
       <c r="A389" s="4" t="n">
@@ -5016,9 +5422,10 @@
       <c r="B389" s="5" t="n"/>
       <c r="C389" s="6" t="n"/>
       <c r="D389" s="6" t="n"/>
-      <c r="E389" s="5" t="n"/>
+      <c r="E389" s="6" t="n"/>
       <c r="F389" s="5" t="n"/>
-      <c r="G389" s="6" t="n"/>
+      <c r="G389" s="5" t="n"/>
+      <c r="H389" s="6" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="7" t="n">
@@ -5034,7 +5441,7 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E390" t="n">
+      <c r="F390" t="n">
         <v>0</v>
       </c>
     </row>
